--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_11sep26_Fri.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_11sep26_Fri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD1CB12-ECF9-4B51-8B4C-FD0C5D65BB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BACBCC1-AF78-40F3-9AEC-DA52BAFC31CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3386" uniqueCount="300">
   <si>
     <t>Date</t>
   </si>
@@ -1103,7 +1103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1279,8 +1279,45 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1681,7 +1718,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B2, $C$2:$C$767, C2, $D$2:$D$767, D2, $E$2:$E$767, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$767, B2, $C$2:$C$767, C2, $D$2:$D$767, D2, $E$2:$E$767, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -1718,7 +1755,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B3, $C$2:$C$767, C3, $D$2:$D$767, D3, $E$2:$E$767, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1755,7 +1792,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B4, $C$2:$C$767, C4, $D$2:$D$767, D4, $E$2:$E$767, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1792,7 +1829,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B5, $C$2:$C$767, C5, $D$2:$D$767, D5, $E$2:$E$767, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1829,7 +1866,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B6, $C$2:$C$767, C6, $D$2:$D$767, D6, $E$2:$E$767, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1866,7 +1903,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B7, $C$2:$C$767, C7, $D$2:$D$767, D7, $E$2:$E$767, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1903,7 +1940,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B8, $C$2:$C$767, C8, $D$2:$D$767, D8, $E$2:$E$767, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1940,7 +1977,7 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B9, $C$2:$C$767, C9, $D$2:$D$767, D9, $E$2:$E$767, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1977,7 +2014,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B10, $C$2:$C$767, C10, $D$2:$D$767, D10, $E$2:$E$767, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10"/>
@@ -2016,7 +2053,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B11, $C$2:$C$767, C11, $D$2:$D$767, D11, $E$2:$E$767, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2053,7 +2090,7 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B12, $C$2:$C$767, C12, $D$2:$D$767, D12, $E$2:$E$767, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2090,7 +2127,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B13, $C$2:$C$767, C13, $D$2:$D$767, D13, $E$2:$E$767, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2129,7 +2166,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B14, $C$2:$C$767, C14, $D$2:$D$767, D14, $E$2:$E$767, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2166,7 +2203,7 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B15, $C$2:$C$767, C15, $D$2:$D$767, D15, $E$2:$E$767, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2212,7 +2249,7 @@
         <v>442</v>
       </c>
       <c r="N16" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B16, $C$2:$C$767, C16, $D$2:$D$767, D16, $E$2:$E$767, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2249,7 +2286,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B17, $C$2:$C$767, C17, $D$2:$D$767, D17, $E$2:$E$767, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2286,7 +2323,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B18, $C$2:$C$767, C18, $D$2:$D$767, D18, $E$2:$E$767, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2325,7 +2362,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B19, $C$2:$C$767, C19, $D$2:$D$767, D19, $E$2:$E$767, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2371,7 +2408,7 @@
         <v>300</v>
       </c>
       <c r="N20" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B20, $C$2:$C$767, C20, $D$2:$D$767, D20, $E$2:$E$767, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2408,7 +2445,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B21, $C$2:$C$767, C21, $D$2:$D$767, D21, $E$2:$E$767, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2445,7 +2482,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B22, $C$2:$C$767, C22, $D$2:$D$767, D22, $E$2:$E$767, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2484,7 +2521,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B23, $C$2:$C$767, C23, $D$2:$D$767, D23, $E$2:$E$767, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2523,7 +2560,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B24, $C$2:$C$767, C24, $D$2:$D$767, D24, $E$2:$E$767, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2564,7 +2601,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B25, $C$2:$C$767, C25, $D$2:$D$767, D25, $E$2:$E$767, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2601,7 +2638,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B26, $C$2:$C$767, C26, $D$2:$D$767, D26, $E$2:$E$767, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2638,7 +2675,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B27, $C$2:$C$767, C27, $D$2:$D$767, D27, $E$2:$E$767, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2675,7 +2712,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B28, $C$2:$C$767, C28, $D$2:$D$767, D28, $E$2:$E$767, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2717,7 +2754,7 @@
         <v>3156</v>
       </c>
       <c r="N29" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B29, $C$2:$C$767, C29, $D$2:$D$767, D29, $E$2:$E$767, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="10"/>
@@ -2756,7 +2793,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B30, $C$2:$C$767, C30, $D$2:$D$767, D30, $E$2:$E$767, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2803,7 +2840,7 @@
         <v>540</v>
       </c>
       <c r="N31" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B31, $C$2:$C$767, C31, $D$2:$D$767, D31, $E$2:$E$767, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2842,7 +2879,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B32, $C$2:$C$767, C32, $D$2:$D$767, D32, $E$2:$E$767, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32" s="10"/>
@@ -2882,7 +2919,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B33, $C$2:$C$767, C33, $D$2:$D$767, D33, $E$2:$E$767, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2921,7 +2958,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B34, $C$2:$C$767, C34, $D$2:$D$767, D34, $E$2:$E$767, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2960,7 +2997,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B35, $C$2:$C$767, C35, $D$2:$D$767, D35, $E$2:$E$767, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3006,7 +3043,7 @@
         <v>300</v>
       </c>
       <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B36, $C$2:$C$767, C36, $D$2:$D$767, D36, $E$2:$E$767, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3043,7 +3080,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B37, $C$2:$C$767, C37, $D$2:$D$767, D37, $E$2:$E$767, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3082,7 +3119,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B38, $C$2:$C$767, C38, $D$2:$D$767, D38, $E$2:$E$767, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3119,7 +3156,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B39, $C$2:$C$767, C39, $D$2:$D$767, D39, $E$2:$E$767, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39" s="10"/>
@@ -3166,7 +3203,7 @@
         <v>460</v>
       </c>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B40, $C$2:$C$767, C40, $D$2:$D$767, D40, $E$2:$E$767, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P40" s="10"/>
@@ -3204,7 +3241,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B41, $C$2:$C$767, C41, $D$2:$D$767, D41, $E$2:$E$767, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -3245,7 +3282,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B42, $C$2:$C$767, C42, $D$2:$D$767, D42, $E$2:$E$767, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -3286,7 +3323,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B43, $C$2:$C$767, C43, $D$2:$D$767, D43, $E$2:$E$767, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3323,7 +3360,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B44, $C$2:$C$767, C44, $D$2:$D$767, D44, $E$2:$E$767, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -3370,7 +3407,7 @@
         <v>300</v>
       </c>
       <c r="N45" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B45, $C$2:$C$767, C45, $D$2:$D$767, D45, $E$2:$E$767, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P45" s="25"/>
@@ -3417,7 +3454,7 @@
         <v>516</v>
       </c>
       <c r="N46" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B46, $C$2:$C$767, C46, $D$2:$D$767, D46, $E$2:$E$767, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3454,7 +3491,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B47, $C$2:$C$767, C47, $D$2:$D$767, D47, $E$2:$E$767, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -3494,7 +3531,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B48, $C$2:$C$767, C48, $D$2:$D$767, D48, $E$2:$E$767, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -3535,7 +3572,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B49, $C$2:$C$767, C49, $D$2:$D$767, D49, $E$2:$E$767, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49"/>
@@ -3576,7 +3613,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B50, $C$2:$C$767, C50, $D$2:$D$767, D50, $E$2:$E$767, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -3617,7 +3654,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B51, $C$2:$C$767, C51, $D$2:$D$767, D51, $E$2:$E$767, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -3666,7 +3703,7 @@
         <v>650</v>
       </c>
       <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B52, $C$2:$C$767, C52, $D$2:$D$767, D52, $E$2:$E$767, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -3707,7 +3744,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B53, $C$2:$C$767, C53, $D$2:$D$767, D53, $E$2:$E$767, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -3748,7 +3785,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B54, $C$2:$C$767, C54, $D$2:$D$767, D54, $E$2:$E$767, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3787,7 +3824,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B55, $C$2:$C$767, C55, $D$2:$D$767, D55, $E$2:$E$767, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55" s="34"/>
@@ -3828,7 +3865,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B56, $C$2:$C$767, C56, $D$2:$D$767, D56, $E$2:$E$767, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -3869,7 +3906,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B57, $C$2:$C$767, C57, $D$2:$D$767, D57, $E$2:$E$767, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3915,7 +3952,7 @@
         <v>300</v>
       </c>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B58, $C$2:$C$767, C58, $D$2:$D$767, D58, $E$2:$E$767, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3954,7 +3991,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B59, $C$2:$C$767, C59, $D$2:$D$767, D59, $E$2:$E$767, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P59"/>
@@ -3992,7 +4029,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B60, $C$2:$C$767, C60, $D$2:$D$767, D60, $E$2:$E$767, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4038,7 +4075,7 @@
         <v>525</v>
       </c>
       <c r="N61" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B61, $C$2:$C$767, C61, $D$2:$D$767, D61, $E$2:$E$767, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4084,7 +4121,7 @@
         <v>300</v>
       </c>
       <c r="N62" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B62, $C$2:$C$767, C62, $D$2:$D$767, D62, $E$2:$E$767, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62"/>
@@ -4125,7 +4162,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B63, $C$2:$C$767, C63, $D$2:$D$767, D63, $E$2:$E$767, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4164,7 +4201,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B64, $C$2:$C$767, C64, $D$2:$D$767, D64, $E$2:$E$767, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -4202,7 +4239,7 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B65, $C$2:$C$767, C65, $D$2:$D$767, D65, $E$2:$E$767, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4241,7 +4278,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B66, $C$2:$C$767, C66, $D$2:$D$767, D66, $E$2:$E$767, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$767, B66, $C$2:$C$767, C66, $D$2:$D$767, D66, $E$2:$E$767, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -4287,7 +4324,7 @@
         <v>300</v>
       </c>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B67, $C$2:$C$767, C67, $D$2:$D$767, D67, $E$2:$E$767, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4326,7 +4363,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B68, $C$2:$C$767, C68, $D$2:$D$767, D68, $E$2:$E$767, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="10"/>
@@ -4367,7 +4404,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B69, $C$2:$C$767, C69, $D$2:$D$767, D69, $E$2:$E$767, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4406,7 +4443,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B70, $C$2:$C$767, C70, $D$2:$D$767, D70, $E$2:$E$767, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -4445,7 +4482,7 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B71, $C$2:$C$767, C71, $D$2:$D$767, D71, $E$2:$E$767, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71" s="19"/>
@@ -4486,7 +4523,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B72, $C$2:$C$767, C72, $D$2:$D$767, D72, $E$2:$E$767, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
@@ -4533,7 +4570,7 @@
         <v>500</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B73, $C$2:$C$767, C73, $D$2:$D$767, D73, $E$2:$E$767, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4570,7 +4607,7 @@
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B74, $C$2:$C$767, C74, $D$2:$D$767, D74, $E$2:$E$767, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74" s="26"/>
@@ -4610,7 +4647,7 @@
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B75, $C$2:$C$767, C75, $D$2:$D$767, D75, $E$2:$E$767, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4649,7 +4686,7 @@
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B76, $C$2:$C$767, C76, $D$2:$D$767, D76, $E$2:$E$767, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4688,7 +4725,7 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B77, $C$2:$C$767, C77, $D$2:$D$767, D77, $E$2:$E$767, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P77" s="26"/>
@@ -4728,11 +4765,11 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B78, $C$2:$C$767, C78, $D$2:$D$767, D78, $E$2:$E$767, E78) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" s="25" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" s="25" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3">
         <v>46304.375</v>
       </c>
@@ -4774,7 +4811,7 @@
         <v>26810</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B79, $C$2:$C$767, C79, $D$2:$D$767, D79, $E$2:$E$767, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="10"/>
@@ -4815,12 +4852,12 @@
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B80, $C$2:$C$767, C80, $D$2:$D$767, D80, $E$2:$E$767, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P80" s="25"/>
     </row>
-    <row r="81" spans="1:16" s="35" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" s="35" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="36">
         <v>46267.375</v>
       </c>
@@ -4858,11 +4895,11 @@
         <v>5755</v>
       </c>
       <c r="M81" s="33">
-        <f>ABS((D81*E81)-L81)</f>
+        <f t="shared" ref="M81:M86" si="2">ABS((D81*E81)-L81)</f>
         <v>275</v>
       </c>
       <c r="N81" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B81, $C$2:$C$767, C81, $D$2:$D$767, D81, $E$2:$E$767, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O81" s="46" t="s">
@@ -4870,7 +4907,7 @@
       </c>
       <c r="P81" s="10"/>
     </row>
-    <row r="82" spans="1:16" s="35" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:16" s="35" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="36">
         <v>46267.375</v>
       </c>
@@ -4908,11 +4945,11 @@
         <v>5805</v>
       </c>
       <c r="M82" s="33">
-        <f>ABS((D82*E82)-L82)</f>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="N82" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B82, $C$2:$C$767, C82, $D$2:$D$767, D82, $E$2:$E$767, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O82" s="46" t="s">
@@ -4920,7 +4957,7 @@
       </c>
       <c r="P82" s="10"/>
     </row>
-    <row r="83" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="3">
         <v>46275.375</v>
       </c>
@@ -4958,15 +4995,15 @@
         <v>10400</v>
       </c>
       <c r="M83" s="18">
-        <f>ABS((D83*E83)-L83)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B83, $C$2:$C$767, C83, $D$2:$D$767, D83, $E$2:$E$767, E83) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="3">
         <v>46276.375590277778</v>
       </c>
@@ -4980,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="E84" s="4">
-        <v>13698</v>
+        <v>14298</v>
       </c>
       <c r="F84" s="4">
         <v>1.76820208</v>
@@ -5004,15 +5041,15 @@
         <v>13052</v>
       </c>
       <c r="M84" s="18">
-        <f>ABS((D84*E84)-L84)</f>
-        <v>646</v>
+        <f t="shared" si="2"/>
+        <v>1246</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B84, $C$2:$C$767, C84, $D$2:$D$767, D84, $E$2:$E$767, E84) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3">
         <v>46304.375</v>
       </c>
@@ -5050,11 +5087,11 @@
         <v>35880</v>
       </c>
       <c r="M85" s="18">
-        <f>ABS((D85*E85)-L85)</f>
+        <f t="shared" si="2"/>
         <v>26710</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B85, $C$2:$C$767, C85, $D$2:$D$767, D85, $E$2:$E$767, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="46" t="s">
@@ -5099,15 +5136,15 @@
         <v>56375</v>
       </c>
       <c r="M86" s="18">
-        <f>ABS((D86*E86)-L86)</f>
+        <f t="shared" si="2"/>
         <v>34175</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B86, $C$2:$C$767, C86, $D$2:$D$767, D86, $E$2:$E$767, E86) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -5142,14 +5179,14 @@
       <c r="L87" s="18"/>
       <c r="M87" s="18"/>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B87, $C$2:$C$767, C87, $D$2:$D$767, D87, $E$2:$E$767, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="88" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="48">
         <v>46273.375</v>
       </c>
@@ -5177,7 +5214,7 @@
       <c r="I88" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J88" s="61" t="s">
+      <c r="J88" s="33" t="s">
         <v>117</v>
       </c>
       <c r="K88" s="33" t="s">
@@ -5187,11 +5224,11 @@
         <v>19730.5</v>
       </c>
       <c r="M88" s="33">
-        <f>ABS((D88*E88)-L88)</f>
+        <f t="shared" ref="M88:M102" si="3">ABS((D88*E88)-L88)</f>
         <v>504.5</v>
       </c>
       <c r="N88" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B88, $C$2:$C$767, C88, $D$2:$D$767, D88, $E$2:$E$767, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O88" s="46" t="s">
@@ -5199,7 +5236,7 @@
       </c>
       <c r="P88" s="35"/>
     </row>
-    <row r="89" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="36">
         <v>46274.375</v>
       </c>
@@ -5227,7 +5264,7 @@
       <c r="I89" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="61" t="s">
+      <c r="J89" s="33" t="s">
         <v>117</v>
       </c>
       <c r="K89" s="33" t="s">
@@ -5237,11 +5274,11 @@
         <v>19690</v>
       </c>
       <c r="M89" s="33">
-        <f>ABS((D89*E89)-L89)</f>
+        <f t="shared" si="3"/>
         <v>545</v>
       </c>
       <c r="N89" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B89, $C$2:$C$767, C89, $D$2:$D$767, D89, $E$2:$E$767, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O89" s="46" t="s">
@@ -5249,7 +5286,7 @@
       </c>
       <c r="P89" s="35"/>
     </row>
-    <row r="90" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="3">
         <v>46304.375</v>
       </c>
@@ -5287,67 +5324,65 @@
         <v>35880</v>
       </c>
       <c r="M90" s="18">
-        <f>ABS((D90*E90)-L90)</f>
+        <f t="shared" si="3"/>
         <v>26610</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B90, $C$2:$C$767, C90, $D$2:$D$767, D90, $E$2:$E$767, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="10"/>
       <c r="P90" s="10"/>
     </row>
-    <row r="91" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="55">
+    <row r="91" spans="1:16" s="67" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="61">
         <v>46265.375694444447</v>
       </c>
-      <c r="B91" s="53" t="s">
+      <c r="B91" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="C91" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91" s="52">
+      <c r="C91" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="63">
         <v>5</v>
       </c>
-      <c r="E91" s="52">
+      <c r="E91" s="63">
         <v>1236</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="63">
         <v>3.7086759520000001</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="H91" s="5">
+      <c r="H91" s="65">
         <v>1191.8</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="54" t="s">
+      <c r="I91" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="K91" s="54" t="s">
+      <c r="K91" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="L91" s="54">
+      <c r="L91" s="66">
         <v>5905</v>
       </c>
-      <c r="M91" s="54">
-        <f>ABS((D91*E91)-L91)</f>
+      <c r="M91" s="66">
+        <f t="shared" si="3"/>
         <v>275</v>
       </c>
-      <c r="N91" s="56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B91, $C$2:$C$767, C91, $D$2:$D$767, D91, $E$2:$E$767, E91) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O91" s="25"/>
-      <c r="P91" s="25" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N91" s="67" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O91" s="68"/>
+      <c r="P91" s="68"/>
+    </row>
+    <row r="92" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="36">
         <v>46262.375</v>
       </c>
@@ -5385,18 +5420,18 @@
         <v>3560</v>
       </c>
       <c r="M92" s="33">
-        <f>ABS((D92*E92)-L92)</f>
+        <f t="shared" si="3"/>
         <v>175</v>
       </c>
       <c r="N92" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B92, $C$2:$C$767, C92, $D$2:$D$767, D92, $E$2:$E$767, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O92" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="36">
         <v>46265.375694444447</v>
       </c>
@@ -5434,11 +5469,11 @@
         <v>3510</v>
       </c>
       <c r="M93" s="33">
-        <f>ABS((D93*E93)-L93)</f>
+        <f t="shared" si="3"/>
         <v>225</v>
       </c>
       <c r="N93" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B93, $C$2:$C$767, C93, $D$2:$D$767, D93, $E$2:$E$767, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O93" s="46" t="s">
@@ -5446,7 +5481,7 @@
       </c>
       <c r="P93" s="10"/>
     </row>
-    <row r="94" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3">
         <v>46276.375590277778</v>
       </c>
@@ -5484,17 +5519,17 @@
         <v>8700</v>
       </c>
       <c r="M94" s="18">
-        <f>ABS((D94*E94)-L94)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B94, $C$2:$C$767, C94, $D$2:$D$767, D94, $E$2:$E$767, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94" s="10"/>
       <c r="P94" s="10"/>
     </row>
-    <row r="95" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="3">
         <v>46267.375</v>
       </c>
@@ -5532,18 +5567,18 @@
         <v>8220</v>
       </c>
       <c r="M95" s="18">
-        <f>ABS((D95*E95)-L95)</f>
+        <f t="shared" si="3"/>
         <v>360</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B95, $C$2:$C$767, C95, $D$2:$D$767, D95, $E$2:$E$767, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="96" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -5581,17 +5616,17 @@
         <v>20010</v>
       </c>
       <c r="M96" s="18">
-        <f>ABS((D96*E96)-L96)</f>
+        <f t="shared" si="3"/>
         <v>450</v>
       </c>
       <c r="N96" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B96, $C$2:$C$767, C96, $D$2:$D$767, D96, $E$2:$E$767, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O96" s="10"/>
       <c r="P96"/>
     </row>
-    <row r="97" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="11">
         <v>46273.375</v>
       </c>
@@ -5629,17 +5664,17 @@
         <v>9170</v>
       </c>
       <c r="M97" s="33">
-        <f>ABS((D97*E97)-L97)</f>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B97, $C$2:$C$767, C97, $D$2:$D$767, D97, $E$2:$E$767, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O97" s="10"/>
       <c r="P97" s="10"/>
     </row>
-    <row r="98" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -5677,11 +5712,11 @@
         <v>8480</v>
       </c>
       <c r="M98" s="27">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" si="3"/>
         <v>280</v>
       </c>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B98, $C$2:$C$767, C98, $D$2:$D$767, D98, $E$2:$E$767, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="46" t="s">
@@ -5727,11 +5762,11 @@
         <v>73800</v>
       </c>
       <c r="M99" s="18">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="3"/>
         <v>48320</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B99, $C$2:$C$767, C99, $D$2:$D$767, D99, $E$2:$E$767, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="46" t="s">
@@ -5739,7 +5774,7 @@
       </c>
       <c r="P99" s="10"/>
     </row>
-    <row r="100" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -5777,17 +5812,17 @@
         <v>20260</v>
       </c>
       <c r="M100" s="18">
-        <f>ABS((D100*E100)-L100)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N100" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B100, $C$2:$C$767, C100, $D$2:$D$767, D100, $E$2:$E$767, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O100"/>
       <c r="P100" s="35"/>
     </row>
-    <row r="101" spans="1:16" s="19" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:16" s="19" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
         <v>46274.414583333331</v>
       </c>
@@ -5825,11 +5860,11 @@
         <v>9902</v>
       </c>
       <c r="M101" s="18">
-        <f>ABS((D101*E101)-L101)</f>
+        <f t="shared" si="3"/>
         <v>646</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B101, $C$2:$C$767, C101, $D$2:$D$767, D101, $E$2:$E$767, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="46" t="s">
@@ -5837,7 +5872,7 @@
       </c>
       <c r="P101" s="10"/>
     </row>
-    <row r="102" spans="1:16" s="26" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:16" s="26" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3">
         <v>46275.375</v>
       </c>
@@ -5875,17 +5910,17 @@
         <v>35880</v>
       </c>
       <c r="M102" s="18">
-        <f>ABS((D102*E102)-L102)</f>
+        <f t="shared" si="3"/>
         <v>26460</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B102, $C$2:$C$767, C102, $D$2:$D$767, D102, $E$2:$E$767, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="10"/>
       <c r="P102" s="10"/>
     </row>
-    <row r="103" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -5915,11 +5950,11 @@
       </c>
       <c r="J103" s="40"/>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B103, $C$2:$C$767, C103, $D$2:$D$767, D103, $E$2:$E$767, E103) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -5949,7 +5984,7 @@
       </c>
       <c r="J104" s="40"/>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B104, $C$2:$C$767, C104, $D$2:$D$767, D104, $E$2:$E$767, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="46" t="s">
@@ -5957,7 +5992,7 @@
       </c>
       <c r="P104"/>
     </row>
-    <row r="105" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>46261.375</v>
       </c>
@@ -5999,13 +6034,13 @@
         <v>300</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B105, $C$2:$C$767, C105, $D$2:$D$767, D105, $E$2:$E$767, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105"/>
       <c r="P105" s="10"/>
     </row>
-    <row r="106" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="36">
         <v>46269.542361111111</v>
       </c>
@@ -6047,7 +6082,7 @@
         <v>300.00000000000182</v>
       </c>
       <c r="N106" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B106, $C$2:$C$767, C106, $D$2:$D$767, D106, $E$2:$E$767, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="46" t="s">
@@ -6055,7 +6090,7 @@
       </c>
       <c r="P106" s="35"/>
     </row>
-    <row r="107" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="36">
         <v>46272.530555555553</v>
       </c>
@@ -6097,7 +6132,7 @@
         <v>274</v>
       </c>
       <c r="N107" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B107, $C$2:$C$767, C107, $D$2:$D$767, D107, $E$2:$E$767, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="46" t="s">
@@ -6105,7 +6140,7 @@
       </c>
       <c r="P107" s="35"/>
     </row>
-    <row r="108" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="36">
         <v>46260.556944444441</v>
       </c>
@@ -6147,11 +6182,11 @@
         <v>150</v>
       </c>
       <c r="N108" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B108, $C$2:$C$767, C108, $D$2:$D$767, D108, $E$2:$E$767, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="109" spans="1:16" s="25" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:16" s="25" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="36">
         <v>46261.375</v>
       </c>
@@ -6193,13 +6228,13 @@
         <v>250</v>
       </c>
       <c r="N109" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B109, $C$2:$C$767, C109, $D$2:$D$767, D109, $E$2:$E$767, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O109" s="10"/>
       <c r="P109" s="10"/>
     </row>
-    <row r="110" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="8" t="s">
         <v>62</v>
       </c>
@@ -6229,11 +6264,11 @@
       </c>
       <c r="J110" s="40"/>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B110, $C$2:$C$767, C110, $D$2:$D$767, D110, $E$2:$E$767, E110) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3">
         <v>46274.375</v>
       </c>
@@ -6271,15 +6306,15 @@
         <v>20070</v>
       </c>
       <c r="M111" s="18">
-        <f>ABS((D111*E111)-L111)</f>
+        <f t="shared" ref="M111:M123" si="4">ABS((D111*E111)-L111)</f>
         <v>810</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B111, $C$2:$C$767, C111, $D$2:$D$767, D111, $E$2:$E$767, E111) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -6317,18 +6352,18 @@
         <v>15075</v>
       </c>
       <c r="M112" s="18">
-        <f>ABS((D112*E112)-L112)</f>
+        <f t="shared" si="4"/>
         <v>645</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B112, $C$2:$C$767, C112, $D$2:$D$767, D112, $E$2:$E$767, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O112" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="113" spans="1:16" s="26" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:16" s="26" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="11">
         <v>46273.375</v>
       </c>
@@ -6366,17 +6401,17 @@
         <v>9170</v>
       </c>
       <c r="M113" s="33">
-        <f>ABS((D113*E113)-L113)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B113, $C$2:$C$767, C113, $D$2:$D$767, D113, $E$2:$E$767, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O113" s="10"/>
       <c r="P113" s="10"/>
     </row>
-    <row r="114" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3">
         <v>46262.375</v>
       </c>
@@ -6414,15 +6449,15 @@
         <v>8420</v>
       </c>
       <c r="M114" s="18">
-        <f>ABS((D114*E114)-L114)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B114, $C$2:$C$767, C114, $D$2:$D$767, D114, $E$2:$E$767, E114) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3">
         <v>46276.375590277778</v>
       </c>
@@ -6460,15 +6495,15 @@
         <v>11320</v>
       </c>
       <c r="M115" s="18">
-        <f>ABS((D115*E115)-L115)</f>
+        <f t="shared" si="4"/>
         <v>400</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B115, $C$2:$C$767, C115, $D$2:$D$767, D115, $E$2:$E$767, E115) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
         <v>46267.375</v>
       </c>
@@ -6506,17 +6541,17 @@
         <v>3005</v>
       </c>
       <c r="M116" s="18">
-        <f>ABS((D116*E116)-L116)</f>
+        <f t="shared" si="4"/>
         <v>240</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B116, $C$2:$C$767, C116, $D$2:$D$767, D116, $E$2:$E$767, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="10"/>
       <c r="P116" s="26"/>
     </row>
-    <row r="117" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>46335.442361111112</v>
       </c>
@@ -6554,11 +6589,11 @@
         <v>14100</v>
       </c>
       <c r="M117" s="18">
-        <f>ABS((D117*E117)-L117)</f>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B117, $C$2:$C$767, C117, $D$2:$D$767, D117, $E$2:$E$767, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="10"/>
@@ -6602,18 +6637,18 @@
         <v>73800</v>
       </c>
       <c r="M118" s="18">
-        <f>ABS((D118*E118)-L118)</f>
+        <f t="shared" si="4"/>
         <v>47900</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B118, $C$2:$C$767, C118, $D$2:$D$767, D118, $E$2:$E$767, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3">
         <v>46276.375613425924</v>
       </c>
@@ -6651,15 +6686,15 @@
         <v>18960</v>
       </c>
       <c r="M119" s="18">
-        <f>ABS((D119*E119)-L119)</f>
+        <f t="shared" si="4"/>
         <v>816</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B119, $C$2:$C$767, C119, $D$2:$D$767, D119, $E$2:$E$767, E119) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3">
         <v>46275.375</v>
       </c>
@@ -6697,11 +6732,11 @@
         <v>3300</v>
       </c>
       <c r="M120" s="18">
-        <f>ABS((D120*E120)-L120)</f>
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B120, $C$2:$C$767, C120, $D$2:$D$767, D120, $E$2:$E$767, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6743,11 +6778,11 @@
         <v>25300</v>
       </c>
       <c r="M121" s="18">
-        <f>ABS((D121*E121)-L121)</f>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B121, $C$2:$C$767, C121, $D$2:$D$767, D121, $E$2:$E$767, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="46" t="s">
@@ -6792,18 +6827,18 @@
         <v>12480</v>
       </c>
       <c r="M122" s="18">
-        <f>ABS((D122*E122)-L122)</f>
+        <f t="shared" si="4"/>
         <v>495</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B122, $C$2:$C$767, C122, $D$2:$D$767, D122, $E$2:$E$767, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3">
         <v>46268.375</v>
       </c>
@@ -6841,15 +6876,15 @@
         <v>32200</v>
       </c>
       <c r="M123" s="18">
-        <f>ABS((D123*E123)-L123)</f>
+        <f t="shared" si="4"/>
         <v>1200</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B123, $C$2:$C$767, C123, $D$2:$D$767, D123, $E$2:$E$767, E123) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="11">
         <v>46252.645833333336</v>
       </c>
@@ -6879,12 +6914,12 @@
       </c>
       <c r="J124" s="40"/>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B124, $C$2:$C$767, C124, $D$2:$D$767, D124, $E$2:$E$767, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="25"/>
     </row>
-    <row r="125" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="11">
         <v>46243.375</v>
       </c>
@@ -6922,11 +6957,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M125" s="33">
-        <f>ABS((D125*E125)-L125)</f>
+        <f t="shared" ref="M125:M130" si="5">ABS((D125*E125)-L125)</f>
         <v>710.99999999999636</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B125, $C$2:$C$767, C125, $D$2:$D$767, D125, $E$2:$E$767, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O125" s="46" t="s">
@@ -6934,7 +6969,7 @@
       </c>
       <c r="P125"/>
     </row>
-    <row r="126" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="11">
         <v>46243.375</v>
       </c>
@@ -6972,18 +7007,18 @@
         <v>8570</v>
       </c>
       <c r="M126" s="33">
-        <f>ABS((D126*E126)-L126)</f>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B126, $C$2:$C$767, C126, $D$2:$D$767, D126, $E$2:$E$767, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3">
         <v>46267.375</v>
       </c>
@@ -7021,16 +7056,16 @@
         <v>9270</v>
       </c>
       <c r="M127" s="18">
-        <f>ABS((D127*E127)-L127)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B127, $C$2:$C$767, C127, $D$2:$D$767, D127, $E$2:$E$767, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P127" s="19"/>
     </row>
-    <row r="128" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3">
         <v>46266.375</v>
       </c>
@@ -7068,17 +7103,17 @@
         <v>10300</v>
       </c>
       <c r="M128" s="18">
-        <f>ABS((D128*E128)-L128)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B128, $C$2:$C$767, C128, $D$2:$D$767, D128, $E$2:$E$767, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
       <c r="P128" s="35"/>
     </row>
-    <row r="129" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3">
         <v>46276.400173611109</v>
       </c>
@@ -7116,11 +7151,11 @@
         <v>14200</v>
       </c>
       <c r="M129" s="18">
-        <f>ABS((D129*E129)-L129)</f>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B129, $C$2:$C$767, C129, $D$2:$D$767, D129, $E$2:$E$767, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7162,11 +7197,11 @@
         <v>25780</v>
       </c>
       <c r="M130" s="18">
-        <f>ABS((D130*E130)-L130)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N130" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B130, $C$2:$C$767, C130, $D$2:$D$767, D130, $E$2:$E$767, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="6">IF(COUNTIFS( $B$2:$B$767, B130, $C$2:$C$767, C130, $D$2:$D$767, D130, $E$2:$E$767, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="46" t="s">
@@ -7174,7 +7209,7 @@
       </c>
       <c r="P130"/>
     </row>
-    <row r="131" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -7206,11 +7241,11 @@
         <v>117</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B131, $C$2:$C$767, C131, $D$2:$D$767, D131, $E$2:$E$767, E131) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3">
         <v>46274.375</v>
       </c>
@@ -7252,11 +7287,11 @@
         <v>651</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B132, $C$2:$C$767, C132, $D$2:$D$767, D132, $E$2:$E$767, E132) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3">
         <v>46274.375</v>
       </c>
@@ -7298,11 +7333,11 @@
         <v>300</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B133, $C$2:$C$767, C133, $D$2:$D$767, D133, $E$2:$E$767, E133) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -7344,13 +7379,13 @@
         <v>650</v>
       </c>
       <c r="N134" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B134, $C$2:$C$767, C134, $D$2:$D$767, D134, $E$2:$E$767, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O134"/>
       <c r="P134"/>
     </row>
-    <row r="135" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3">
         <v>46267.425694444442</v>
       </c>
@@ -7392,14 +7427,14 @@
         <v>270</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B135, $C$2:$C$767, C135, $D$2:$D$767, D135, $E$2:$E$767, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O135" s="47" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="8" t="s">
         <v>62</v>
       </c>
@@ -7429,11 +7464,11 @@
       </c>
       <c r="J136" s="40"/>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B136, $C$2:$C$767, C136, $D$2:$D$767, D136, $E$2:$E$767, E136) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -7475,14 +7510,14 @@
         <v>880</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B137, $C$2:$C$767, C137, $D$2:$D$767, D137, $E$2:$E$767, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="8" t="s">
         <v>62</v>
       </c>
@@ -7514,11 +7549,11 @@
         <v>118</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B138, $C$2:$C$767, C138, $D$2:$D$767, D138, $E$2:$E$767, E138) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="3">
         <v>46267.375</v>
       </c>
@@ -7556,15 +7591,15 @@
         <v>4080</v>
       </c>
       <c r="M139" s="18">
-        <f>ABS((D139*E139)-L139)</f>
+        <f t="shared" ref="M139:M144" si="7">ABS((D139*E139)-L139)</f>
         <v>300</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B139, $C$2:$C$767, C139, $D$2:$D$767, D139, $E$2:$E$767, E139) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3">
         <v>46335.62777777778</v>
       </c>
@@ -7578,7 +7613,7 @@
         <v>20</v>
       </c>
       <c r="E140" s="4">
-        <v>286.5</v>
+        <v>284.5</v>
       </c>
       <c r="F140" s="4">
         <v>7.3636874649999999</v>
@@ -7602,15 +7637,15 @@
         <v>5370</v>
       </c>
       <c r="M140" s="18">
-        <f>ABS((D140*E140)-L140)</f>
-        <v>360</v>
+        <f t="shared" si="7"/>
+        <v>320</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B140, $C$2:$C$767, C140, $D$2:$D$767, D140, $E$2:$E$767, E140) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="50">
         <v>46273.385416666664</v>
       </c>
@@ -7648,11 +7683,11 @@
         <v>16580</v>
       </c>
       <c r="M141" s="54">
-        <f>ABS((D141*E141)-L141)</f>
+        <f t="shared" si="7"/>
         <v>750</v>
       </c>
       <c r="N141" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B141, $C$2:$C$767, C141, $D$2:$D$767, D141, $E$2:$E$767, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="25"/>
@@ -7660,7 +7695,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3">
         <v>46262.375</v>
       </c>
@@ -7698,16 +7733,16 @@
         <v>10410</v>
       </c>
       <c r="M142" s="18">
-        <f>ABS((D142*E142)-L142)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B142, $C$2:$C$767, C142, $D$2:$D$767, D142, $E$2:$E$767, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="35"/>
     </row>
-    <row r="143" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -7745,15 +7780,15 @@
         <v>73800</v>
       </c>
       <c r="M143" s="18">
-        <f>ABS((D143*E143)-L143)</f>
+        <f t="shared" si="7"/>
         <v>47480</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B143, $C$2:$C$767, C143, $D$2:$D$767, D143, $E$2:$E$767, E143) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -7791,15 +7826,15 @@
         <v>12510</v>
       </c>
       <c r="M144" s="18">
-        <f>ABS((D144*E144)-L144)</f>
+        <f t="shared" si="7"/>
         <v>290</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B144, $C$2:$C$767, C144, $D$2:$D$767, D144, $E$2:$E$767, E144) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="8" t="s">
         <v>62</v>
       </c>
@@ -7829,11 +7864,11 @@
       </c>
       <c r="J145" s="40"/>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B145, $C$2:$C$767, C145, $D$2:$D$767, D145, $E$2:$E$767, E145) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="36">
         <v>46267.461111111108</v>
       </c>
@@ -7871,16 +7906,16 @@
         <v>32900</v>
       </c>
       <c r="M146" s="33">
-        <f>ABS((D146*E146)-L146)</f>
+        <f t="shared" ref="M146:M158" si="8">ABS((D146*E146)-L146)</f>
         <v>1000</v>
       </c>
       <c r="N146" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B146, $C$2:$C$767, C146, $D$2:$D$767, D146, $E$2:$E$767, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O146" s="26"/>
     </row>
-    <row r="147" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="36">
         <v>46267.38958333333</v>
       </c>
@@ -7918,15 +7953,15 @@
         <v>33200</v>
       </c>
       <c r="M147" s="33">
-        <f>ABS((D147*E147)-L147)</f>
+        <f t="shared" si="8"/>
         <v>700</v>
       </c>
       <c r="N147" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B147, $C$2:$C$767, C147, $D$2:$D$767, D147, $E$2:$E$767, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="148" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -7964,17 +7999,17 @@
         <v>26020</v>
       </c>
       <c r="M148" s="18">
-        <f>ABS((D148*E148)-L148)</f>
+        <f t="shared" si="8"/>
         <v>340</v>
       </c>
       <c r="N148" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B148, $C$2:$C$767, C148, $D$2:$D$767, D148, $E$2:$E$767, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="10"/>
       <c r="P148" s="10"/>
     </row>
-    <row r="149" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3">
         <v>46274.375</v>
       </c>
@@ -8012,18 +8047,18 @@
         <v>11660</v>
       </c>
       <c r="M149" s="18">
-        <f>ABS((D149*E149)-L149)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B149, $C$2:$C$767, C149, $D$2:$D$767, D149, $E$2:$E$767, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="3">
         <v>46276.390462962961</v>
       </c>
@@ -8061,15 +8096,15 @@
         <v>14400</v>
       </c>
       <c r="M150" s="18">
-        <f>ABS((D150*E150)-L150)</f>
+        <f t="shared" si="8"/>
         <v>500</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B150, $C$2:$C$767, C150, $D$2:$D$767, D150, $E$2:$E$767, E150) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="3">
         <v>46269.643055555556</v>
       </c>
@@ -8107,15 +8142,15 @@
         <v>5180</v>
       </c>
       <c r="M151" s="27">
-        <f>ABS((D151*E151)-L151)</f>
+        <f t="shared" si="8"/>
         <v>268</v>
       </c>
       <c r="N151" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B151, $C$2:$C$767, C151, $D$2:$D$767, D151, $E$2:$E$767, E151) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3">
         <v>46269.411111111112</v>
       </c>
@@ -8153,18 +8188,18 @@
         <v>18140</v>
       </c>
       <c r="M152" s="27">
-        <f>ABS((D152*E152)-L152)</f>
+        <f t="shared" si="8"/>
         <v>650</v>
       </c>
       <c r="N152" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B152, $C$2:$C$767, C152, $D$2:$D$767, D152, $E$2:$E$767, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="153" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -8202,17 +8237,17 @@
         <v>26180</v>
       </c>
       <c r="M153" s="18">
-        <f>ABS((D153*E153)-L153)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B153, $C$2:$C$767, C153, $D$2:$D$767, D153, $E$2:$E$767, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="10"/>
       <c r="P153" s="10"/>
     </row>
-    <row r="154" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3">
         <v>46267.375</v>
       </c>
@@ -8250,15 +8285,15 @@
         <v>16755</v>
       </c>
       <c r="M154" s="18">
-        <f>ABS((D154*E154)-L154)</f>
+        <f t="shared" si="8"/>
         <v>295</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B154, $C$2:$C$767, C154, $D$2:$D$767, D154, $E$2:$E$767, E154) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3">
         <v>46335.421527777777</v>
       </c>
@@ -8296,15 +8331,15 @@
         <v>8049</v>
       </c>
       <c r="M155" s="18">
-        <f>ABS((D155*E155)-L155)</f>
+        <f t="shared" si="8"/>
         <v>800</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B155, $C$2:$C$767, C155, $D$2:$D$767, D155, $E$2:$E$767, E155) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3">
         <v>46261.375</v>
       </c>
@@ -8342,15 +8377,15 @@
         <v>10510</v>
       </c>
       <c r="M156" s="18">
-        <f>ABS((D156*E156)-L156)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B156, $C$2:$C$767, C156, $D$2:$D$767, D156, $E$2:$E$767, E156) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -8388,18 +8423,18 @@
         <v>18800</v>
       </c>
       <c r="M157" s="18">
-        <f>ABS((D157*E157)-L157)</f>
+        <f t="shared" si="8"/>
         <v>500</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B157, $C$2:$C$767, C157, $D$2:$D$767, D157, $E$2:$E$767, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O157" s="47" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="158" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -8437,15 +8472,15 @@
         <v>9470</v>
       </c>
       <c r="M158" s="18">
-        <f>ABS((D158*E158)-L158)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B158, $C$2:$C$767, C158, $D$2:$D$767, D158, $E$2:$E$767, E158) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="11">
         <v>46252.6875</v>
       </c>
@@ -8477,11 +8512,11 @@
         <v>118</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B159, $C$2:$C$767, C159, $D$2:$D$767, D159, $E$2:$E$767, E159) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3">
         <v>46262.375</v>
       </c>
@@ -8523,11 +8558,11 @@
         <v>300</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B160, $C$2:$C$767, C160, $D$2:$D$767, D160, $E$2:$E$767, E160) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="51" t="s">
         <v>62</v>
       </c>
@@ -8562,7 +8597,7 @@
       <c r="L161" s="54"/>
       <c r="M161" s="54"/>
       <c r="N161" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B161, $C$2:$C$767, C161, $D$2:$D$767, D161, $E$2:$E$767, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="25"/>
@@ -8570,7 +8605,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="162" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3">
         <v>46266.375</v>
       </c>
@@ -8608,15 +8643,15 @@
         <v>12600</v>
       </c>
       <c r="M162" s="18">
-        <f>ABS((D162*E162)-L162)</f>
+        <f t="shared" ref="M162:M168" si="9">ABS((D162*E162)-L162)</f>
         <v>360</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B162, $C$2:$C$767, C162, $D$2:$D$767, D162, $E$2:$E$767, E162) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3">
         <v>46274.375</v>
       </c>
@@ -8654,15 +8689,15 @@
         <v>3400</v>
       </c>
       <c r="M163" s="18">
-        <f>ABS((D163*E163)-L163)</f>
+        <f t="shared" si="9"/>
         <v>250</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B163, $C$2:$C$767, C163, $D$2:$D$767, D163, $E$2:$E$767, E163) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="36">
         <v>46265.375694444447</v>
       </c>
@@ -8700,17 +8735,17 @@
         <v>7578</v>
       </c>
       <c r="M164" s="33">
-        <f>ABS((D164*E164)-L164)</f>
+        <f t="shared" si="9"/>
         <v>294</v>
       </c>
       <c r="N164" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B164, $C$2:$C$767, C164, $D$2:$D$767, D164, $E$2:$E$767, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O164" s="10"/>
       <c r="P164" s="10"/>
     </row>
-    <row r="165" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="36">
         <v>46266.375694444447</v>
       </c>
@@ -8748,153 +8783,153 @@
         <v>7578</v>
       </c>
       <c r="M165" s="33">
-        <f>ABS((D165*E165)-L165)</f>
+        <f t="shared" si="9"/>
         <v>294</v>
       </c>
       <c r="N165" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B165, $C$2:$C$767, C165, $D$2:$D$767, D165, $E$2:$E$767, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="166" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="3">
+    <row r="166" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="69">
         <v>46267.424305555556</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B166" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D166" s="4">
+      <c r="C166" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D166" s="71">
         <v>2</v>
       </c>
-      <c r="E166" s="4">
+      <c r="E166" s="71">
         <v>2624</v>
       </c>
-      <c r="F166" s="4">
+      <c r="F166" s="71">
         <v>8.9746251919999995</v>
       </c>
-      <c r="G166" s="2" t="s">
+      <c r="G166" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="H166" s="5">
+      <c r="H166" s="73">
         <v>2407.9</v>
       </c>
-      <c r="I166" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J166" s="18" t="s">
+      <c r="I166" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="J166" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="K166" s="18" t="s">
+      <c r="K166" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="L166" s="18">
+      <c r="L166" s="33">
         <v>4968</v>
       </c>
-      <c r="M166" s="18">
-        <f>ABS((D166*E166)-L166)</f>
+      <c r="M166" s="33">
+        <f t="shared" si="9"/>
         <v>280</v>
       </c>
-      <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B166, $C$2:$C$767, C166, $D$2:$D$767, D166, $E$2:$E$767, E166) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="3">
+      <c r="N166" s="35" t="str">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="69">
         <v>46272.451388888891</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B167" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D167" s="4">
+      <c r="C167" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" s="71">
         <v>5</v>
       </c>
-      <c r="E167" s="4">
+      <c r="E167" s="71">
         <v>1894</v>
       </c>
-      <c r="F167" s="4">
+      <c r="F167" s="71">
         <v>8.975834292</v>
       </c>
-      <c r="G167" s="2" t="s">
+      <c r="G167" s="72" t="s">
         <v>91</v>
       </c>
-      <c r="H167" s="5">
+      <c r="H167" s="73">
         <v>1738</v>
       </c>
-      <c r="I167" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J167" s="10" t="s">
+      <c r="I167" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="J167" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="K167" s="18" t="s">
+      <c r="K167" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="L167" s="18">
+      <c r="L167" s="33">
         <v>8820</v>
       </c>
-      <c r="M167" s="18">
-        <f>ABS((D167*E167)-L167)</f>
+      <c r="M167" s="33">
+        <f t="shared" si="9"/>
         <v>650</v>
       </c>
-      <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B167, $C$2:$C$767, C167, $D$2:$D$767, D167, $E$2:$E$767, E167) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="3">
+      <c r="N167" s="35" t="str">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A168" s="69">
         <v>46272.390972222223</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B168" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C168" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D168" s="4">
+      <c r="C168" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168" s="71">
         <v>20</v>
       </c>
-      <c r="E168" s="4">
+      <c r="E168" s="71">
         <v>1894</v>
       </c>
-      <c r="F168" s="4">
+      <c r="F168" s="71">
         <v>8.975834292</v>
       </c>
-      <c r="G168" s="2" t="s">
+      <c r="G168" s="72" t="s">
         <v>91</v>
       </c>
-      <c r="H168" s="5">
+      <c r="H168" s="73">
         <v>1738</v>
       </c>
-      <c r="I168" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J168" s="10" t="s">
+      <c r="I168" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="J168" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="K168" s="18" t="s">
+      <c r="K168" s="33" t="s">
         <v>255</v>
       </c>
-      <c r="L168" s="18">
+      <c r="L168" s="33">
         <v>36946</v>
       </c>
-      <c r="M168" s="18">
-        <f>ABS((D168*E168)-L168)</f>
+      <c r="M168" s="33">
+        <f t="shared" si="9"/>
         <v>934</v>
       </c>
-      <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B168, $C$2:$C$767, C168, $D$2:$D$767, D168, $E$2:$E$767, E168) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N168" s="35" t="str">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -8931,18 +8966,18 @@
       <c r="L169" s="17"/>
       <c r="M169" s="17"/>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B169, $C$2:$C$767, C169, $D$2:$D$767, D169, $E$2:$E$767, E169) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="11">
         <v>46252.635416666664</v>
       </c>
       <c r="B170" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C170" s="8" t="s">
+      <c r="C170" s="74" t="s">
         <v>7</v>
       </c>
       <c r="D170" s="8">
@@ -8965,12 +9000,12 @@
       </c>
       <c r="J170" s="40"/>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B170, $C$2:$C$767, C170, $D$2:$D$767, D170, $E$2:$E$767, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O170" s="35"/>
     </row>
-    <row r="171" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="3">
         <v>46266.642361111109</v>
       </c>
@@ -9012,11 +9047,11 @@
         <v>500</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B171, $C$2:$C$767, C171, $D$2:$D$767, D171, $E$2:$E$767, E171) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="3">
         <v>46276.388252314813</v>
       </c>
@@ -9058,11 +9093,11 @@
         <v>450</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B172, $C$2:$C$767, C172, $D$2:$D$767, D172, $E$2:$E$767, E172) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="8" t="s">
         <v>62</v>
       </c>
@@ -9094,11 +9129,11 @@
         <v>118</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B173, $C$2:$C$767, C173, $D$2:$D$767, D173, $E$2:$E$767, E173) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="3">
         <v>46265.474999999999</v>
       </c>
@@ -9140,11 +9175,11 @@
         <v>300</v>
       </c>
       <c r="N174" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B174, $C$2:$C$767, C174, $D$2:$D$767, D174, $E$2:$E$767, E174) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -9186,7 +9221,7 @@
         <v>650</v>
       </c>
       <c r="N175" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B175, $C$2:$C$767, C175, $D$2:$D$767, D175, $E$2:$E$767, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O175" s="46" t="s">
@@ -9194,7 +9229,7 @@
       </c>
       <c r="P175" s="35"/>
     </row>
-    <row r="176" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="11">
         <v>46252.6875</v>
       </c>
@@ -9226,11 +9261,11 @@
         <v>117</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B176, $C$2:$C$767, C176, $D$2:$D$767, D176, $E$2:$E$767, E176) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -9272,11 +9307,11 @@
         <v>250</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B177, $C$2:$C$767, C177, $D$2:$D$767, D177, $E$2:$E$767, E177) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -9318,11 +9353,11 @@
         <v>300</v>
       </c>
       <c r="N178" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B178, $C$2:$C$767, C178, $D$2:$D$767, D178, $E$2:$E$767, E178) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="8" t="s">
         <v>62</v>
       </c>
@@ -9355,13 +9390,13 @@
       <c r="L179" s="18"/>
       <c r="M179" s="18"/>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B179, $C$2:$C$767, C179, $D$2:$D$767, D179, $E$2:$E$767, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="10"/>
       <c r="P179" s="10"/>
     </row>
-    <row r="180" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="3">
         <v>46260.554861111108</v>
       </c>
@@ -9403,13 +9438,13 @@
         <v>250</v>
       </c>
       <c r="N180" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B180, $C$2:$C$767, C180, $D$2:$D$767, D180, $E$2:$E$767, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="10"/>
       <c r="P180" s="10"/>
     </row>
-    <row r="181" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="11">
         <v>46252.6875</v>
       </c>
@@ -9441,11 +9476,11 @@
         <v>156</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B181, $C$2:$C$767, C181, $D$2:$D$767, D181, $E$2:$E$767, E181) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9477,14 +9512,14 @@
         <v>118</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B182, $C$2:$C$767, C182, $D$2:$D$767, D182, $E$2:$E$767, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O182" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="183" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9514,11 +9549,11 @@
       </c>
       <c r="J183" s="21"/>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B183, $C$2:$C$767, C183, $D$2:$D$767, D183, $E$2:$E$767, E183) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="3">
         <v>46266.375</v>
       </c>
@@ -9560,7 +9595,7 @@
         <v>300</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B184, $C$2:$C$767, C184, $D$2:$D$767, D184, $E$2:$E$767, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="46" t="s">
@@ -9568,7 +9603,7 @@
       </c>
       <c r="P184" s="35"/>
     </row>
-    <row r="185" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -9610,7 +9645,7 @@
         <v>501</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B185, $C$2:$C$767, C185, $D$2:$D$767, D185, $E$2:$E$767, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="46" t="s">
@@ -9618,7 +9653,7 @@
       </c>
       <c r="P185" s="10"/>
     </row>
-    <row r="186" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="8" t="s">
         <v>62</v>
       </c>
@@ -9650,11 +9685,11 @@
         <v>117</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B186, $C$2:$C$767, C186, $D$2:$D$767, D186, $E$2:$E$767, E186) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="3">
         <v>46261.375</v>
       </c>
@@ -9696,12 +9731,12 @@
         <v>700</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B187, $C$2:$C$767, C187, $D$2:$D$767, D187, $E$2:$E$767, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O187" s="35"/>
     </row>
-    <row r="188" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -9743,12 +9778,12 @@
         <v>250</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B188, $C$2:$C$767, C188, $D$2:$D$767, D188, $E$2:$E$767, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P188" s="35"/>
     </row>
-    <row r="189" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -9790,12 +9825,12 @@
         <v>1000</v>
       </c>
       <c r="N189" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B189, $C$2:$C$767, C189, $D$2:$D$767, D189, $E$2:$E$767, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P189" s="35"/>
     </row>
-    <row r="190" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="3">
         <v>46262.375</v>
       </c>
@@ -9837,11 +9872,11 @@
         <v>320</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B190, $C$2:$C$767, C190, $D$2:$D$767, D190, $E$2:$E$767, E190) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3">
         <v>46265.486111111109</v>
       </c>
@@ -9883,11 +9918,11 @@
         <v>448</v>
       </c>
       <c r="N191" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B191, $C$2:$C$767, C191, $D$2:$D$767, D191, $E$2:$E$767, E191) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9919,11 +9954,11 @@
         <v>117</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B192, $C$2:$C$767, C192, $D$2:$D$767, D192, $E$2:$E$767, E192) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="3">
         <v>46261.375</v>
       </c>
@@ -9965,13 +10000,13 @@
         <v>300</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B193, $C$2:$C$767, C193, $D$2:$D$767, D193, $E$2:$E$767, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O193" s="10"/>
       <c r="P193" s="10"/>
     </row>
-    <row r="194" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10001,11 +10036,11 @@
       </c>
       <c r="J194" s="40"/>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B194, $C$2:$C$767, C194, $D$2:$D$767, D194, $E$2:$E$767, E194) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="195" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N194:N257" si="10">IF(COUNTIFS( $B$2:$B$767, B194, $C$2:$C$767, C194, $D$2:$D$767, D194, $E$2:$E$767, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="11">
         <v>46243.375</v>
       </c>
@@ -10047,12 +10082,12 @@
         <v>300</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B195, $C$2:$C$767, C195, $D$2:$D$767, D195, $E$2:$E$767, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P195" s="26"/>
     </row>
-    <row r="196" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -10094,11 +10129,11 @@
         <v>400</v>
       </c>
       <c r="N196" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B196, $C$2:$C$767, C196, $D$2:$D$767, D196, $E$2:$E$767, E196) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="11">
         <v>46253.375</v>
       </c>
@@ -10133,11 +10168,11 @@
         <v>144</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B197, $C$2:$C$767, C197, $D$2:$D$767, D197, $E$2:$E$767, E197) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="39">
         <v>46255</v>
       </c>
@@ -10179,12 +10214,12 @@
         <v>140</v>
       </c>
       <c r="N198" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B198, $C$2:$C$767, C198, $D$2:$D$767, D198, $E$2:$E$767, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Duplicate</v>
       </c>
       <c r="O198" s="10"/>
     </row>
-    <row r="199" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="36">
         <v>46261.385416666664</v>
       </c>
@@ -10226,13 +10261,13 @@
         <v>300</v>
       </c>
       <c r="N199" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B199, $C$2:$C$767, C199, $D$2:$D$767, D199, $E$2:$E$767, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Duplicate</v>
       </c>
       <c r="O199" s="10"/>
       <c r="P199" s="10"/>
     </row>
-    <row r="200" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="11">
         <v>46252.6875</v>
       </c>
@@ -10264,11 +10299,11 @@
         <v>117</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B200, $C$2:$C$767, C200, $D$2:$D$767, D200, $E$2:$E$767, E200) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="201" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -10298,12 +10333,12 @@
       </c>
       <c r="J201" s="40"/>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B201, $C$2:$C$767, C201, $D$2:$D$767, D201, $E$2:$E$767, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P201" s="35"/>
     </row>
-    <row r="202" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="36">
         <v>46265.375694444447</v>
       </c>
@@ -10331,7 +10366,7 @@
       <c r="I202" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J202" s="61" t="s">
+      <c r="J202" s="33" t="s">
         <v>118</v>
       </c>
       <c r="K202" s="33" t="s">
@@ -10345,12 +10380,12 @@
         <v>300</v>
       </c>
       <c r="N202" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B202, $C$2:$C$767, C202, $D$2:$D$767, D202, $E$2:$E$767, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="35"/>
     </row>
-    <row r="203" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="48">
         <v>46243.505555555559</v>
       </c>
@@ -10392,12 +10427,12 @@
         <v>253</v>
       </c>
       <c r="N203" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B203, $C$2:$C$767, C203, $D$2:$D$767, D203, $E$2:$E$767, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O203" s="35"/>
     </row>
-    <row r="204" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10439,11 +10474,11 @@
         <v>260</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B204, $C$2:$C$767, C204, $D$2:$D$767, D204, $E$2:$E$767, E204) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="205" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="8" t="s">
         <v>62</v>
       </c>
@@ -10475,11 +10510,11 @@
         <v>198</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B205, $C$2:$C$767, C205, $D$2:$D$767, D205, $E$2:$E$767, E205) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="8" t="s">
         <v>62</v>
       </c>
@@ -10511,11 +10546,11 @@
         <v>117</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B206, $C$2:$C$767, C206, $D$2:$D$767, D206, $E$2:$E$767, E206) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="207" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="8" t="s">
         <v>62</v>
       </c>
@@ -10547,11 +10582,11 @@
         <v>118</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B207, $C$2:$C$767, C207, $D$2:$D$767, D207, $E$2:$E$767, E207) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="3">
         <v>46260.375</v>
       </c>
@@ -10593,11 +10628,11 @@
         <v>800</v>
       </c>
       <c r="N208" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B208, $C$2:$C$767, C208, $D$2:$D$767, D208, $E$2:$E$767, E208) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="209" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="3">
         <v>46258.443055555559</v>
       </c>
@@ -10639,11 +10674,11 @@
         <v>300</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B209, $C$2:$C$767, C209, $D$2:$D$767, D209, $E$2:$E$767, E209) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3">
         <v>46259.375</v>
       </c>
@@ -10685,12 +10720,12 @@
         <v>188</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B210, $C$2:$C$767, C210, $D$2:$D$767, D210, $E$2:$E$767, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P210" s="35"/>
     </row>
-    <row r="211" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="8" t="s">
         <v>62</v>
       </c>
@@ -10722,11 +10757,11 @@
         <v>55</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B211, $C$2:$C$767, C211, $D$2:$D$767, D211, $E$2:$E$767, E211) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="11">
         <v>46253.375</v>
       </c>
@@ -10761,11 +10796,11 @@
         <v>145</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B212, $C$2:$C$767, C212, $D$2:$D$767, D212, $E$2:$E$767, E212) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="213" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -10807,11 +10842,11 @@
         <v>940</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B213, $C$2:$C$767, C213, $D$2:$D$767, D213, $E$2:$E$767, E213) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="3">
         <v>46276.375613425924</v>
       </c>
@@ -10853,11 +10888,11 @@
         <v>450</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B214, $C$2:$C$767, C214, $D$2:$D$767, D214, $E$2:$E$767, E214) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="8" t="s">
         <v>62</v>
       </c>
@@ -10889,11 +10924,11 @@
         <v>118</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B215, $C$2:$C$767, C215, $D$2:$D$767, D215, $E$2:$E$767, E215) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -10935,11 +10970,11 @@
         <v>300</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B216, $C$2:$C$767, C216, $D$2:$D$767, D216, $E$2:$E$767, E216) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="217" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="8" t="s">
         <v>62</v>
       </c>
@@ -10971,11 +11006,11 @@
         <v>118</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B217, $C$2:$C$767, C217, $D$2:$D$767, D217, $E$2:$E$767, E217) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="218" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="3">
         <v>46262.375</v>
       </c>
@@ -11017,12 +11052,12 @@
         <v>370</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B218, $C$2:$C$767, C218, $D$2:$D$767, D218, $E$2:$E$767, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P218" s="35"/>
     </row>
-    <row r="219" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="36">
         <v>46258.443749999999</v>
       </c>
@@ -11064,13 +11099,13 @@
         <v>527.5</v>
       </c>
       <c r="N219" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B219, $C$2:$C$767, C219, $D$2:$D$767, D219, $E$2:$E$767, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O219" s="35"/>
       <c r="P219" s="35"/>
     </row>
-    <row r="220" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="48">
         <v>46253.4</v>
       </c>
@@ -11107,13 +11142,13 @@
       <c r="L220" s="33"/>
       <c r="M220" s="33"/>
       <c r="N220" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B220, $C$2:$C$767, C220, $D$2:$D$767, D220, $E$2:$E$767, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O220" s="35"/>
       <c r="P220" s="35"/>
     </row>
-    <row r="221" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="9" t="s">
         <v>62</v>
       </c>
@@ -11146,13 +11181,13 @@
       <c r="L221" s="18"/>
       <c r="M221" s="18"/>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B221, $C$2:$C$767, C221, $D$2:$D$767, D221, $E$2:$E$767, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="10"/>
       <c r="P221" s="10"/>
     </row>
-    <row r="222" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="3">
         <v>46268.375</v>
       </c>
@@ -11194,11 +11229,11 @@
         <v>1800</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B222, $C$2:$C$767, C222, $D$2:$D$767, D222, $E$2:$E$767, E222) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="223" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="8" t="s">
         <v>62</v>
       </c>
@@ -11228,11 +11263,11 @@
       </c>
       <c r="J223" s="40"/>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B223, $C$2:$C$767, C223, $D$2:$D$767, D223, $E$2:$E$767, E223) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="224" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="3">
         <v>46259.375</v>
       </c>
@@ -11274,12 +11309,12 @@
         <v>650</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B224, $C$2:$C$767, C224, $D$2:$D$767, D224, $E$2:$E$767, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O224" s="35"/>
     </row>
-    <row r="225" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -11321,14 +11356,14 @@
         <v>500</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B225, $C$2:$C$767, C225, $D$2:$D$767, D225, $E$2:$E$767, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O225" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="226" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="8" t="s">
         <v>62</v>
       </c>
@@ -11363,12 +11398,12 @@
       <c r="L226" s="18"/>
       <c r="M226" s="18"/>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B226, $C$2:$C$767, C226, $D$2:$D$767, D226, $E$2:$E$767, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P226" s="10"/>
     </row>
-    <row r="227" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -11400,11 +11435,11 @@
         <v>117</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B227, $C$2:$C$767, C227, $D$2:$D$767, D227, $E$2:$E$767, E227) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="228" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="8" t="s">
         <v>62</v>
       </c>
@@ -11434,11 +11469,11 @@
       </c>
       <c r="J228" s="40"/>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B228, $C$2:$C$767, C228, $D$2:$D$767, D228, $E$2:$E$767, E228) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="229" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -11468,12 +11503,12 @@
       </c>
       <c r="J229" s="40"/>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B229, $C$2:$C$767, C229, $D$2:$D$767, D229, $E$2:$E$767, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="35"/>
     </row>
-    <row r="230" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="8" t="s">
         <v>62</v>
       </c>
@@ -11505,11 +11540,11 @@
         <v>118</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B230, $C$2:$C$767, C230, $D$2:$D$767, D230, $E$2:$E$767, E230) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="231" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="8" t="s">
         <v>62</v>
       </c>
@@ -11539,11 +11574,11 @@
       </c>
       <c r="J231" s="40"/>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B231, $C$2:$C$767, C231, $D$2:$D$767, D231, $E$2:$E$767, E231) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="232" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="3">
         <v>46261.375</v>
       </c>
@@ -11585,11 +11620,11 @@
         <v>260</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B232, $C$2:$C$767, C232, $D$2:$D$767, D232, $E$2:$E$767, E232) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="233" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="8" t="s">
         <v>62</v>
       </c>
@@ -11619,11 +11654,11 @@
       </c>
       <c r="J233" s="40"/>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B233, $C$2:$C$767, C233, $D$2:$D$767, D233, $E$2:$E$767, E233) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="3">
         <v>46269.375</v>
       </c>
@@ -11665,11 +11700,11 @@
         <v>250</v>
       </c>
       <c r="N234" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B234, $C$2:$C$767, C234, $D$2:$D$767, D234, $E$2:$E$767, E234) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="3">
         <v>46262.375</v>
       </c>
@@ -11711,11 +11746,11 @@
         <v>300</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B235, $C$2:$C$767, C235, $D$2:$D$767, D235, $E$2:$E$767, E235) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="236" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="11">
         <v>46252.6875</v>
       </c>
@@ -11747,11 +11782,11 @@
         <v>117</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B236, $C$2:$C$767, C236, $D$2:$D$767, D236, $E$2:$E$767, E236) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="237" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -11781,11 +11816,11 @@
       </c>
       <c r="J237" s="40"/>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B237, $C$2:$C$767, C237, $D$2:$D$767, D237, $E$2:$E$767, E237) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="238" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="3">
         <v>46266.509722222225</v>
       </c>
@@ -11827,11 +11862,11 @@
         <v>300</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B238, $C$2:$C$767, C238, $D$2:$D$767, D238, $E$2:$E$767, E238) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -11863,11 +11898,11 @@
         <v>55</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B239, $C$2:$C$767, C239, $D$2:$D$767, D239, $E$2:$E$767, E239) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="8" t="s">
         <v>62</v>
       </c>
@@ -11899,12 +11934,12 @@
         <v>117</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B240, $C$2:$C$767, C240, $D$2:$D$767, D240, $E$2:$E$767, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P240" s="35"/>
     </row>
-    <row r="241" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="3">
         <v>46260.375</v>
       </c>
@@ -11946,12 +11981,12 @@
         <v>650</v>
       </c>
       <c r="N241" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B241, $C$2:$C$767, C241, $D$2:$D$767, D241, $E$2:$E$767, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P241" s="35"/>
     </row>
-    <row r="242" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="8" t="s">
         <v>62</v>
       </c>
@@ -11983,11 +12018,11 @@
         <v>118</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B242, $C$2:$C$767, C242, $D$2:$D$767, D242, $E$2:$E$767, E242) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="11">
         <v>46252.6875</v>
       </c>
@@ -12019,12 +12054,12 @@
         <v>118</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B243, $C$2:$C$767, C243, $D$2:$D$767, D243, $E$2:$E$767, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O243" s="35"/>
     </row>
-    <row r="244" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -12056,11 +12091,11 @@
         <v>118</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B244, $C$2:$C$767, C244, $D$2:$D$767, D244, $E$2:$E$767, E244) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="8" t="s">
         <v>62</v>
       </c>
@@ -12093,13 +12128,13 @@
       <c r="L245" s="18"/>
       <c r="M245" s="18"/>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B245, $C$2:$C$767, C245, $D$2:$D$767, D245, $E$2:$E$767, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="10"/>
       <c r="P245" s="10"/>
     </row>
-    <row r="246" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="8" t="s">
         <v>62</v>
       </c>
@@ -12131,11 +12166,11 @@
         <v>117</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B246, $C$2:$C$767, C246, $D$2:$D$767, D246, $E$2:$E$767, E246) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="247" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -12177,11 +12212,11 @@
         <v>285</v>
       </c>
       <c r="N247" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B247, $C$2:$C$767, C247, $D$2:$D$767, D247, $E$2:$E$767, E247) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="3">
         <v>46266.375</v>
       </c>
@@ -12223,11 +12258,11 @@
         <v>726</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B248, $C$2:$C$767, C248, $D$2:$D$767, D248, $E$2:$E$767, E248) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12262,11 +12297,11 @@
         <v>146</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B249, $C$2:$C$767, C249, $D$2:$D$767, D249, $E$2:$E$767, E249) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="250" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="8" t="s">
         <v>62</v>
       </c>
@@ -12296,11 +12331,11 @@
       </c>
       <c r="J250" s="40"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B250, $C$2:$C$767, C250, $D$2:$D$767, D250, $E$2:$E$767, E250) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="251" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="8" t="s">
         <v>62</v>
       </c>
@@ -12330,11 +12365,11 @@
       </c>
       <c r="J251" s="40"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B251, $C$2:$C$767, C251, $D$2:$D$767, D251, $E$2:$E$767, E251) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="252" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="8" t="s">
         <v>62</v>
       </c>
@@ -12364,11 +12399,11 @@
       </c>
       <c r="J252" s="40"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B252, $C$2:$C$767, C252, $D$2:$D$767, D252, $E$2:$E$767, E252) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="253" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="3">
         <v>46260.375</v>
       </c>
@@ -12410,11 +12445,11 @@
         <v>300</v>
       </c>
       <c r="N253" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B253, $C$2:$C$767, C253, $D$2:$D$767, D253, $E$2:$E$767, E253) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="20">
         <v>46255</v>
       </c>
@@ -12456,13 +12491,13 @@
         <v>300</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B254, $C$2:$C$767, C254, $D$2:$D$767, D254, $E$2:$E$767, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="10"/>
       <c r="P254" s="10"/>
     </row>
-    <row r="255" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="8" t="s">
         <v>62</v>
       </c>
@@ -12492,11 +12527,11 @@
       </c>
       <c r="J255" s="40"/>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B255, $C$2:$C$767, C255, $D$2:$D$767, D255, $E$2:$E$767, E255) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="256" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -12538,11 +12573,11 @@
         <v>275</v>
       </c>
       <c r="N256" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B256, $C$2:$C$767, C256, $D$2:$D$767, D256, $E$2:$E$767, E256) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="257" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="8" t="s">
         <v>62</v>
       </c>
@@ -12572,11 +12607,11 @@
       </c>
       <c r="J257" s="40"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B257, $C$2:$C$767, C257, $D$2:$D$767, D257, $E$2:$E$767, E257) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="258" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="11">
         <v>46252.6875</v>
       </c>
@@ -12608,11 +12643,11 @@
         <v>118</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B258, $C$2:$C$767, C258, $D$2:$D$767, D258, $E$2:$E$767, E258) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="259" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N258:N291" si="11">IF(COUNTIFS( $B$2:$B$767, B258, $C$2:$C$767, C258, $D$2:$D$767, D258, $E$2:$E$767, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="8" t="s">
         <v>62</v>
       </c>
@@ -12642,11 +12677,11 @@
       </c>
       <c r="J259" s="40"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B259, $C$2:$C$767, C259, $D$2:$D$767, D259, $E$2:$E$767, E259) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="8" t="s">
         <v>62</v>
       </c>
@@ -12678,12 +12713,12 @@
         <v>118</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B260, $C$2:$C$767, C260, $D$2:$D$767, D260, $E$2:$E$767, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="35"/>
     </row>
-    <row r="261" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="11">
         <v>46252.6875</v>
       </c>
@@ -12715,11 +12750,11 @@
         <v>118</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B261, $C$2:$C$767, C261, $D$2:$D$767, D261, $E$2:$E$767, E261) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="3">
         <v>46260.634027777778</v>
       </c>
@@ -12761,11 +12796,11 @@
         <v>480</v>
       </c>
       <c r="N262" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B262, $C$2:$C$767, C262, $D$2:$D$767, D262, $E$2:$E$767, E262) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="8" t="s">
         <v>62</v>
       </c>
@@ -12795,12 +12830,12 @@
       </c>
       <c r="J263" s="40"/>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B263, $C$2:$C$767, C263, $D$2:$D$767, D263, $E$2:$E$767, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P263" s="35"/>
     </row>
-    <row r="264" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="8" t="s">
         <v>62</v>
       </c>
@@ -12830,11 +12865,11 @@
       </c>
       <c r="J264" s="40"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B264, $C$2:$C$767, C264, $D$2:$D$767, D264, $E$2:$E$767, E264) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="265" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="8" t="s">
         <v>62</v>
       </c>
@@ -12866,11 +12901,11 @@
         <v>118</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B265, $C$2:$C$767, C265, $D$2:$D$767, D265, $E$2:$E$767, E265) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="266" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -12912,12 +12947,12 @@
         <v>250</v>
       </c>
       <c r="N266" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B266, $C$2:$C$767, C266, $D$2:$D$767, D266, $E$2:$E$767, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P266" s="35"/>
     </row>
-    <row r="267" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="8" t="s">
         <v>62</v>
       </c>
@@ -12949,11 +12984,11 @@
         <v>117</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B267, $C$2:$C$767, C267, $D$2:$D$767, D267, $E$2:$E$767, E267) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="268" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="8" t="s">
         <v>62</v>
       </c>
@@ -12985,11 +13020,11 @@
         <v>118</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B268, $C$2:$C$767, C268, $D$2:$D$767, D268, $E$2:$E$767, E268) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="269" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="8" t="s">
         <v>62</v>
       </c>
@@ -13019,11 +13054,11 @@
       </c>
       <c r="J269" s="40"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B269, $C$2:$C$767, C269, $D$2:$D$767, D269, $E$2:$E$767, E269) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="270" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="3">
         <v>46260.550694444442</v>
       </c>
@@ -13065,11 +13100,11 @@
         <v>300</v>
       </c>
       <c r="N270" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B270, $C$2:$C$767, C270, $D$2:$D$767, D270, $E$2:$E$767, E270) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="271" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="8" t="s">
         <v>62</v>
       </c>
@@ -13099,11 +13134,11 @@
       </c>
       <c r="J271" s="40"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B271, $C$2:$C$767, C271, $D$2:$D$767, D271, $E$2:$E$767, E271) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="272" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="8" t="s">
         <v>62</v>
       </c>
@@ -13133,11 +13168,11 @@
       </c>
       <c r="J272" s="40"/>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B272, $C$2:$C$767, C272, $D$2:$D$767, D272, $E$2:$E$767, E272) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="8" t="s">
         <v>62</v>
       </c>
@@ -13167,12 +13202,12 @@
       </c>
       <c r="J273" s="40"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B273, $C$2:$C$767, C273, $D$2:$D$767, D273, $E$2:$E$767, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O273" s="35"/>
     </row>
-    <row r="274" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="8" t="s">
         <v>62</v>
       </c>
@@ -13202,11 +13237,11 @@
       </c>
       <c r="J274" s="40"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B274, $C$2:$C$767, C274, $D$2:$D$767, D274, $E$2:$E$767, E274) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="275" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="11">
         <v>46252.6875</v>
       </c>
@@ -13238,11 +13273,11 @@
         <v>118</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B275, $C$2:$C$767, C275, $D$2:$D$767, D275, $E$2:$E$767, E275) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="276" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="8" t="s">
         <v>62</v>
       </c>
@@ -13272,11 +13307,11 @@
       </c>
       <c r="J276" s="40"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B276, $C$2:$C$767, C276, $D$2:$D$767, D276, $E$2:$E$767, E276) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -13318,11 +13353,11 @@
         <v>250</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B277, $C$2:$C$767, C277, $D$2:$D$767, D277, $E$2:$E$767, E277) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="8" t="s">
         <v>62</v>
       </c>
@@ -13352,11 +13387,11 @@
       </c>
       <c r="J278" s="40"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B278, $C$2:$C$767, C278, $D$2:$D$767, D278, $E$2:$E$767, E278) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="8" t="s">
         <v>62</v>
       </c>
@@ -13386,12 +13421,12 @@
       </c>
       <c r="J279" s="40"/>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B279, $C$2:$C$767, C279, $D$2:$D$767, D279, $E$2:$E$767, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P279" s="35"/>
     </row>
-    <row r="280" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="8" t="s">
         <v>62</v>
       </c>
@@ -13421,11 +13456,11 @@
       </c>
       <c r="J280" s="40"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B280, $C$2:$C$767, C280, $D$2:$D$767, D280, $E$2:$E$767, E280) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="281" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="8" t="s">
         <v>62</v>
       </c>
@@ -13455,11 +13490,11 @@
       </c>
       <c r="J281" s="40"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B281, $C$2:$C$767, C281, $D$2:$D$767, D281, $E$2:$E$767, E281) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="8" t="s">
         <v>62</v>
       </c>
@@ -13489,11 +13524,11 @@
       </c>
       <c r="J282" s="40"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B282, $C$2:$C$767, C282, $D$2:$D$767, D282, $E$2:$E$767, E282) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="283" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="8" t="s">
         <v>62</v>
       </c>
@@ -13525,11 +13560,11 @@
         <v>118</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B283, $C$2:$C$767, C283, $D$2:$D$767, D283, $E$2:$E$767, E283) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="284" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -13561,11 +13596,11 @@
         <v>55</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B284, $C$2:$C$767, C284, $D$2:$D$767, D284, $E$2:$E$767, E284) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="8" t="s">
         <v>62</v>
       </c>
@@ -13597,11 +13632,11 @@
         <v>118</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B285, $C$2:$C$767, C285, $D$2:$D$767, D285, $E$2:$E$767, E285) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="286" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="8" t="s">
         <v>62</v>
       </c>
@@ -13631,11 +13666,11 @@
       </c>
       <c r="J286" s="40"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B286, $C$2:$C$767, C286, $D$2:$D$767, D286, $E$2:$E$767, E286) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="287" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -13677,11 +13712,11 @@
         <v>250</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B287, $C$2:$C$767, C287, $D$2:$D$767, D287, $E$2:$E$767, E287) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="8" t="s">
         <v>62</v>
       </c>
@@ -13711,11 +13746,11 @@
       </c>
       <c r="J288" s="40"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B288, $C$2:$C$767, C288, $D$2:$D$767, D288, $E$2:$E$767, E288) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="289" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="289" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="8" t="s">
         <v>62</v>
       </c>
@@ -13745,11 +13780,11 @@
       </c>
       <c r="J289" s="40"/>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B289, $C$2:$C$767, C289, $D$2:$D$767, D289, $E$2:$E$767, E289) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="290" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="290" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="11">
         <v>46251.506249999999</v>
       </c>
@@ -13779,12 +13814,12 @@
       </c>
       <c r="J290" s="40"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B290, $C$2:$C$767, C290, $D$2:$D$767, D290, $E$2:$E$767, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O290" s="35"/>
     </row>
-    <row r="291" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="8" t="s">
         <v>62</v>
       </c>
@@ -13814,16 +13849,26 @@
       </c>
       <c r="J291" s="40"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B291, $C$2:$C$767, C291, $D$2:$D$767, D291, $E$2:$E$767, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P291" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="GRSEEQ"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="2">
       <filters>
         <filter val="S"/>
       </filters>
+    </filterColumn>
+    <filterColumn colId="14">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P291">
       <sortCondition ref="F1"/>
@@ -14389,7 +14434,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B2, $C$2:$C$767, C2, $D$2:$D$767, D2, $E$2:$E$767, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$767, B2, $C$2:$C$767, C2, $D$2:$D$767, D2, $E$2:$E$767, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -14428,7 +14473,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B3, $C$2:$C$767, C3, $D$2:$D$767, D3, $E$2:$E$767, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14465,7 +14510,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B4, $C$2:$C$767, C4, $D$2:$D$767, D4, $E$2:$E$767, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14502,7 +14547,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B5, $C$2:$C$767, C5, $D$2:$D$767, D5, $E$2:$E$767, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14539,7 +14584,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B6, $C$2:$C$767, C6, $D$2:$D$767, D6, $E$2:$E$767, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14576,7 +14621,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B7, $C$2:$C$767, C7, $D$2:$D$767, D7, $E$2:$E$767, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14613,7 +14658,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B8, $C$2:$C$767, C8, $D$2:$D$767, D8, $E$2:$E$767, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14650,7 +14695,7 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B9, $C$2:$C$767, C9, $D$2:$D$767, D9, $E$2:$E$767, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14687,7 +14732,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B10, $C$2:$C$767, C10, $D$2:$D$767, D10, $E$2:$E$767, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10"/>
@@ -14726,7 +14771,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B11, $C$2:$C$767, C11, $D$2:$D$767, D11, $E$2:$E$767, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14763,7 +14808,7 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B12, $C$2:$C$767, C12, $D$2:$D$767, D12, $E$2:$E$767, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14800,7 +14845,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B13, $C$2:$C$767, C13, $D$2:$D$767, D13, $E$2:$E$767, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14839,7 +14884,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B14, $C$2:$C$767, C14, $D$2:$D$767, D14, $E$2:$E$767, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14878,7 +14923,7 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B15, $C$2:$C$767, C15, $D$2:$D$767, D15, $E$2:$E$767, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14924,7 +14969,7 @@
         <v>442</v>
       </c>
       <c r="N16" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B16, $C$2:$C$767, C16, $D$2:$D$767, D16, $E$2:$E$767, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14961,7 +15006,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B17, $C$2:$C$767, C17, $D$2:$D$767, D17, $E$2:$E$767, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14998,7 +15043,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B18, $C$2:$C$767, C18, $D$2:$D$767, D18, $E$2:$E$767, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15035,7 +15080,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B19, $C$2:$C$767, C19, $D$2:$D$767, D19, $E$2:$E$767, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15072,7 +15117,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B20, $C$2:$C$767, C20, $D$2:$D$767, D20, $E$2:$E$767, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15118,7 +15163,7 @@
         <v>300</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B21, $C$2:$C$767, C21, $D$2:$D$767, D21, $E$2:$E$767, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15157,7 +15202,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B22, $C$2:$C$767, C22, $D$2:$D$767, D22, $E$2:$E$767, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P22" s="34"/>
@@ -15195,7 +15240,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B23, $C$2:$C$767, C23, $D$2:$D$767, D23, $E$2:$E$767, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15232,7 +15277,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B24, $C$2:$C$767, C24, $D$2:$D$767, D24, $E$2:$E$767, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15269,7 +15314,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B25, $C$2:$C$767, C25, $D$2:$D$767, D25, $E$2:$E$767, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15306,7 +15351,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B26, $C$2:$C$767, C26, $D$2:$D$767, D26, $E$2:$E$767, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15345,7 +15390,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B27, $C$2:$C$767, C27, $D$2:$D$767, D27, $E$2:$E$767, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15384,7 +15429,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B28, $C$2:$C$767, C28, $D$2:$D$767, D28, $E$2:$E$767, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15423,7 +15468,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B29, $C$2:$C$767, C29, $D$2:$D$767, D29, $E$2:$E$767, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15464,7 +15509,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B30, $C$2:$C$767, C30, $D$2:$D$767, D30, $E$2:$E$767, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15506,7 +15551,7 @@
         <v>3156</v>
       </c>
       <c r="N31" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B31, $C$2:$C$767, C31, $D$2:$D$767, D31, $E$2:$E$767, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31" s="10"/>
@@ -15545,7 +15590,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B32, $C$2:$C$767, C32, $D$2:$D$767, D32, $E$2:$E$767, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15584,7 +15629,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B33, $C$2:$C$767, C33, $D$2:$D$767, D33, $E$2:$E$767, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15623,7 +15668,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B34, $C$2:$C$767, C34, $D$2:$D$767, D34, $E$2:$E$767, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15662,7 +15707,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B35, $C$2:$C$767, C35, $D$2:$D$767, D35, $E$2:$E$767, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35" s="10"/>
@@ -15700,7 +15745,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B36, $C$2:$C$767, C36, $D$2:$D$767, D36, $E$2:$E$767, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15739,7 +15784,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B37, $C$2:$C$767, C37, $D$2:$D$767, D37, $E$2:$E$767, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15776,7 +15821,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B38, $C$2:$C$767, C38, $D$2:$D$767, D38, $E$2:$E$767, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15813,7 +15858,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B39, $C$2:$C$767, C39, $D$2:$D$767, D39, $E$2:$E$767, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P39" s="10"/>
@@ -15860,7 +15905,7 @@
         <v>300</v>
       </c>
       <c r="N40" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B40, $C$2:$C$767, C40, $D$2:$D$767, D40, $E$2:$E$767, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15897,7 +15942,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B41, $C$2:$C$767, C41, $D$2:$D$767, D41, $E$2:$E$767, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P41"/>
@@ -15945,7 +15990,7 @@
         <v>540</v>
       </c>
       <c r="N42" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B42, $C$2:$C$767, C42, $D$2:$D$767, D42, $E$2:$E$767, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -15986,7 +16031,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B43, $C$2:$C$767, C43, $D$2:$D$767, D43, $E$2:$E$767, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43"/>
@@ -16027,7 +16072,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B44, $C$2:$C$767, C44, $D$2:$D$767, D44, $E$2:$E$767, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16066,7 +16111,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B45, $C$2:$C$767, C45, $D$2:$D$767, D45, $E$2:$E$767, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -16107,7 +16152,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B46, $C$2:$C$767, C46, $D$2:$D$767, D46, $E$2:$E$767, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -16148,7 +16193,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B47, $C$2:$C$767, C47, $D$2:$D$767, D47, $E$2:$E$767, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -16186,7 +16231,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B48, $C$2:$C$767, C48, $D$2:$D$767, D48, $E$2:$E$767, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -16233,7 +16278,7 @@
         <v>500</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B49, $C$2:$C$767, C49, $D$2:$D$767, D49, $E$2:$E$767, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16279,7 +16324,7 @@
         <v>300</v>
       </c>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B50, $C$2:$C$767, C50, $D$2:$D$767, D50, $E$2:$E$767, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -16327,7 +16372,7 @@
         <v>300</v>
       </c>
       <c r="N51" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B51, $C$2:$C$767, C51, $D$2:$D$767, D51, $E$2:$E$767, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P51" s="25"/>
@@ -16374,7 +16419,7 @@
         <v>516</v>
       </c>
       <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B52, $C$2:$C$767, C52, $D$2:$D$767, D52, $E$2:$E$767, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="10"/>
@@ -16415,7 +16460,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B53, $C$2:$C$767, C53, $D$2:$D$767, D53, $E$2:$E$767, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16454,7 +16499,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B54, $C$2:$C$767, C54, $D$2:$D$767, D54, $E$2:$E$767, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -16495,7 +16540,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B55, $C$2:$C$767, C55, $D$2:$D$767, D55, $E$2:$E$767, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -16536,7 +16581,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B56, $C$2:$C$767, C56, $D$2:$D$767, D56, $E$2:$E$767, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -16577,7 +16622,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B57, $C$2:$C$767, C57, $D$2:$D$767, D57, $E$2:$E$767, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57" s="34"/>
@@ -16618,7 +16663,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B58, $C$2:$C$767, C58, $D$2:$D$767, D58, $E$2:$E$767, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16657,7 +16702,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B59, $C$2:$C$767, C59, $D$2:$D$767, D59, $E$2:$E$767, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16694,7 +16739,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B60, $C$2:$C$767, C60, $D$2:$D$767, D60, $E$2:$E$767, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16733,7 +16778,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B61, $C$2:$C$767, C61, $D$2:$D$767, D61, $E$2:$E$767, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
@@ -16773,7 +16818,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B62, $C$2:$C$767, C62, $D$2:$D$767, D62, $E$2:$E$767, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16812,7 +16857,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B63, $C$2:$C$767, C63, $D$2:$D$767, D63, $E$2:$E$767, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
@@ -16861,7 +16906,7 @@
         <v>650</v>
       </c>
       <c r="N64" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B64, $C$2:$C$767, C64, $D$2:$D$767, D64, $E$2:$E$767, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -16908,7 +16953,7 @@
         <v>525</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B65, $C$2:$C$767, C65, $D$2:$D$767, D65, $E$2:$E$767, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16947,7 +16992,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B66, $C$2:$C$767, C66, $D$2:$D$767, D66, $E$2:$E$767, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$767, B66, $C$2:$C$767, C66, $D$2:$D$767, D66, $E$2:$E$767, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -16984,7 +17029,7 @@
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B67, $C$2:$C$767, C67, $D$2:$D$767, D67, $E$2:$E$767, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17030,7 +17075,7 @@
         <v>300</v>
       </c>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B68, $C$2:$C$767, C68, $D$2:$D$767, D68, $E$2:$E$767, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="10"/>
@@ -17078,7 +17123,7 @@
         <v>460</v>
       </c>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B69, $C$2:$C$767, C69, $D$2:$D$767, D69, $E$2:$E$767, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -17118,7 +17163,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B70, $C$2:$C$767, C70, $D$2:$D$767, D70, $E$2:$E$767, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17155,7 +17200,7 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B71, $C$2:$C$767, C71, $D$2:$D$767, D71, $E$2:$E$767, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71" s="19"/>
@@ -17196,7 +17241,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B72, $C$2:$C$767, C72, $D$2:$D$767, D72, $E$2:$E$767, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P72"/>
@@ -17236,7 +17281,7 @@
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B73, $C$2:$C$767, C73, $D$2:$D$767, D73, $E$2:$E$767, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P73" s="26"/>
@@ -17274,7 +17319,7 @@
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B74, $C$2:$C$767, C74, $D$2:$D$767, D74, $E$2:$E$767, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74" s="26"/>
@@ -17321,7 +17366,7 @@
         <v>300</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B75, $C$2:$C$767, C75, $D$2:$D$767, D75, $E$2:$E$767, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17367,7 +17412,7 @@
         <v>34175</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B76, $C$2:$C$767, C76, $D$2:$D$767, D76, $E$2:$E$767, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17406,7 +17451,7 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B77, $C$2:$C$767, C77, $D$2:$D$767, D77, $E$2:$E$767, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17445,7 +17490,7 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B78, $C$2:$C$767, C78, $D$2:$D$767, D78, $E$2:$E$767, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17484,7 +17529,7 @@
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B79, $C$2:$C$767, C79, $D$2:$D$767, D79, $E$2:$E$767, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="10"/>
@@ -17532,7 +17577,7 @@
         <v>26810</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B80, $C$2:$C$767, C80, $D$2:$D$767, D80, $E$2:$E$767, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17571,7 +17616,7 @@
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
       <c r="N81" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B81, $C$2:$C$767, C81, $D$2:$D$767, D81, $E$2:$E$767, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="10"/>
@@ -17615,11 +17660,11 @@
         <v>5755</v>
       </c>
       <c r="M82" s="33">
-        <f t="shared" ref="M82:M99" si="0">ABS((D82*E82)-L82)</f>
+        <f t="shared" ref="M82:M99" si="2">ABS((D82*E82)-L82)</f>
         <v>275</v>
       </c>
       <c r="N82" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B82, $C$2:$C$767, C82, $D$2:$D$767, D82, $E$2:$E$767, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O82" s="46" t="s">
@@ -17665,11 +17710,11 @@
         <v>5805</v>
       </c>
       <c r="M83" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="N83" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B83, $C$2:$C$767, C83, $D$2:$D$767, D83, $E$2:$E$767, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O83" s="46" t="s">
@@ -17714,11 +17759,11 @@
         <v>35880</v>
       </c>
       <c r="M84" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>26710</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B84, $C$2:$C$767, C84, $D$2:$D$767, D84, $E$2:$E$767, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O84" s="46" t="s">
@@ -17763,11 +17808,11 @@
         <v>19730.5</v>
       </c>
       <c r="M85" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>504.5</v>
       </c>
       <c r="N85" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B85, $C$2:$C$767, C85, $D$2:$D$767, D85, $E$2:$E$767, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O85" s="46" t="s">
@@ -17813,11 +17858,11 @@
         <v>19690</v>
       </c>
       <c r="M86" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>545</v>
       </c>
       <c r="N86" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B86, $C$2:$C$767, C86, $D$2:$D$767, D86, $E$2:$E$767, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O86" s="46" t="s">
@@ -17863,11 +17908,11 @@
         <v>35880</v>
       </c>
       <c r="M87" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>26610</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B87, $C$2:$C$767, C87, $D$2:$D$767, D87, $E$2:$E$767, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="10"/>
@@ -17911,11 +17956,11 @@
         <v>11660</v>
       </c>
       <c r="M88" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B88, $C$2:$C$767, C88, $D$2:$D$767, D88, $E$2:$E$767, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="46" t="s">
@@ -17961,11 +18006,11 @@
         <v>10400</v>
       </c>
       <c r="M89" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B89, $C$2:$C$767, C89, $D$2:$D$767, D89, $E$2:$E$767, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O89" s="10"/>
@@ -18009,11 +18054,11 @@
         <v>20010</v>
       </c>
       <c r="M90" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B90, $C$2:$C$767, C90, $D$2:$D$767, D90, $E$2:$E$767, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="10"/>
@@ -18056,11 +18101,11 @@
         <v>8220</v>
       </c>
       <c r="M91" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B91, $C$2:$C$767, C91, $D$2:$D$767, D91, $E$2:$E$767, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O91" s="46" t="s">
@@ -18106,11 +18151,11 @@
         <v>3560</v>
       </c>
       <c r="M92" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="N92" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B92, $C$2:$C$767, C92, $D$2:$D$767, D92, $E$2:$E$767, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O92" s="46" t="s">
@@ -18155,11 +18200,11 @@
         <v>3510</v>
       </c>
       <c r="M93" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="N93" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B93, $C$2:$C$767, C93, $D$2:$D$767, D93, $E$2:$E$767, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O93" s="46" t="s">
@@ -18205,11 +18250,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M94" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>710.99999999999636</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B94, $C$2:$C$767, C94, $D$2:$D$767, D94, $E$2:$E$767, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94" s="10" t="s">
@@ -18254,11 +18299,11 @@
         <v>15075</v>
       </c>
       <c r="M95" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>645</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B95, $C$2:$C$767, C95, $D$2:$D$767, D95, $E$2:$E$767, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95" s="10" t="s">
@@ -18303,11 +18348,11 @@
         <v>9170</v>
       </c>
       <c r="M96" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B96, $C$2:$C$767, C96, $D$2:$D$767, D96, $E$2:$E$767, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O96" s="10"/>
@@ -18351,11 +18396,11 @@
         <v>20260</v>
       </c>
       <c r="M97" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N97" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B97, $C$2:$C$767, C97, $D$2:$D$767, D97, $E$2:$E$767, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O97"/>
@@ -18398,11 +18443,11 @@
         <v>73800</v>
       </c>
       <c r="M98" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>48320</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B98, $C$2:$C$767, C98, $D$2:$D$767, D98, $E$2:$E$767, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="10" t="s">
@@ -18448,11 +18493,11 @@
         <v>5905</v>
       </c>
       <c r="M99" s="54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>275</v>
       </c>
       <c r="N99" s="56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B99, $C$2:$C$767, C99, $D$2:$D$767, D99, $E$2:$E$767, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="25"/>
@@ -18490,7 +18535,7 @@
       </c>
       <c r="J100" s="40"/>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B100, $C$2:$C$767, C100, $D$2:$D$767, D100, $E$2:$E$767, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18536,7 +18581,7 @@
         <v>651</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B101, $C$2:$C$767, C101, $D$2:$D$767, D101, $E$2:$E$767, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="10"/>
@@ -18584,7 +18629,7 @@
         <v>26460</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B102, $C$2:$C$767, C102, $D$2:$D$767, D102, $E$2:$E$767, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="10"/>
@@ -18632,7 +18677,7 @@
         <v>646</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B103, $C$2:$C$767, C103, $D$2:$D$767, D103, $E$2:$E$767, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O103" s="46" t="s">
@@ -18681,7 +18726,7 @@
         <v>300</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B104, $C$2:$C$767, C104, $D$2:$D$767, D104, $E$2:$E$767, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O104"/>
@@ -18719,7 +18764,7 @@
       <c r="L105" s="18"/>
       <c r="M105" s="18"/>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B105, $C$2:$C$767, C105, $D$2:$D$767, D105, $E$2:$E$767, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="46" t="s">
@@ -18769,7 +18814,7 @@
         <v>810</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B106, $C$2:$C$767, C106, $D$2:$D$767, D106, $E$2:$E$767, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18803,7 +18848,7 @@
       </c>
       <c r="J107" s="40"/>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B107, $C$2:$C$767, C107, $D$2:$D$767, D107, $E$2:$E$767, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18849,7 +18894,7 @@
         <v>300</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B108, $C$2:$C$767, C108, $D$2:$D$767, D108, $E$2:$E$767, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P108" s="35"/>
@@ -18896,7 +18941,7 @@
         <v>300</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B109, $C$2:$C$767, C109, $D$2:$D$767, D109, $E$2:$E$767, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="10"/>
@@ -18944,7 +18989,7 @@
         <v>280</v>
       </c>
       <c r="N110" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B110, $C$2:$C$767, C110, $D$2:$D$767, D110, $E$2:$E$767, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O110" s="46" t="s">
@@ -18993,7 +19038,7 @@
         <v>300</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B111, $C$2:$C$767, C111, $D$2:$D$767, D111, $E$2:$E$767, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19039,7 +19084,7 @@
         <v>300</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B112, $C$2:$C$767, C112, $D$2:$D$767, D112, $E$2:$E$767, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P112" s="26"/>
@@ -19079,7 +19124,7 @@
       <c r="L113" s="18"/>
       <c r="M113" s="18"/>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B113, $C$2:$C$767, C113, $D$2:$D$767, D113, $E$2:$E$767, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O113" s="46" t="s">
@@ -19129,7 +19174,7 @@
         <v>150</v>
       </c>
       <c r="N114" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B114, $C$2:$C$767, C114, $D$2:$D$767, D114, $E$2:$E$767, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -19175,7 +19220,7 @@
         <v>250</v>
       </c>
       <c r="N115" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B115, $C$2:$C$767, C115, $D$2:$D$767, D115, $E$2:$E$767, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -19221,7 +19266,7 @@
         <v>300.00000000000182</v>
       </c>
       <c r="N116" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B116, $C$2:$C$767, C116, $D$2:$D$767, D116, $E$2:$E$767, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="46" t="s">
@@ -19270,7 +19315,7 @@
         <v>274</v>
       </c>
       <c r="N117" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B117, $C$2:$C$767, C117, $D$2:$D$767, D117, $E$2:$E$767, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="46" t="s">
@@ -19307,7 +19352,7 @@
       </c>
       <c r="J118" s="40"/>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B118, $C$2:$C$767, C118, $D$2:$D$767, D118, $E$2:$E$767, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="25"/>
@@ -19350,11 +19395,11 @@
         <v>73800</v>
       </c>
       <c r="M119" s="18">
-        <f t="shared" ref="M119:M125" si="1">ABS((D119*E119)-L119)</f>
+        <f t="shared" ref="M119:M125" si="3">ABS((D119*E119)-L119)</f>
         <v>47900</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B119, $C$2:$C$767, C119, $D$2:$D$767, D119, $E$2:$E$767, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="10" t="s">
@@ -19399,11 +19444,11 @@
         <v>4852</v>
       </c>
       <c r="M120" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N120" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B120, $C$2:$C$767, C120, $D$2:$D$767, D120, $E$2:$E$767, E120) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -19445,11 +19490,11 @@
         <v>25300</v>
       </c>
       <c r="M121" s="18">
+        <f t="shared" si="3"/>
+        <v>650</v>
+      </c>
+      <c r="N121" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>650</v>
-      </c>
-      <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B121, $C$2:$C$767, C121, $D$2:$D$767, D121, $E$2:$E$767, E121) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O121" s="46" t="s">
@@ -19494,11 +19539,11 @@
         <v>12480</v>
       </c>
       <c r="M122" s="18">
+        <f t="shared" si="3"/>
+        <v>495</v>
+      </c>
+      <c r="N122" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>495</v>
-      </c>
-      <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B122, $C$2:$C$767, C122, $D$2:$D$767, D122, $E$2:$E$767, E122) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O122" s="46" t="s">
@@ -19543,11 +19588,11 @@
         <v>3300</v>
       </c>
       <c r="M123" s="18">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="N123" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B123, $C$2:$C$767, C123, $D$2:$D$767, D123, $E$2:$E$767, E123) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -19589,11 +19634,11 @@
         <v>10410</v>
       </c>
       <c r="M124" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N124" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B124, $C$2:$C$767, C124, $D$2:$D$767, D124, $E$2:$E$767, E124) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O124" s="35"/>
@@ -19636,11 +19681,11 @@
         <v>9270</v>
       </c>
       <c r="M125" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N125" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B125, $C$2:$C$767, C125, $D$2:$D$767, D125, $E$2:$E$767, E125) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P125" s="19"/>
@@ -19677,7 +19722,7 @@
         <v>118</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B126, $C$2:$C$767, C126, $D$2:$D$767, D126, $E$2:$E$767, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19723,7 +19768,7 @@
         <v>270</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B127, $C$2:$C$767, C127, $D$2:$D$767, D127, $E$2:$E$767, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O127" s="47" t="s">
@@ -19765,7 +19810,7 @@
       <c r="L128" s="18"/>
       <c r="M128" s="18"/>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B128, $C$2:$C$767, C128, $D$2:$D$767, D128, $E$2:$E$767, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
@@ -19809,11 +19854,11 @@
         <v>25780</v>
       </c>
       <c r="M129" s="18">
-        <f t="shared" ref="M129:M139" si="2">ABS((D129*E129)-L129)</f>
+        <f t="shared" ref="M129:M139" si="4">ABS((D129*E129)-L129)</f>
         <v>300</v>
       </c>
       <c r="N129" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B129, $C$2:$C$767, C129, $D$2:$D$767, D129, $E$2:$E$767, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O129" s="46" t="s">
@@ -19859,11 +19904,11 @@
         <v>17040</v>
       </c>
       <c r="M130" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>880</v>
       </c>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B130, $C$2:$C$767, C130, $D$2:$D$767, D130, $E$2:$E$767, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="5">IF(COUNTIFS( $B$2:$B$767, B130, $C$2:$C$767, C130, $D$2:$D$767, D130, $E$2:$E$767, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="46" t="s">
@@ -19908,11 +19953,11 @@
         <v>32200</v>
       </c>
       <c r="M131" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1200</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B131, $C$2:$C$767, C131, $D$2:$D$767, D131, $E$2:$E$767, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19954,11 +19999,11 @@
         <v>25530</v>
       </c>
       <c r="M132" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N132" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B132, $C$2:$C$767, C132, $D$2:$D$767, D132, $E$2:$E$767, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O132"/>
@@ -20002,11 +20047,11 @@
         <v>12510</v>
       </c>
       <c r="M133" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>290</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B133, $C$2:$C$767, C133, $D$2:$D$767, D133, $E$2:$E$767, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20048,11 +20093,11 @@
         <v>10510</v>
       </c>
       <c r="M134" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B134, $C$2:$C$767, C134, $D$2:$D$767, D134, $E$2:$E$767, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20094,11 +20139,11 @@
         <v>4680</v>
       </c>
       <c r="M135" s="33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="N135" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B135, $C$2:$C$767, C135, $D$2:$D$767, D135, $E$2:$E$767, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="P135" s="35"/>
@@ -20141,11 +20186,11 @@
         <v>4520</v>
       </c>
       <c r="M136" s="33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N136" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B136, $C$2:$C$767, C136, $D$2:$D$767, D136, $E$2:$E$767, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20187,11 +20232,11 @@
         <v>3005</v>
       </c>
       <c r="M137" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>240</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B137, $C$2:$C$767, C137, $D$2:$D$767, D137, $E$2:$E$767, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P137" s="26"/>
@@ -20234,11 +20279,11 @@
         <v>4080</v>
       </c>
       <c r="M138" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B138, $C$2:$C$767, C138, $D$2:$D$767, D138, $E$2:$E$767, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20280,11 +20325,11 @@
         <v>8570</v>
       </c>
       <c r="M139" s="33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B139, $C$2:$C$767, C139, $D$2:$D$767, D139, $E$2:$E$767, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="46" t="s">
@@ -20323,7 +20368,7 @@
         <v>118</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B140, $C$2:$C$767, C140, $D$2:$D$767, D140, $E$2:$E$767, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20369,7 +20414,7 @@
         <v>750</v>
       </c>
       <c r="N141" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B141, $C$2:$C$767, C141, $D$2:$D$767, D141, $E$2:$E$767, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="25"/>
@@ -20419,7 +20464,7 @@
         <v>300</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B142, $C$2:$C$767, C142, $D$2:$D$767, D142, $E$2:$E$767, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20453,7 +20498,7 @@
       </c>
       <c r="J143" s="40"/>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B143, $C$2:$C$767, C143, $D$2:$D$767, D143, $E$2:$E$767, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20495,11 +20540,11 @@
         <v>73800</v>
       </c>
       <c r="M144" s="18">
-        <f t="shared" ref="M144:M153" si="3">ABS((D144*E144)-L144)</f>
+        <f t="shared" ref="M144:M153" si="6">ABS((D144*E144)-L144)</f>
         <v>47480</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B144, $C$2:$C$767, C144, $D$2:$D$767, D144, $E$2:$E$767, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20541,11 +20586,11 @@
         <v>8810</v>
       </c>
       <c r="M145" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
       <c r="N145" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B145, $C$2:$C$767, C145, $D$2:$D$767, D145, $E$2:$E$767, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="46" t="s">
@@ -20591,11 +20636,11 @@
         <v>26020</v>
       </c>
       <c r="M146" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>340</v>
       </c>
       <c r="N146" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B146, $C$2:$C$767, C146, $D$2:$D$767, D146, $E$2:$E$767, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20637,11 +20682,11 @@
         <v>7578</v>
       </c>
       <c r="M147" s="33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>294</v>
       </c>
       <c r="N147" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B147, $C$2:$C$767, C147, $D$2:$D$767, D147, $E$2:$E$767, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20683,11 +20728,11 @@
         <v>7578</v>
       </c>
       <c r="M148" s="33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>294</v>
       </c>
       <c r="N148" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B148, $C$2:$C$767, C148, $D$2:$D$767, D148, $E$2:$E$767, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O148" s="10"/>
@@ -20731,11 +20776,11 @@
         <v>4968</v>
       </c>
       <c r="M149" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>280</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B149, $C$2:$C$767, C149, $D$2:$D$767, D149, $E$2:$E$767, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20777,11 +20822,11 @@
         <v>18800</v>
       </c>
       <c r="M150" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B150, $C$2:$C$767, C150, $D$2:$D$767, D150, $E$2:$E$767, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O150" s="47" t="s">
@@ -20826,11 +20871,11 @@
         <v>3810</v>
       </c>
       <c r="M151" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N151" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B151, $C$2:$C$767, C151, $D$2:$D$767, D151, $E$2:$E$767, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20872,11 +20917,11 @@
         <v>5180</v>
       </c>
       <c r="M152" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>268</v>
       </c>
       <c r="N152" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B152, $C$2:$C$767, C152, $D$2:$D$767, D152, $E$2:$E$767, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20918,11 +20963,11 @@
         <v>26180</v>
       </c>
       <c r="M153" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B153, $C$2:$C$767, C153, $D$2:$D$767, D153, $E$2:$E$767, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="10"/>
@@ -20958,7 +21003,7 @@
       </c>
       <c r="J154" s="40"/>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B154, $C$2:$C$767, C154, $D$2:$D$767, D154, $E$2:$E$767, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O154" s="35"/>
@@ -21005,7 +21050,7 @@
         <v>1000</v>
       </c>
       <c r="N155" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B155, $C$2:$C$767, C155, $D$2:$D$767, D155, $E$2:$E$767, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O155" s="26"/>
@@ -21052,7 +21097,7 @@
         <v>700</v>
       </c>
       <c r="N156" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B156, $C$2:$C$767, C156, $D$2:$D$767, D156, $E$2:$E$767, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -21098,7 +21143,7 @@
         <v>360</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B157, $C$2:$C$767, C157, $D$2:$D$767, D157, $E$2:$E$767, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21134,7 +21179,7 @@
         <v>117</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B158, $C$2:$C$767, C158, $D$2:$D$767, D158, $E$2:$E$767, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21180,7 +21225,7 @@
         <v>300</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B159, $C$2:$C$767, C159, $D$2:$D$767, D159, $E$2:$E$767, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21226,7 +21271,7 @@
         <v>300</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B160, $C$2:$C$767, C160, $D$2:$D$767, D160, $E$2:$E$767, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21272,7 +21317,7 @@
         <v>300</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B161, $C$2:$C$767, C161, $D$2:$D$767, D161, $E$2:$E$767, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21318,7 +21363,7 @@
         <v>295</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B162, $C$2:$C$767, C162, $D$2:$D$767, D162, $E$2:$E$767, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21354,7 +21399,7 @@
         <v>117</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B163, $C$2:$C$767, C163, $D$2:$D$767, D163, $E$2:$E$767, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21395,7 +21440,7 @@
       <c r="L164" s="17"/>
       <c r="M164" s="17"/>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B164, $C$2:$C$767, C164, $D$2:$D$767, D164, $E$2:$E$767, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O164" s="10"/>
@@ -21443,7 +21488,7 @@
         <v>250</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B165, $C$2:$C$767, C165, $D$2:$D$767, D165, $E$2:$E$767, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21489,7 +21534,7 @@
         <v>650</v>
       </c>
       <c r="N166" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B166, $C$2:$C$767, C166, $D$2:$D$767, D166, $E$2:$E$767, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O166" s="46" t="s">
@@ -21538,7 +21583,7 @@
         <v>250</v>
       </c>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B167, $C$2:$C$767, C167, $D$2:$D$767, D167, $E$2:$E$767, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21584,7 +21629,7 @@
         <v>300</v>
       </c>
       <c r="N168" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B168, $C$2:$C$767, C168, $D$2:$D$767, D168, $E$2:$E$767, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21630,7 +21675,7 @@
         <v>501</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B169, $C$2:$C$767, C169, $D$2:$D$767, D169, $E$2:$E$767, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O169" s="46" t="s">
@@ -21667,7 +21712,7 @@
       </c>
       <c r="J170" s="40"/>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B170, $C$2:$C$767, C170, $D$2:$D$767, D170, $E$2:$E$767, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21703,7 +21748,7 @@
         <v>118</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B171, $C$2:$C$767, C171, $D$2:$D$767, D171, $E$2:$E$767, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O171" s="46" t="s">
@@ -21752,7 +21797,7 @@
         <v>250</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B172, $C$2:$C$767, C172, $D$2:$D$767, D172, $E$2:$E$767, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P172" s="35"/>
@@ -21799,7 +21844,7 @@
         <v>250</v>
       </c>
       <c r="N173" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B173, $C$2:$C$767, C173, $D$2:$D$767, D173, $E$2:$E$767, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21833,7 +21878,7 @@
       </c>
       <c r="J174" s="40"/>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B174, $C$2:$C$767, C174, $D$2:$D$767, D174, $E$2:$E$767, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21879,7 +21924,7 @@
         <v>320</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B175, $C$2:$C$767, C175, $D$2:$D$767, D175, $E$2:$E$767, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21925,7 +21970,7 @@
         <v>448</v>
       </c>
       <c r="N176" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B176, $C$2:$C$767, C176, $D$2:$D$767, D176, $E$2:$E$767, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21961,7 +22006,7 @@
         <v>156</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B177, $C$2:$C$767, C177, $D$2:$D$767, D177, $E$2:$E$767, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21995,7 +22040,7 @@
       </c>
       <c r="J178" s="40"/>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B178, $C$2:$C$767, C178, $D$2:$D$767, D178, $E$2:$E$767, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22041,7 +22086,7 @@
         <v>500</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B179, $C$2:$C$767, C179, $D$2:$D$767, D179, $E$2:$E$767, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="10"/>
@@ -22082,7 +22127,7 @@
       <c r="L180" s="54"/>
       <c r="M180" s="54"/>
       <c r="N180" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B180, $C$2:$C$767, C180, $D$2:$D$767, D180, $E$2:$E$767, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="25"/>
@@ -22128,11 +22173,11 @@
         <v>8820</v>
       </c>
       <c r="M181" s="18">
-        <f t="shared" ref="M181:M186" si="4">ABS((D181*E181)-L181)</f>
+        <f t="shared" ref="M181:M186" si="7">ABS((D181*E181)-L181)</f>
         <v>650</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B181, $C$2:$C$767, C181, $D$2:$D$767, D181, $E$2:$E$767, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22174,11 +22219,11 @@
         <v>36946</v>
       </c>
       <c r="M182" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>934</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B182, $C$2:$C$767, C182, $D$2:$D$767, D182, $E$2:$E$767, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22220,11 +22265,11 @@
         <v>5520</v>
       </c>
       <c r="M183" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N183" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B183, $C$2:$C$767, C183, $D$2:$D$767, D183, $E$2:$E$767, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="35"/>
@@ -22267,11 +22312,11 @@
         <v>2657</v>
       </c>
       <c r="M184" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>253</v>
       </c>
       <c r="N184" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B184, $C$2:$C$767, C184, $D$2:$D$767, D184, $E$2:$E$767, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="35"/>
@@ -22314,11 +22359,11 @@
         <v>14552</v>
       </c>
       <c r="M185" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B185, $C$2:$C$767, C185, $D$2:$D$767, D185, $E$2:$E$767, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="46" t="s">
@@ -22363,11 +22408,11 @@
         <v>12800</v>
       </c>
       <c r="M186" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400</v>
       </c>
       <c r="N186" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B186, $C$2:$C$767, C186, $D$2:$D$767, D186, $E$2:$E$767, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22401,7 +22446,7 @@
       </c>
       <c r="J187" s="40"/>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B187, $C$2:$C$767, C187, $D$2:$D$767, D187, $E$2:$E$767, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22447,7 +22492,7 @@
         <v>260</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B188, $C$2:$C$767, C188, $D$2:$D$767, D188, $E$2:$E$767, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22483,7 +22528,7 @@
         <v>117</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B189, $C$2:$C$767, C189, $D$2:$D$767, D189, $E$2:$E$767, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22517,7 +22562,7 @@
       </c>
       <c r="J190" s="40"/>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B190, $C$2:$C$767, C190, $D$2:$D$767, D190, $E$2:$E$767, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22553,7 +22598,7 @@
         <v>117</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B191, $C$2:$C$767, C191, $D$2:$D$767, D191, $E$2:$E$767, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22587,7 +22632,7 @@
       </c>
       <c r="J192" s="40"/>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B192, $C$2:$C$767, C192, $D$2:$D$767, D192, $E$2:$E$767, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P192" s="35"/>
@@ -22634,7 +22679,7 @@
         <v>300</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B193, $C$2:$C$767, C193, $D$2:$D$767, D193, $E$2:$E$767, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O193" s="10"/>
@@ -22682,7 +22727,7 @@
         <v>188</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B194, $C$2:$C$767, C194, $D$2:$D$767, D194, $E$2:$E$767, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="8">IF(COUNTIFS( $B$2:$B$767, B194, $C$2:$C$767, C194, $D$2:$D$767, D194, $E$2:$E$767, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P194" s="35"/>
@@ -22729,7 +22774,7 @@
         <v>700</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B195, $C$2:$C$767, C195, $D$2:$D$767, D195, $E$2:$E$767, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O195" s="35"/>
@@ -22766,7 +22811,7 @@
         <v>117</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B196, $C$2:$C$767, C196, $D$2:$D$767, D196, $E$2:$E$767, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22812,7 +22857,7 @@
         <v>527.5</v>
       </c>
       <c r="N197" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B197, $C$2:$C$767, C197, $D$2:$D$767, D197, $E$2:$E$767, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O197" s="35"/>
@@ -22855,7 +22900,7 @@
       <c r="L198" s="33"/>
       <c r="M198" s="33"/>
       <c r="N198" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B198, $C$2:$C$767, C198, $D$2:$D$767, D198, $E$2:$E$767, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22901,7 +22946,7 @@
         <v>500</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B199, $C$2:$C$767, C199, $D$2:$D$767, D199, $E$2:$E$767, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="46" t="s">
@@ -22941,7 +22986,7 @@
         <v>118</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B200, $C$2:$C$767, C200, $D$2:$D$767, D200, $E$2:$E$767, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22977,7 +23022,7 @@
         <v>118</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B201, $C$2:$C$767, C201, $D$2:$D$767, D201, $E$2:$E$767, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23023,7 +23068,7 @@
         <v>800</v>
       </c>
       <c r="N202" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B202, $C$2:$C$767, C202, $D$2:$D$767, D202, $E$2:$E$767, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23057,7 +23102,7 @@
       </c>
       <c r="J203" s="40"/>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B203, $C$2:$C$767, C203, $D$2:$D$767, D203, $E$2:$E$767, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23093,7 +23138,7 @@
         <v>55</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B204, $C$2:$C$767, C204, $D$2:$D$767, D204, $E$2:$E$767, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23139,7 +23184,7 @@
         <v>300</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B205, $C$2:$C$767, C205, $D$2:$D$767, D205, $E$2:$E$767, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23185,7 +23230,7 @@
         <v>250</v>
       </c>
       <c r="N206" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B206, $C$2:$C$767, C206, $D$2:$D$767, D206, $E$2:$E$767, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23219,7 +23264,7 @@
       </c>
       <c r="J207" s="40"/>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B207, $C$2:$C$767, C207, $D$2:$D$767, D207, $E$2:$E$767, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23265,7 +23310,7 @@
         <v>1000</v>
       </c>
       <c r="N208" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B208, $C$2:$C$767, C208, $D$2:$D$767, D208, $E$2:$E$767, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P208" s="35"/>
@@ -23302,7 +23347,7 @@
         <v>198</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B209, $C$2:$C$767, C209, $D$2:$D$767, D209, $E$2:$E$767, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23348,7 +23393,7 @@
         <v>1800</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B210, $C$2:$C$767, C210, $D$2:$D$767, D210, $E$2:$E$767, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23394,7 +23439,7 @@
         <v>260</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B211, $C$2:$C$767, C211, $D$2:$D$767, D211, $E$2:$E$767, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23440,7 +23485,7 @@
         <v>370</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B212, $C$2:$C$767, C212, $D$2:$D$767, D212, $E$2:$E$767, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P212" s="35"/>
@@ -23477,7 +23522,7 @@
         <v>118</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B213, $C$2:$C$767, C213, $D$2:$D$767, D213, $E$2:$E$767, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23513,7 +23558,7 @@
         <v>117</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B214, $C$2:$C$767, C214, $D$2:$D$767, D214, $E$2:$E$767, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23559,7 +23604,7 @@
         <v>650</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B215, $C$2:$C$767, C215, $D$2:$D$767, D215, $E$2:$E$767, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="35"/>
@@ -23596,7 +23641,7 @@
         <v>118</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B216, $C$2:$C$767, C216, $D$2:$D$767, D216, $E$2:$E$767, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O216" s="35"/>
@@ -23636,7 +23681,7 @@
         <v>144</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B217, $C$2:$C$767, C217, $D$2:$D$767, D217, $E$2:$E$767, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23670,7 +23715,7 @@
       </c>
       <c r="J218" s="40"/>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B218, $C$2:$C$767, C218, $D$2:$D$767, D218, $E$2:$E$767, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23704,7 +23749,7 @@
       </c>
       <c r="J219" s="40"/>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B219, $C$2:$C$767, C219, $D$2:$D$767, D219, $E$2:$E$767, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23743,7 +23788,7 @@
         <v>145</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B220, $C$2:$C$767, C220, $D$2:$D$767, D220, $E$2:$E$767, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23782,7 +23827,7 @@
       <c r="L221" s="18"/>
       <c r="M221" s="18"/>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B221, $C$2:$C$767, C221, $D$2:$D$767, D221, $E$2:$E$767, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="10"/>
@@ -23830,7 +23875,7 @@
         <v>940</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B222, $C$2:$C$767, C222, $D$2:$D$767, D222, $E$2:$E$767, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23866,7 +23911,7 @@
         <v>118</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B223, $C$2:$C$767, C223, $D$2:$D$767, D223, $E$2:$E$767, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23912,7 +23957,7 @@
         <v>300</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B224, $C$2:$C$767, C224, $D$2:$D$767, D224, $E$2:$E$767, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23948,7 +23993,7 @@
         <v>118</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B225, $C$2:$C$767, C225, $D$2:$D$767, D225, $E$2:$E$767, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23987,7 +24032,7 @@
       <c r="L226" s="18"/>
       <c r="M226" s="18"/>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B226, $C$2:$C$767, C226, $D$2:$D$767, D226, $E$2:$E$767, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O226" s="10"/>
@@ -24025,7 +24070,7 @@
         <v>117</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B227, $C$2:$C$767, C227, $D$2:$D$767, D227, $E$2:$E$767, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P227" s="35"/>
@@ -24060,7 +24105,7 @@
       </c>
       <c r="J228" s="40"/>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B228, $C$2:$C$767, C228, $D$2:$D$767, D228, $E$2:$E$767, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O228" s="35"/>
@@ -24095,7 +24140,7 @@
       </c>
       <c r="J229" s="40"/>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B229, $C$2:$C$767, C229, $D$2:$D$767, D229, $E$2:$E$767, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24131,7 +24176,7 @@
         <v>117</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B230, $C$2:$C$767, C230, $D$2:$D$767, D230, $E$2:$E$767, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24167,7 +24212,7 @@
         <v>118</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B231, $C$2:$C$767, C231, $D$2:$D$767, D231, $E$2:$E$767, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24213,7 +24258,7 @@
         <v>285</v>
       </c>
       <c r="N232" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B232, $C$2:$C$767, C232, $D$2:$D$767, D232, $E$2:$E$767, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24259,7 +24304,7 @@
         <v>726</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B233, $C$2:$C$767, C233, $D$2:$D$767, D233, $E$2:$E$767, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24293,7 +24338,7 @@
       </c>
       <c r="J234" s="40"/>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B234, $C$2:$C$767, C234, $D$2:$D$767, D234, $E$2:$E$767, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24332,7 +24377,7 @@
         <v>146</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B235, $C$2:$C$767, C235, $D$2:$D$767, D235, $E$2:$E$767, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24366,7 +24411,7 @@
       </c>
       <c r="J236" s="40"/>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B236, $C$2:$C$767, C236, $D$2:$D$767, D236, $E$2:$E$767, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24412,7 +24457,7 @@
         <v>300</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B237, $C$2:$C$767, C237, $D$2:$D$767, D237, $E$2:$E$767, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24446,7 +24491,7 @@
       </c>
       <c r="J238" s="40"/>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B238, $C$2:$C$767, C238, $D$2:$D$767, D238, $E$2:$E$767, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24492,7 +24537,7 @@
         <v>650</v>
       </c>
       <c r="N239" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B239, $C$2:$C$767, C239, $D$2:$D$767, D239, $E$2:$E$767, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P239" s="35"/>
@@ -24539,7 +24584,7 @@
         <v>300</v>
       </c>
       <c r="N240" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B240, $C$2:$C$767, C240, $D$2:$D$767, D240, $E$2:$E$767, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24573,7 +24618,7 @@
       </c>
       <c r="J241" s="40"/>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B241, $C$2:$C$767, C241, $D$2:$D$767, D241, $E$2:$E$767, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24609,7 +24654,7 @@
         <v>118</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B242, $C$2:$C$767, C242, $D$2:$D$767, D242, $E$2:$E$767, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24643,7 +24688,7 @@
       </c>
       <c r="J243" s="40"/>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B243, $C$2:$C$767, C243, $D$2:$D$767, D243, $E$2:$E$767, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24689,7 +24734,7 @@
         <v>300</v>
       </c>
       <c r="N244" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B244, $C$2:$C$767, C244, $D$2:$D$767, D244, $E$2:$E$767, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24735,7 +24780,7 @@
         <v>275</v>
       </c>
       <c r="N245" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B245, $C$2:$C$767, C245, $D$2:$D$767, D245, $E$2:$E$767, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="10"/>
@@ -24773,7 +24818,7 @@
         <v>118</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B246, $C$2:$C$767, C246, $D$2:$D$767, D246, $E$2:$E$767, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O246" s="35"/>
@@ -24808,7 +24853,7 @@
       </c>
       <c r="J247" s="40"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B247, $C$2:$C$767, C247, $D$2:$D$767, D247, $E$2:$E$767, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24844,7 +24889,7 @@
         <v>118</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B248, $C$2:$C$767, C248, $D$2:$D$767, D248, $E$2:$E$767, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24878,7 +24923,7 @@
       </c>
       <c r="J249" s="40"/>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B249, $C$2:$C$767, C249, $D$2:$D$767, D249, $E$2:$E$767, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24912,7 +24957,7 @@
       </c>
       <c r="J250" s="40"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B250, $C$2:$C$767, C250, $D$2:$D$767, D250, $E$2:$E$767, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24946,7 +24991,7 @@
       </c>
       <c r="J251" s="40"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B251, $C$2:$C$767, C251, $D$2:$D$767, D251, $E$2:$E$767, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24992,7 +25037,7 @@
         <v>250</v>
       </c>
       <c r="N252" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B252, $C$2:$C$767, C252, $D$2:$D$767, D252, $E$2:$E$767, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P252" s="35"/>
@@ -25039,7 +25084,7 @@
         <v>480</v>
       </c>
       <c r="N253" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B253, $C$2:$C$767, C253, $D$2:$D$767, D253, $E$2:$E$767, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25078,7 +25123,7 @@
       <c r="L254" s="18"/>
       <c r="M254" s="18"/>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B254, $C$2:$C$767, C254, $D$2:$D$767, D254, $E$2:$E$767, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="10"/>
@@ -25114,7 +25159,7 @@
       </c>
       <c r="J255" s="40"/>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B255, $C$2:$C$767, C255, $D$2:$D$767, D255, $E$2:$E$767, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P255" s="35"/>
@@ -25161,7 +25206,7 @@
         <v>250</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B256, $C$2:$C$767, C256, $D$2:$D$767, D256, $E$2:$E$767, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25195,7 +25240,7 @@
       </c>
       <c r="J257" s="40"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B257, $C$2:$C$767, C257, $D$2:$D$767, D257, $E$2:$E$767, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25231,7 +25276,7 @@
         <v>118</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B258, $C$2:$C$767, C258, $D$2:$D$767, D258, $E$2:$E$767, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N291" si="9">IF(COUNTIFS( $B$2:$B$767, B258, $C$2:$C$767, C258, $D$2:$D$767, D258, $E$2:$E$767, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25265,7 +25310,7 @@
       </c>
       <c r="J259" s="40"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B259, $C$2:$C$767, C259, $D$2:$D$767, D259, $E$2:$E$767, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25301,7 +25346,7 @@
         <v>118</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B260, $C$2:$C$767, C260, $D$2:$D$767, D260, $E$2:$E$767, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="35"/>
@@ -25336,7 +25381,7 @@
       </c>
       <c r="J261" s="40"/>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B261, $C$2:$C$767, C261, $D$2:$D$767, D261, $E$2:$E$767, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O261" s="35"/>
@@ -25371,7 +25416,7 @@
       </c>
       <c r="J262" s="40"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B262, $C$2:$C$767, C262, $D$2:$D$767, D262, $E$2:$E$767, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25405,7 +25450,7 @@
       </c>
       <c r="J263" s="40"/>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B263, $C$2:$C$767, C263, $D$2:$D$767, D263, $E$2:$E$767, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25439,7 +25484,7 @@
       </c>
       <c r="J264" s="40"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B264, $C$2:$C$767, C264, $D$2:$D$767, D264, $E$2:$E$767, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25473,7 +25518,7 @@
       </c>
       <c r="J265" s="40"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B265, $C$2:$C$767, C265, $D$2:$D$767, D265, $E$2:$E$767, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25507,7 +25552,7 @@
       </c>
       <c r="J266" s="40"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B266, $C$2:$C$767, C266, $D$2:$D$767, D266, $E$2:$E$767, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25543,7 +25588,7 @@
         <v>118</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B267, $C$2:$C$767, C267, $D$2:$D$767, D267, $E$2:$E$767, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25579,7 +25624,7 @@
         <v>118</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B268, $C$2:$C$767, C268, $D$2:$D$767, D268, $E$2:$E$767, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25613,7 +25658,7 @@
       </c>
       <c r="J269" s="40"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B269, $C$2:$C$767, C269, $D$2:$D$767, D269, $E$2:$E$767, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25647,7 +25692,7 @@
       </c>
       <c r="J270" s="40"/>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B270, $C$2:$C$767, C270, $D$2:$D$767, D270, $E$2:$E$767, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P270" s="35"/>
@@ -25684,7 +25729,7 @@
         <v>118</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B271, $C$2:$C$767, C271, $D$2:$D$767, D271, $E$2:$E$767, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25720,7 +25765,7 @@
         <v>55</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B272, $C$2:$C$767, C272, $D$2:$D$767, D272, $E$2:$E$767, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25754,7 +25799,7 @@
       </c>
       <c r="J273" s="40"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B273, $C$2:$C$767, C273, $D$2:$D$767, D273, $E$2:$E$767, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25800,7 +25845,7 @@
         <v>250</v>
       </c>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B274, $C$2:$C$767, C274, $D$2:$D$767, D274, $E$2:$E$767, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25834,7 +25879,7 @@
       </c>
       <c r="J275" s="40"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B275, $C$2:$C$767, C275, $D$2:$D$767, D275, $E$2:$E$767, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25868,7 +25913,7 @@
       </c>
       <c r="J276" s="40"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B276, $C$2:$C$767, C276, $D$2:$D$767, D276, $E$2:$E$767, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25902,7 +25947,7 @@
       </c>
       <c r="J277" s="40"/>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B277, $C$2:$C$767, C277, $D$2:$D$767, D277, $E$2:$E$767, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O277" s="35"/>
@@ -25937,7 +25982,7 @@
       </c>
       <c r="J278" s="40"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B278, $C$2:$C$767, C278, $D$2:$D$767, D278, $E$2:$E$767, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25973,7 +26018,7 @@
         <v>118</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B279, $C$2:$C$767, C279, $D$2:$D$767, D279, $E$2:$E$767, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26009,7 +26054,7 @@
         <v>118</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B280, $C$2:$C$767, C280, $D$2:$D$767, D280, $E$2:$E$767, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26044,7 +26089,7 @@
         <v>360</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B281, $C$2:$C$767, C281, $D$2:$D$767, D281, $E$2:$E$767, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26075,11 +26120,11 @@
         <v>14100</v>
       </c>
       <c r="M282" s="18">
-        <f t="shared" ref="M282:M291" si="5">ABS((D282*E282)-L282)</f>
+        <f t="shared" ref="M282:M291" si="10">ABS((D282*E282)-L282)</f>
         <v>500</v>
       </c>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B282, $C$2:$C$767, C282, $D$2:$D$767, D282, $E$2:$E$767, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26110,11 +26155,11 @@
         <v>8049</v>
       </c>
       <c r="M283" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>800</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B283, $C$2:$C$767, C283, $D$2:$D$767, D283, $E$2:$E$767, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26145,11 +26190,11 @@
         <v>14200</v>
       </c>
       <c r="M284" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>500</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B284, $C$2:$C$767, C284, $D$2:$D$767, D284, $E$2:$E$767, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26180,11 +26225,11 @@
         <v>14400</v>
       </c>
       <c r="M285" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>500</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B285, $C$2:$C$767, C285, $D$2:$D$767, D285, $E$2:$E$767, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26215,11 +26260,11 @@
         <v>14650</v>
       </c>
       <c r="M286" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>450</v>
       </c>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B286, $C$2:$C$767, C286, $D$2:$D$767, D286, $E$2:$E$767, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26250,11 +26295,11 @@
         <v>13052</v>
       </c>
       <c r="M287" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>646</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B287, $C$2:$C$767, C287, $D$2:$D$767, D287, $E$2:$E$767, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26285,11 +26330,11 @@
         <v>11320</v>
       </c>
       <c r="M288" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>400</v>
       </c>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B288, $C$2:$C$767, C288, $D$2:$D$767, D288, $E$2:$E$767, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26320,11 +26365,11 @@
         <v>15030</v>
       </c>
       <c r="M289" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>450</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B289, $C$2:$C$767, C289, $D$2:$D$767, D289, $E$2:$E$767, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26355,11 +26400,11 @@
         <v>8700</v>
       </c>
       <c r="M290" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>300</v>
       </c>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B290, $C$2:$C$767, C290, $D$2:$D$767, D290, $E$2:$E$767, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26390,11 +26435,11 @@
         <v>18960</v>
       </c>
       <c r="M291" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>816</v>
       </c>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B291, $C$2:$C$767, C291, $D$2:$D$767, D291, $E$2:$E$767, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>

--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_11sep26_Fri.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_11sep26_Fri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BACBCC1-AF78-40F3-9AEC-DA52BAFC31CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14B6B1A-CA60-47B6-8DC2-D70C476504AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1683,88 +1683,101 @@
         <v>251</v>
       </c>
     </row>
-    <row r="2" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
-        <v>62</v>
+    <row r="2" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
+        <v>46275.457638888889</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E2" s="4">
-        <v>3914</v>
+        <v>222</v>
       </c>
       <c r="F2" s="4">
-        <v>-22.410546140000001</v>
+        <v>2.2805805110000001</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="H2" s="5">
-        <v>5044.5</v>
+        <v>217.05</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="42" t="s">
+      <c r="J2" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" t="str">
-        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$767, B2, $C$2:$C$767, C2, $D$2:$D$767, D2, $E$2:$E$767, E2) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K2" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="L2" s="18">
+        <v>56375</v>
+      </c>
+      <c r="M2" s="18">
+        <f>ABS((D2*E2)-L2)</f>
+        <v>34175</v>
+      </c>
+      <c r="N2" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B2, $C$2:$C$767, C2, $D$2:$D$767, D2, $E$2:$E$767, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+    </row>
+    <row r="3" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" s="4">
-        <v>2560</v>
+        <v>2470</v>
       </c>
       <c r="F3" s="4">
-        <v>-22.162425129999999</v>
+        <v>0.93992644049999996</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="H3" s="5">
-        <v>3288.9</v>
+        <v>2447</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="41"/>
+      <c r="J3" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
-        <v>62</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B3, $C$2:$C$767, C3, $D$2:$D$767, D3, $E$2:$E$767, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O3" s="10"/>
+      <c r="P3" s="25"/>
+    </row>
+    <row r="4" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
@@ -1773,164 +1786,180 @@
         <v>1</v>
       </c>
       <c r="E4" s="4">
-        <v>4014</v>
+        <v>13552</v>
       </c>
       <c r="F4" s="4">
-        <v>-20.428189119999999</v>
+        <v>0.68350668650000002</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H4" s="5">
-        <v>5044.5</v>
+        <v>13460</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="41"/>
+      <c r="J4" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B4, $C$2:$C$767, C4, $D$2:$D$767, D4, $E$2:$E$767, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4">
-        <v>660</v>
+        <v>281</v>
       </c>
       <c r="F5" s="4">
-        <v>-20.318725100000002</v>
+        <v>1.779676099E-2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="H5" s="5">
-        <v>828.3</v>
+        <v>280.95</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="41"/>
+      <c r="J5" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B5, $C$2:$C$767, C5, $D$2:$D$767, D5, $E$2:$E$767, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O5" s="10"/>
+      <c r="P5" s="26"/>
+    </row>
+    <row r="6" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="4">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4">
-        <v>18052</v>
+        <v>2435</v>
       </c>
       <c r="F6" s="4">
-        <v>-19.230425060000002</v>
+        <v>-0.49039640379999999</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5">
-        <v>22350</v>
+        <v>2447</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="41"/>
+      <c r="J6" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>62</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B6, $C$2:$C$767, C6, $D$2:$D$767, D6, $E$2:$E$767, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+    </row>
+    <row r="7" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>46252.645138888889</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4">
-        <v>2660</v>
+        <v>401</v>
       </c>
       <c r="F7" s="4">
-        <v>-19.121894860000001</v>
+        <v>-0.82849016939999998</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5">
-        <v>3288.9</v>
+        <v>404.35</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="41"/>
+      <c r="J7" s="43" t="s">
+        <v>41</v>
+      </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3">
-        <v>46252.688194444447</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B7, $C$2:$C$767, C7, $D$2:$D$767, D7, $E$2:$E$767, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="4">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E8" s="4">
-        <v>136.15</v>
+        <v>3888</v>
       </c>
       <c r="F8" s="4">
-        <v>-18.055973519999998</v>
+        <v>-1.2746940229999999</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="H8" s="5">
-        <v>166.15</v>
+        <v>3938.2</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
@@ -1940,110 +1969,125 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
-        <v>62</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B8, $C$2:$C$767, C8, $D$2:$D$767, D8, $E$2:$E$767, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O8" s="26"/>
+      <c r="P8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>46268.385416666664</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E9" s="4">
-        <v>4164</v>
+        <v>214</v>
       </c>
       <c r="F9" s="4">
-        <v>-17.454653579999999</v>
+        <v>-1.4052061739999999</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="H9" s="5">
-        <v>5044.5</v>
+        <v>217.05</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="41"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" s="34" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
-        <v>62</v>
+      <c r="J9" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="L9" s="18">
+        <v>21900</v>
+      </c>
+      <c r="M9" s="18">
+        <f>ABS((D9*E9)-L9)</f>
+        <v>500</v>
+      </c>
+      <c r="N9" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B9, $C$2:$C$767, C9, $D$2:$D$767, D9, $E$2:$E$767, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+    </row>
+    <row r="10" spans="1:16" s="34" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="4">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E10" s="4">
-        <v>18552</v>
+        <v>277</v>
       </c>
       <c r="F10" s="4">
-        <v>-16.993288589999999</v>
+        <v>-1.4059441180000001</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="H10" s="5">
-        <v>22350</v>
+        <v>280.95</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="41"/>
+      <c r="J10" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B10, $C$2:$C$767, C10, $D$2:$D$767, D10, $E$2:$E$767, E10) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O10"/>
-      <c r="P10"/>
-    </row>
-    <row r="11" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P10" s="10"/>
+    </row>
+    <row r="11" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>2752</v>
+        <v>3856</v>
       </c>
       <c r="F11" s="4">
-        <v>-16.324607010000001</v>
+        <v>-2.087247981</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="H11" s="5">
-        <v>3288.9</v>
+        <v>3938.2</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>8</v>
@@ -2053,212 +2097,229 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B11, $C$2:$C$767, C11, $D$2:$D$767, D11, $E$2:$E$767, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O11" s="19"/>
+      <c r="P11" s="10"/>
+    </row>
+    <row r="12" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E12" s="4">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="F12" s="4">
-        <v>-16.239316240000001</v>
+        <v>-2.1922428329999999</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H12" s="5">
-        <v>234</v>
+        <v>266.85000000000002</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="41"/>
+      <c r="J12" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B12, $C$2:$C$767, C12, $D$2:$D$767, D12, $E$2:$E$767, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="P12" s="34"/>
+    </row>
+    <row r="13" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E13" s="4">
-        <v>19052</v>
+        <v>212</v>
       </c>
       <c r="F13" s="4">
-        <v>-14.75615213</v>
+        <v>-2.3266528449999999</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="H13" s="5">
-        <v>22350</v>
+        <v>217.05</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="41"/>
+      <c r="J13" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B13, $C$2:$C$767, C13, $D$2:$D$767, D13, $E$2:$E$767, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+    </row>
+    <row r="14" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E14" s="4">
-        <v>4364</v>
+        <v>878</v>
       </c>
       <c r="F14" s="4">
-        <v>-13.48993954</v>
+        <v>-2.4444444440000002</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="H14" s="5">
-        <v>5044.5</v>
+        <v>900</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="42" t="s">
-        <v>41</v>
+      <c r="J14" s="41" t="s">
+        <v>55</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
+        <f>IF(COUNTIFS( $B$2:$B$767, B14, $C$2:$C$767, C14, $D$2:$D$767, D14, $E$2:$E$767, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+    </row>
+    <row r="15" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
+        <v>46261.375</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="4">
+        <v>50</v>
+      </c>
+      <c r="E15" s="4">
+        <v>205</v>
+      </c>
+      <c r="F15" s="4">
+        <v>-2.543380081</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="5">
+        <v>210.35</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="L15" s="18">
+        <v>10550</v>
+      </c>
+      <c r="M15" s="18">
+        <f>ABS((D15*E15)-L15)</f>
+        <v>300</v>
+      </c>
+      <c r="N15" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B15, $C$2:$C$767, C15, $D$2:$D$767, D15, $E$2:$E$767, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+    </row>
+    <row r="16" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
+        <v>46252.6875</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4">
+        <v>122</v>
+      </c>
+      <c r="F16" s="4">
+        <v>-2.5481268469999998</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="5">
+        <v>125.19</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B16, $C$2:$C$767, C16, $D$2:$D$767, D16, $E$2:$E$767, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+    </row>
+    <row r="17" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="4">
-        <v>4410</v>
-      </c>
-      <c r="F15" s="4">
-        <v>-12.57805531</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H15" s="5">
-        <v>5044.5</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="41"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="29">
-        <v>46255</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="31">
-        <v>1</v>
-      </c>
-      <c r="E16" s="31">
-        <v>19550</v>
-      </c>
-      <c r="F16" s="4">
-        <v>-12.52796421</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" s="5">
-        <v>22350</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="L16" s="27">
-        <v>19992</v>
-      </c>
-      <c r="M16" s="27">
-        <f>ABS((D16*E16)-L16)</f>
-        <v>442</v>
-      </c>
-      <c r="N16" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3">
-        <v>46252.635416666664</v>
-      </c>
       <c r="B17" s="1" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>10</v>
@@ -2267,16 +2328,16 @@
         <v>2</v>
       </c>
       <c r="E17" s="4">
-        <v>2892</v>
+        <v>3830</v>
       </c>
       <c r="F17" s="4">
-        <v>-12.06786464</v>
+        <v>-2.7474480730000002</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="H17" s="5">
-        <v>3288.9</v>
+        <v>3938.2</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
@@ -2286,71 +2347,76 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B17, $C$2:$C$767, C17, $D$2:$D$767, D17, $E$2:$E$767, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+    </row>
+    <row r="18" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="4">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E18" s="4">
-        <v>111</v>
+        <v>401</v>
       </c>
       <c r="F18" s="4">
-        <v>-11.33477115</v>
+        <v>-2.8702918739999999</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H18" s="5">
-        <v>125.19</v>
+        <v>412.85</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="41"/>
+      <c r="J18" s="22" t="s">
+        <v>55</v>
+      </c>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B18, $C$2:$C$767, C18, $D$2:$D$767, D18, $E$2:$E$767, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="P18" s="10"/>
+    </row>
+    <row r="19" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4">
-        <v>701</v>
+        <v>4010</v>
       </c>
       <c r="F19" s="4">
-        <v>-11.265822780000001</v>
+        <v>-2.9760464550000001</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="H19" s="5">
-        <v>790</v>
+        <v>4133</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>8</v>
@@ -2362,62 +2428,64 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3">
-        <v>46267.375</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B19, $C$2:$C$767, C19, $D$2:$D$767, D19, $E$2:$E$767, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+    </row>
+    <row r="20" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="20">
+        <v>46255</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E20" s="4">
-        <v>20050</v>
+        <v>336</v>
       </c>
       <c r="F20" s="4">
-        <v>-10.290827739999999</v>
+        <v>-3.156074362</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H20" s="5">
-        <v>22350</v>
+        <v>346.95</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J20" s="24" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>237</v>
+        <v>150</v>
       </c>
       <c r="L20" s="18">
-        <v>20350</v>
+        <v>8700</v>
       </c>
       <c r="M20" s="18">
         <f>ABS((D20*E20)-L20)</f>
         <v>300</v>
       </c>
       <c r="N20" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
-        <v>62</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B20, $C$2:$C$767, C20, $D$2:$D$767, D20, $E$2:$E$767, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="3">
+        <v>46274.375</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>10</v>
@@ -2426,53 +2494,64 @@
         <v>15</v>
       </c>
       <c r="E21" s="4">
-        <v>4415</v>
+        <v>1005</v>
       </c>
       <c r="F21" s="4">
-        <v>-10.20947732</v>
+        <v>-3.2071655589999999</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H21" s="5">
-        <v>4917</v>
+        <v>1038.3</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="41"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J21" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="L21" s="18">
+        <v>15600</v>
+      </c>
+      <c r="M21" s="18">
+        <f>ABS((D21*E21)-L21)</f>
+        <v>525</v>
+      </c>
+      <c r="N21" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B21, $C$2:$C$767, C21, $D$2:$D$767, D21, $E$2:$E$767, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+    </row>
+    <row r="22" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="4">
-        <v>4456</v>
+        <v>3810</v>
       </c>
       <c r="F22" s="4">
-        <v>-9.3756355500000002</v>
+        <v>-3.2552942969999998</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="H22" s="5">
-        <v>4917</v>
+        <v>3938.2</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>8</v>
@@ -2482,327 +2561,354 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
-        <v>62</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B22, $C$2:$C$767, C22, $D$2:$D$767, D22, $E$2:$E$767, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+    </row>
+    <row r="23" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E23" s="4">
-        <v>561</v>
+        <v>203.5</v>
       </c>
       <c r="F23" s="4">
-        <v>-8.706265256</v>
+        <v>-3.2564772999999998</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H23" s="5">
-        <v>614.5</v>
+        <v>210.35</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="41" t="s">
-        <v>41</v>
+      <c r="J23" s="42" t="s">
+        <v>55</v>
       </c>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
-        <v>62</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B23, $C$2:$C$767, C23, $D$2:$D$767, D23, $E$2:$E$767, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O23" s="10"/>
+    </row>
+    <row r="24" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="3">
+        <v>46260.375</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E24" s="4">
-        <v>836</v>
+        <v>2348</v>
       </c>
       <c r="F24" s="4">
-        <v>-8.3835616440000003</v>
+        <v>-3.2709895360000001</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H24" s="5">
-        <v>912.5</v>
+        <v>2427.4</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
+      <c r="J24" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="L24" s="18">
+        <v>7344</v>
+      </c>
+      <c r="M24" s="18">
+        <f>ABS((D24*E24)-L24)</f>
+        <v>300</v>
+      </c>
       <c r="N24" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B24, $C$2:$C$767, C24, $D$2:$D$767, D24, $E$2:$E$767, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+    </row>
+    <row r="25" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="3">
-        <v>46254.375</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="4">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="E25" s="4">
-        <v>2230</v>
+        <v>391</v>
       </c>
       <c r="F25" s="4">
-        <v>-8.1321578639999998</v>
+        <v>-3.3015951530000001</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H25" s="5">
-        <v>2427.4</v>
+        <v>404.35</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="23" t="s">
+      <c r="J25" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="K25" s="17" t="s">
-        <v>148</v>
-      </c>
+      <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
-      <c r="N25" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="6" t="s">
-        <v>62</v>
+      <c r="N25" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B25, $C$2:$C$767, C25, $D$2:$D$767, D25, $E$2:$E$767, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+    </row>
+    <row r="26" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="4">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E26" s="4">
-        <v>115.25</v>
+        <v>1666</v>
       </c>
       <c r="F26" s="4">
-        <v>-7.9399313039999999</v>
+        <v>-3.59354204</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H26" s="5">
-        <v>125.19</v>
+        <v>1728.1</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="41"/>
+      <c r="J26" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K26" s="17"/>
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B26, $C$2:$C$767, C26, $D$2:$D$767, D26, $E$2:$E$767, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="4">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="E27" s="4">
-        <v>1751</v>
+        <v>31.01</v>
       </c>
       <c r="F27" s="4">
-        <v>-7.6963626779999998</v>
+        <v>-3.8747675140000002</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="H27" s="5">
-        <v>1897</v>
+        <v>32.26</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="41"/>
+      <c r="J27" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="6" t="s">
-        <v>62</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B27, $C$2:$C$767, C27, $D$2:$D$767, D27, $E$2:$E$767, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O27" s="34"/>
+    </row>
+    <row r="28" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="4">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E28" s="4">
-        <v>116</v>
+        <v>1142</v>
       </c>
       <c r="F28" s="4">
-        <v>-7.3408419199999999</v>
+        <v>-4.1785534489999998</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H28" s="5">
-        <v>125.19</v>
+        <v>1191.8</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J28" s="41"/>
+      <c r="J28" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="3">
-        <v>46031.4375</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B28, $C$2:$C$767, C28, $D$2:$D$767, D28, $E$2:$E$767, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+    </row>
+    <row r="29" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>214</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D29" s="4">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E29" s="4">
-        <v>1052</v>
+        <v>862</v>
       </c>
       <c r="F29" s="4">
-        <v>-7.3168582879999997</v>
+        <v>-4.2222222220000001</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>225</v>
+        <v>52</v>
       </c>
       <c r="H29" s="5">
-        <v>1135.05</v>
+        <v>900</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="24" t="s">
+      <c r="J29" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18">
-        <f>ABS((D29*E29)-L29)</f>
-        <v>3156</v>
-      </c>
-      <c r="N29" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-      <c r="O29" s="10"/>
-      <c r="P29" s="19"/>
-    </row>
-    <row r="30" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="6" t="s">
-        <v>62</v>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B29, $C$2:$C$767, C29, $D$2:$D$767, D29, $E$2:$E$767, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="3">
+        <v>46121.375</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30" s="4">
-        <v>4560</v>
+        <v>1664</v>
       </c>
       <c r="F30" s="4">
-        <v>-7.2605247100000003</v>
+        <v>-4.2577675490000004</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H30" s="5">
-        <v>4917</v>
+        <v>1738</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J30" s="41"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J30" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="L30" s="18">
+        <f>5*1794</f>
+        <v>8970</v>
+      </c>
+      <c r="M30" s="18">
+        <f>ABS((D30*E30)-L30)</f>
+        <v>650</v>
+      </c>
+      <c r="N30" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B30, $C$2:$C$767, C30, $D$2:$D$767, D30, $E$2:$E$767, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="P30" s="10"/>
+    </row>
+    <row r="31" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
-        <v>46121.375</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>10</v>
@@ -2811,80 +2917,71 @@
         <v>3</v>
       </c>
       <c r="E31" s="4">
-        <v>1614</v>
+        <v>1302</v>
       </c>
       <c r="F31" s="4">
-        <v>-7.1346375139999996</v>
+        <v>-4.2647058820000003</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H31" s="5">
-        <v>1738</v>
+        <v>1360</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J31" s="24" t="s">
+      <c r="J31" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="K31" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="L31" s="18">
-        <f>3*1794</f>
-        <v>5382</v>
-      </c>
-      <c r="M31" s="18">
-        <f>ABS((D31*E31)-L31)</f>
-        <v>540</v>
-      </c>
-      <c r="N31" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="3">
-        <v>46252.635416666664</v>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B31, $C$2:$C$767, C31, $D$2:$D$767, D31, $E$2:$E$767, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E32" s="4">
-        <v>850</v>
+        <v>6920</v>
       </c>
       <c r="F32" s="4">
-        <v>-6.8493150680000001</v>
+        <v>-4.4198895030000003</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="H32" s="5">
-        <v>912.5</v>
+        <v>7240</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="42" t="s">
-        <v>55</v>
+      <c r="J32" s="22" t="s">
+        <v>140</v>
       </c>
       <c r="K32" s="17"/>
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-      <c r="O32" s="10"/>
-    </row>
-    <row r="33" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B32, $C$2:$C$767, C32, $D$2:$D$767, D32, $E$2:$E$767, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
         <v>62</v>
       </c>
@@ -2898,10 +2995,10 @@
         <v>50</v>
       </c>
       <c r="E33" s="4">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F33" s="4">
-        <v>-6.821963394</v>
+        <v>-4.4449726649999999</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>70</v>
@@ -2912,119 +3009,118 @@
       <c r="I33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="41" t="s">
+      <c r="J33" s="42" t="s">
         <v>41</v>
       </c>
       <c r="K33" s="17"/>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="6" t="s">
-        <v>62</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B33, $C$2:$C$767, C33, $D$2:$D$767, D33, $E$2:$E$767, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="3">
+        <v>46252.688194444447</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E34" s="4">
-        <v>4710</v>
+        <v>640</v>
       </c>
       <c r="F34" s="4">
-        <v>-6.6309842400000001</v>
+        <v>-4.4633527390000003</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H34" s="5">
-        <v>5044.5</v>
+        <v>669.9</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J34" s="41" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="K34" s="17"/>
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B34, $C$2:$C$767, C34, $D$2:$D$767, D34, $E$2:$E$767, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E35" s="4">
-        <v>1614</v>
+        <v>3760</v>
       </c>
       <c r="F35" s="4">
-        <v>-6.6026271630000002</v>
+        <v>-4.5249098569999999</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="H35" s="5">
-        <v>1728.1</v>
+        <v>3938.2</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="22" t="s">
-        <v>41</v>
-      </c>
+      <c r="J35" s="41"/>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B35, $C$2:$C$767, C35, $D$2:$D$767, D35, $E$2:$E$767, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="P35" s="10"/>
+    </row>
+    <row r="36" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="3">
-        <v>46258.601388888892</v>
+        <v>46268.375</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E36" s="4">
-        <v>2271</v>
+        <v>870.2</v>
       </c>
       <c r="F36" s="4">
-        <v>-6.4431078519999998</v>
+        <v>-4.6356164379999996</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H36" s="5">
-        <v>2427.4</v>
+        <v>912.5</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>8</v>
@@ -3033,182 +3129,189 @@
         <v>55</v>
       </c>
       <c r="K36" s="18" t="s">
-        <v>161</v>
+        <v>241</v>
       </c>
       <c r="L36" s="18">
-        <v>7113</v>
+        <v>17920</v>
       </c>
       <c r="M36" s="18">
         <f>ABS((D36*E36)-L36)</f>
+        <v>516</v>
+      </c>
+      <c r="N36" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B36, $C$2:$C$767, C36, $D$2:$D$767, D36, $E$2:$E$767, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+    </row>
+    <row r="37" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="3">
+        <v>46261.375</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="4">
+        <v>20</v>
+      </c>
+      <c r="E37" s="4">
+        <v>870</v>
+      </c>
+      <c r="F37" s="4">
+        <v>-4.6575342470000001</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H37" s="5">
+        <v>912.5</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K37" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="L37" s="18">
+        <v>17700</v>
+      </c>
+      <c r="M37" s="18">
+        <f>ABS((D37*E37)-L37)</f>
         <v>300</v>
       </c>
-      <c r="N36" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="6" t="s">
+      <c r="N37" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B37, $C$2:$C$767, C37, $D$2:$D$767, D37, $E$2:$E$767, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O37" s="10"/>
+      <c r="P37" s="25"/>
+    </row>
+    <row r="38" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="4">
-        <v>69</v>
-      </c>
-      <c r="E37" s="4">
-        <v>1277</v>
-      </c>
-      <c r="F37" s="4">
-        <v>-6.1029411759999999</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H37" s="5">
-        <v>1360</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J37" s="41"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="3">
-        <v>46252.6875</v>
-      </c>
       <c r="B38" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E38" s="4">
-        <v>326</v>
+        <v>119</v>
       </c>
       <c r="F38" s="4">
-        <v>-6.0383340539999999</v>
+        <v>-4.9444843839999999</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H38" s="5">
-        <v>346.95</v>
+        <v>125.19</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J38" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J38" s="41"/>
       <c r="K38" s="17"/>
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="6" t="s">
-        <v>62</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B38, $C$2:$C$767, C38, $D$2:$D$767, D38, $E$2:$E$767, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="P38" s="10"/>
+    </row>
+    <row r="39" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E39" s="4">
-        <v>4640</v>
+        <v>1132</v>
       </c>
       <c r="F39" s="4">
-        <v>-5.6335163719999999</v>
+        <v>-5.0176204059999998</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="H39" s="5">
-        <v>4917</v>
+        <v>1191.8</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="41"/>
+      <c r="J39" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B39, $C$2:$C$767, C39, $D$2:$D$767, D39, $E$2:$E$767, E39) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O39" s="10"/>
-    </row>
-    <row r="40" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="3">
-        <v>46269.375</v>
+      <c r="P39" s="10"/>
+    </row>
+    <row r="40" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E40" s="4">
-        <v>3210</v>
+        <v>206</v>
       </c>
       <c r="F40" s="4">
-        <v>-5.3320750270000001</v>
+        <v>-5.090992859</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="H40" s="5">
-        <v>3390.8</v>
+        <v>217.05</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J40" s="24" t="s">
+      <c r="J40" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="K40" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="L40" s="18">
-        <v>6880</v>
-      </c>
-      <c r="M40" s="27">
-        <f>ABS((D40*E40)-L40)</f>
-        <v>460</v>
-      </c>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-      <c r="P40" s="10"/>
-    </row>
-    <row r="41" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B40, $C$2:$C$767, C40, $D$2:$D$767, D40, $E$2:$E$767, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="6" t="s">
         <v>62</v>
       </c>
@@ -3241,201 +3344,201 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B41, $C$2:$C$767, C41, $D$2:$D$767, D41, $E$2:$E$767, E41) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O41"/>
       <c r="P41"/>
     </row>
-    <row r="42" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="6" t="s">
+    <row r="42" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="3">
+        <v>46269.375</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="4">
+        <v>2</v>
+      </c>
+      <c r="E42" s="4">
+        <v>3210</v>
+      </c>
+      <c r="F42" s="4">
+        <v>-5.3320750270000001</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H42" s="5">
+        <v>3390.8</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K42" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="L42" s="18">
+        <v>6880</v>
+      </c>
+      <c r="M42" s="27">
+        <f>ABS((D42*E42)-L42)</f>
+        <v>460</v>
+      </c>
+      <c r="N42" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B42, $C$2:$C$767, C42, $D$2:$D$767, D42, $E$2:$E$767, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O42"/>
+    </row>
+    <row r="43" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="4">
-        <v>50</v>
-      </c>
-      <c r="E42" s="4">
-        <v>206</v>
-      </c>
-      <c r="F42" s="4">
-        <v>-5.090992859</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H42" s="5">
-        <v>217.05</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-      <c r="O42"/>
-      <c r="P42"/>
-    </row>
-    <row r="43" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="3">
-        <v>46252.635416666664</v>
-      </c>
       <c r="B43" s="1" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E43" s="4">
-        <v>1132</v>
+        <v>4640</v>
       </c>
       <c r="F43" s="4">
-        <v>-5.0176204059999998</v>
+        <v>-5.6335163719999999</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="H43" s="5">
-        <v>1191.8</v>
+        <v>4917</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J43" s="41"/>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="6" t="s">
-        <v>62</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B43, $C$2:$C$767, C43, $D$2:$D$767, D43, $E$2:$E$767, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="P43"/>
+    </row>
+    <row r="44" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E44" s="4">
-        <v>119</v>
+        <v>326</v>
       </c>
       <c r="F44" s="4">
-        <v>-4.9444843839999999</v>
+        <v>-6.0383340539999999</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H44" s="5">
-        <v>125.19</v>
+        <v>346.95</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="41"/>
+      <c r="J44" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K44" s="17"/>
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B44, $C$2:$C$767, C44, $D$2:$D$767, D44, $E$2:$E$767, E44) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O44"/>
-    </row>
-    <row r="45" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="3">
-        <v>46261.375</v>
+      <c r="P44"/>
+    </row>
+    <row r="45" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="4">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="E45" s="4">
-        <v>870</v>
+        <v>1277</v>
       </c>
       <c r="F45" s="4">
-        <v>-4.6575342470000001</v>
+        <v>-6.1029411759999999</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H45" s="5">
-        <v>912.5</v>
+        <v>1360</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K45" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="L45" s="18">
-        <v>17700</v>
-      </c>
-      <c r="M45" s="18">
-        <f>ABS((D45*E45)-L45)</f>
-        <v>300</v>
-      </c>
-      <c r="N45" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-      <c r="P45" s="25"/>
-    </row>
-    <row r="46" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J45" s="41"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B45, $C$2:$C$767, C45, $D$2:$D$767, D45, $E$2:$E$767, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O45"/>
+      <c r="P45"/>
+    </row>
+    <row r="46" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="3">
-        <v>46268.375</v>
+        <v>46258.601388888892</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E46" s="4">
-        <v>870.2</v>
+        <v>2271</v>
       </c>
       <c r="F46" s="4">
-        <v>-4.6356164379999996</v>
+        <v>-6.4431078519999998</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H46" s="5">
-        <v>912.5</v>
+        <v>2427.4</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>8</v>
@@ -3444,100 +3547,105 @@
         <v>55</v>
       </c>
       <c r="K46" s="18" t="s">
-        <v>241</v>
+        <v>161</v>
       </c>
       <c r="L46" s="18">
-        <v>17920</v>
+        <v>7113</v>
       </c>
       <c r="M46" s="18">
         <f>ABS((D46*E46)-L46)</f>
-        <v>516</v>
+        <v>300</v>
       </c>
       <c r="N46" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B46, $C$2:$C$767, C46, $D$2:$D$767, D46, $E$2:$E$767, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O46"/>
+      <c r="P46"/>
+    </row>
+    <row r="47" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E47" s="4">
-        <v>3760</v>
+        <v>1614</v>
       </c>
       <c r="F47" s="4">
-        <v>-4.5249098569999999</v>
+        <v>-6.6026271630000002</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="H47" s="5">
-        <v>3938.2</v>
+        <v>1728.1</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="41"/>
+      <c r="J47" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B47, $C$2:$C$767, C47, $D$2:$D$767, D47, $E$2:$E$767, E47) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O47"/>
-    </row>
-    <row r="48" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="3">
-        <v>46252.688194444447</v>
+      <c r="P47"/>
+    </row>
+    <row r="48" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E48" s="4">
-        <v>640</v>
+        <v>4710</v>
       </c>
       <c r="F48" s="4">
-        <v>-4.4633527390000003</v>
+        <v>-6.6309842400000001</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="H48" s="5">
-        <v>669.9</v>
+        <v>5044.5</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J48" s="41" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B48, $C$2:$C$767, C48, $D$2:$D$767, D48, $E$2:$E$767, E48) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O48"/>
       <c r="P48"/>
     </row>
-    <row r="49" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="6" t="s">
         <v>62</v>
       </c>
@@ -3551,10 +3659,10 @@
         <v>50</v>
       </c>
       <c r="E49" s="4">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F49" s="4">
-        <v>-4.4449726649999999</v>
+        <v>-6.821963394</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>70</v>
@@ -3565,66 +3673,65 @@
       <c r="I49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J49" s="42" t="s">
+      <c r="J49" s="41" t="s">
         <v>41</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B49, $C$2:$C$767, C49, $D$2:$D$767, D49, $E$2:$E$767, E49) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O49"/>
       <c r="P49"/>
     </row>
-    <row r="50" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="6" t="s">
-        <v>62</v>
+    <row r="50" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D50" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E50" s="4">
-        <v>6920</v>
+        <v>850</v>
       </c>
       <c r="F50" s="4">
-        <v>-4.4198895030000003</v>
+        <v>-6.8493150680000001</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="H50" s="5">
-        <v>7240</v>
+        <v>912.5</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J50" s="22" t="s">
-        <v>140</v>
+      <c r="J50" s="42" t="s">
+        <v>55</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-      <c r="O50"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B50, $C$2:$C$767, C50, $D$2:$D$767, D50, $E$2:$E$767, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
       <c r="P50"/>
     </row>
-    <row r="51" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="3">
-        <v>46252.635416666664</v>
+        <v>46121.375</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>10</v>
@@ -3633,393 +3740,387 @@
         <v>3</v>
       </c>
       <c r="E51" s="4">
-        <v>1302</v>
+        <v>1614</v>
       </c>
       <c r="F51" s="4">
-        <v>-4.2647058820000003</v>
+        <v>-7.1346375139999996</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H51" s="5">
-        <v>1360</v>
+        <v>1738</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J51" s="41" t="s">
+      <c r="J51" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" t="str">
-        <f t="shared" si="0"/>
+      <c r="K51" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="L51" s="18">
+        <f>3*1794</f>
+        <v>5382</v>
+      </c>
+      <c r="M51" s="18">
+        <f>ABS((D51*E51)-L51)</f>
+        <v>540</v>
+      </c>
+      <c r="N51" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B51, $C$2:$C$767, C51, $D$2:$D$767, D51, $E$2:$E$767, E51) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O51"/>
       <c r="P51"/>
     </row>
-    <row r="52" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="3">
-        <v>46121.375</v>
+    <row r="52" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D52" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E52" s="4">
-        <v>1664</v>
+        <v>4560</v>
       </c>
       <c r="F52" s="4">
-        <v>-4.2577675490000004</v>
+        <v>-7.2605247100000003</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="H52" s="5">
-        <v>1738</v>
+        <v>4917</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="24" t="s">
+      <c r="J52" s="41"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B52, $C$2:$C$767, C52, $D$2:$D$767, D52, $E$2:$E$767, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O52"/>
+      <c r="P52"/>
+    </row>
+    <row r="53" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="3">
+        <v>46031.4375</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="4">
+        <v>3</v>
+      </c>
+      <c r="E53" s="4">
+        <v>1052</v>
+      </c>
+      <c r="F53" s="4">
+        <v>-7.3168582879999997</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H53" s="5">
+        <v>1135.05</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J53" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K52" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="L52" s="18">
-        <f>5*1794</f>
-        <v>8970</v>
-      </c>
-      <c r="M52" s="18">
-        <f>ABS((D52*E52)-L52)</f>
-        <v>650</v>
-      </c>
-      <c r="N52" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-      <c r="O52"/>
-      <c r="P52" s="10"/>
-    </row>
-    <row r="53" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="6" t="s">
+      <c r="M53" s="18">
+        <f>ABS((D53*E53)-L53)</f>
+        <v>3156</v>
+      </c>
+      <c r="N53" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B53, $C$2:$C$767, C53, $D$2:$D$767, D53, $E$2:$E$767, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="P53" s="19"/>
+    </row>
+    <row r="54" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="4">
-        <v>40</v>
-      </c>
-      <c r="E53" s="4">
-        <v>862</v>
-      </c>
-      <c r="F53" s="4">
-        <v>-4.2222222220000001</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H53" s="5">
-        <v>900</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J53" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-      <c r="O53"/>
-      <c r="P53"/>
-    </row>
-    <row r="54" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="3">
-        <v>46252.635416666664</v>
-      </c>
       <c r="B54" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="4">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E54" s="4">
-        <v>1142</v>
+        <v>116</v>
       </c>
       <c r="F54" s="4">
-        <v>-4.1785534489999998</v>
+        <v>-7.3408419199999999</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="H54" s="5">
-        <v>1191.8</v>
+        <v>125.19</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="22" t="s">
-        <v>41</v>
-      </c>
+      <c r="J54" s="41"/>
       <c r="K54" s="17"/>
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B54, $C$2:$C$767, C54, $D$2:$D$767, D54, $E$2:$E$767, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O54"/>
+      <c r="P54"/>
+    </row>
+    <row r="55" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D55" s="4">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="E55" s="4">
-        <v>31.01</v>
+        <v>1751</v>
       </c>
       <c r="F55" s="4">
-        <v>-3.8747675140000002</v>
+        <v>-7.6963626779999998</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="H55" s="5">
-        <v>32.26</v>
+        <v>1897</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J55" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J55" s="41"/>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-      <c r="O55" s="34"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B55, $C$2:$C$767, C55, $D$2:$D$767, D55, $E$2:$E$767, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O55"/>
       <c r="P55"/>
     </row>
-    <row r="56" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="3">
-        <v>46252.6875</v>
+    <row r="56" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="4">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="E56" s="4">
-        <v>1666</v>
+        <v>115.25</v>
       </c>
       <c r="F56" s="4">
-        <v>-3.59354204</v>
+        <v>-7.9399313039999999</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H56" s="5">
-        <v>1728.1</v>
+        <v>125.19</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J56" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J56" s="41"/>
       <c r="K56" s="17"/>
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B56, $C$2:$C$767, C56, $D$2:$D$767, D56, $E$2:$E$767, E56) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O56"/>
       <c r="P56"/>
     </row>
-    <row r="57" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3">
-        <v>46252.635416666664</v>
+        <v>46254.375</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D57" s="4">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="E57" s="4">
-        <v>391</v>
+        <v>2230</v>
       </c>
       <c r="F57" s="4">
-        <v>-3.3015951530000001</v>
+        <v>-8.1321578639999998</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H57" s="5">
-        <v>404.35</v>
+        <v>2427.4</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J57" s="41" t="s">
+      <c r="J57" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="17"/>
+      <c r="K57" s="17" t="s">
+        <v>148</v>
+      </c>
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
-      <c r="N57" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="3">
-        <v>46260.375</v>
+      <c r="N57" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B57, $C$2:$C$767, C57, $D$2:$D$767, D57, $E$2:$E$767, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O57"/>
+      <c r="P57"/>
+    </row>
+    <row r="58" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D58" s="4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E58" s="4">
-        <v>2348</v>
+        <v>836</v>
       </c>
       <c r="F58" s="4">
-        <v>-3.2709895360000001</v>
+        <v>-8.3835616440000003</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H58" s="5">
-        <v>2427.4</v>
+        <v>912.5</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="24" t="s">
+      <c r="J58" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B58, $C$2:$C$767, C58, $D$2:$D$767, D58, $E$2:$E$767, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O58"/>
+      <c r="P58"/>
+    </row>
+    <row r="59" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="4">
+        <v>10</v>
+      </c>
+      <c r="E59" s="4">
+        <v>561</v>
+      </c>
+      <c r="F59" s="4">
+        <v>-8.706265256</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H59" s="5">
+        <v>614.5</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="41" t="s">
         <v>41</v>
-      </c>
-      <c r="K58" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="L58" s="18">
-        <v>7344</v>
-      </c>
-      <c r="M58" s="18">
-        <f>ABS((D58*E58)-L58)</f>
-        <v>300</v>
-      </c>
-      <c r="N58" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="3">
-        <v>46252.6875</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="4">
-        <v>50</v>
-      </c>
-      <c r="E59" s="4">
-        <v>203.5</v>
-      </c>
-      <c r="F59" s="4">
-        <v>-3.2564772999999998</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H59" s="5">
-        <v>210.35</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J59" s="42" t="s">
-        <v>55</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
+        <f>IF(COUNTIFS( $B$2:$B$767, B59, $C$2:$C$767, C59, $D$2:$D$767, D59, $E$2:$E$767, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O59"/>
       <c r="P59"/>
     </row>
-    <row r="60" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" s="4">
-        <v>3810</v>
+        <v>4456</v>
       </c>
       <c r="F60" s="4">
-        <v>-3.2552942969999998</v>
+        <v>-9.3756355500000002</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H60" s="5">
-        <v>3938.2</v>
+        <v>4917</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>8</v>
@@ -4029,16 +4130,18 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="3">
-        <v>46274.375</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B60, $C$2:$C$767, C60, $D$2:$D$767, D60, $E$2:$E$767, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O60"/>
+      <c r="P60"/>
+    </row>
+    <row r="61" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>10</v>
@@ -4047,110 +4150,103 @@
         <v>15</v>
       </c>
       <c r="E61" s="4">
-        <v>1005</v>
+        <v>4415</v>
       </c>
       <c r="F61" s="4">
-        <v>-3.2071655589999999</v>
+        <v>-10.20947732</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H61" s="5">
-        <v>1038.3</v>
+        <v>4917</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J61" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K61" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="L61" s="18">
-        <v>15600</v>
-      </c>
-      <c r="M61" s="18">
-        <f>ABS((D61*E61)-L61)</f>
-        <v>525</v>
-      </c>
-      <c r="N61" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="20">
-        <v>46255</v>
+      <c r="J61" s="41"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
+      <c r="N61" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B61, $C$2:$C$767, C61, $D$2:$D$767, D61, $E$2:$E$767, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O61"/>
+      <c r="P61"/>
+    </row>
+    <row r="62" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="3">
+        <v>46267.375</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D62" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E62" s="4">
-        <v>336</v>
+        <v>20050</v>
       </c>
       <c r="F62" s="4">
-        <v>-3.156074362</v>
+        <v>-10.290827739999999</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H62" s="5">
-        <v>346.95</v>
+        <v>22350</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J62" s="24" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="K62" s="18" t="s">
-        <v>150</v>
+        <v>237</v>
       </c>
       <c r="L62" s="18">
-        <v>8700</v>
+        <v>20350</v>
       </c>
       <c r="M62" s="18">
         <f>ABS((D62*E62)-L62)</f>
         <v>300</v>
       </c>
       <c r="N62" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B62, $C$2:$C$767, C62, $D$2:$D$767, D62, $E$2:$E$767, E62) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O62"/>
       <c r="P62"/>
     </row>
-    <row r="63" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D63" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E63" s="4">
-        <v>4010</v>
+        <v>701</v>
       </c>
       <c r="F63" s="4">
-        <v>-2.9760464550000001</v>
+        <v>-11.265822780000001</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="H63" s="5">
-        <v>4133</v>
+        <v>790</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>8</v>
@@ -4162,56 +4258,57 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B63, $C$2:$C$767, C63, $D$2:$D$767, D63, $E$2:$E$767, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O63"/>
+      <c r="P63"/>
+    </row>
+    <row r="64" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D64" s="4">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="E64" s="4">
-        <v>401</v>
+        <v>111</v>
       </c>
       <c r="F64" s="4">
-        <v>-2.8702918739999999</v>
+        <v>-11.33477115</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H64" s="5">
-        <v>412.85</v>
+        <v>125.19</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J64" s="22" t="s">
-        <v>55</v>
-      </c>
+      <c r="J64" s="41"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B64, $C$2:$C$767, C64, $D$2:$D$767, D64, $E$2:$E$767, E64) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O64"/>
-    </row>
-    <row r="65" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="6" t="s">
-        <v>62</v>
+      <c r="P64"/>
+    </row>
+    <row r="65" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>10</v>
@@ -4220,16 +4317,16 @@
         <v>2</v>
       </c>
       <c r="E65" s="4">
-        <v>3830</v>
+        <v>2892</v>
       </c>
       <c r="F65" s="4">
-        <v>-2.7474480730000002</v>
+        <v>-12.06786464</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H65" s="5">
-        <v>3938.2</v>
+        <v>3288.9</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>8</v>
@@ -4239,240 +4336,242 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="3">
-        <v>46252.6875</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D66" s="4">
-        <v>20</v>
-      </c>
-      <c r="E66" s="4">
-        <v>122</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B65, $C$2:$C$767, C65, $D$2:$D$767, D65, $E$2:$E$767, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O65"/>
+      <c r="P65"/>
+    </row>
+    <row r="66" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="29">
+        <v>46255</v>
+      </c>
+      <c r="B66" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="31">
+        <v>1</v>
+      </c>
+      <c r="E66" s="31">
+        <v>19550</v>
       </c>
       <c r="F66" s="4">
-        <v>-2.5481268469999998</v>
+        <v>-12.52796421</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="H66" s="5">
-        <v>125.19</v>
+        <v>22350</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="42" t="s">
+      <c r="J66" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
-      <c r="M66" s="17"/>
-      <c r="N66" t="str">
-        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$767, B66, $C$2:$C$767, C66, $D$2:$D$767, D66, $E$2:$E$767, E66) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="3">
-        <v>46261.375</v>
+      <c r="K66" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="L66" s="27">
+        <v>19992</v>
+      </c>
+      <c r="M66" s="27">
+        <f>ABS((D66*E66)-L66)</f>
+        <v>442</v>
+      </c>
+      <c r="N66" s="28" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B66, $C$2:$C$767, C66, $D$2:$D$767, D66, $E$2:$E$767, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O66"/>
+      <c r="P66"/>
+    </row>
+    <row r="67" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D67" s="4">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E67" s="4">
-        <v>205</v>
+        <v>4410</v>
       </c>
       <c r="F67" s="4">
-        <v>-2.543380081</v>
+        <v>-12.57805531</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="H67" s="5">
-        <v>210.35</v>
+        <v>5044.5</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K67" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="L67" s="18">
-        <v>10550</v>
-      </c>
-      <c r="M67" s="18">
-        <f>ABS((D67*E67)-L67)</f>
-        <v>300</v>
-      </c>
-      <c r="N67" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" s="26" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J67" s="41"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B67, $C$2:$C$767, C67, $D$2:$D$767, D67, $E$2:$E$767, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O67"/>
+      <c r="P67"/>
+    </row>
+    <row r="68" spans="1:16" s="26" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D68" s="4">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E68" s="4">
-        <v>878</v>
+        <v>4364</v>
       </c>
       <c r="F68" s="4">
-        <v>-2.4444444440000002</v>
+        <v>-13.48993954</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="H68" s="5">
-        <v>900</v>
+        <v>5044.5</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="41" t="s">
-        <v>55</v>
+      <c r="J68" s="42" t="s">
+        <v>41</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-      <c r="O68" s="10"/>
-      <c r="P68" s="10"/>
-    </row>
-    <row r="69" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B68, $C$2:$C$767, C68, $D$2:$D$767, D68, $E$2:$E$767, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O68"/>
+      <c r="P68"/>
+    </row>
+    <row r="69" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D69" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E69" s="4">
-        <v>212</v>
+        <v>19052</v>
       </c>
       <c r="F69" s="4">
-        <v>-2.3266528449999999</v>
+        <v>-14.75615213</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="H69" s="5">
-        <v>217.05</v>
+        <v>22350</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J69" s="41"/>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B69, $C$2:$C$767, C69, $D$2:$D$767, D69, $E$2:$E$767, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O69"/>
+      <c r="P69"/>
+    </row>
+    <row r="70" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D70" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E70" s="4">
-        <v>261</v>
+        <v>196</v>
       </c>
       <c r="F70" s="4">
-        <v>-2.1922428329999999</v>
+        <v>-16.239316240000001</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H70" s="5">
-        <v>266.85000000000002</v>
+        <v>234</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J70" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J70" s="41"/>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B70, $C$2:$C$767, C70, $D$2:$D$767, D70, $E$2:$E$767, E70) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O70"/>
-      <c r="P70" s="34"/>
-    </row>
-    <row r="71" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P70"/>
+    </row>
+    <row r="71" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D71" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="4">
-        <v>3856</v>
+        <v>2752</v>
       </c>
       <c r="F71" s="4">
-        <v>-2.087247981</v>
+        <v>-16.324607010000001</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H71" s="5">
-        <v>3938.2</v>
+        <v>3288.9</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>8</v>
@@ -4482,122 +4581,114 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-      <c r="O71" s="19"/>
-      <c r="P71" s="10"/>
-    </row>
-    <row r="72" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="3">
-        <v>46252.6875</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B71, $C$2:$C$767, C71, $D$2:$D$767, D71, $E$2:$E$767, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O71"/>
+      <c r="P71"/>
+    </row>
+    <row r="72" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D72" s="4">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E72" s="4">
-        <v>277</v>
+        <v>18552</v>
       </c>
       <c r="F72" s="4">
-        <v>-1.4059441180000001</v>
+        <v>-16.993288589999999</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H72" s="5">
-        <v>280.95</v>
+        <v>22350</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J72" s="41"/>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B72, $C$2:$C$767, C72, $D$2:$D$767, D72, $E$2:$E$767, E72) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O72"/>
-    </row>
-    <row r="73" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="3">
-        <v>46268.385416666664</v>
+      <c r="P72"/>
+    </row>
+    <row r="73" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D73" s="4">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E73" s="4">
-        <v>214</v>
+        <v>4164</v>
       </c>
       <c r="F73" s="4">
-        <v>-1.4052061739999999</v>
+        <v>-17.454653579999999</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="H73" s="5">
-        <v>217.05</v>
+        <v>5044.5</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J73" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K73" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="L73" s="18">
-        <v>21900</v>
-      </c>
-      <c r="M73" s="18">
-        <f>ABS((D73*E73)-L73)</f>
-        <v>500</v>
-      </c>
-      <c r="N73" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="6" t="s">
-        <v>62</v>
+      <c r="J73" s="41"/>
+      <c r="K73" s="17"/>
+      <c r="L73" s="17"/>
+      <c r="M73" s="17"/>
+      <c r="N73" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B73, $C$2:$C$767, C73, $D$2:$D$767, D73, $E$2:$E$767, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O73"/>
+      <c r="P73"/>
+    </row>
+    <row r="74" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="3">
+        <v>46252.688194444447</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D74" s="4">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="E74" s="4">
-        <v>3888</v>
+        <v>136.15</v>
       </c>
       <c r="F74" s="4">
-        <v>-1.2746940229999999</v>
+        <v>-18.055973519999998</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="H74" s="5">
-        <v>3938.2</v>
+        <v>166.15</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>8</v>
@@ -4607,135 +4698,135 @@
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-      <c r="O74" s="26"/>
-    </row>
-    <row r="75" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="3">
-        <v>46252.645138888889</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B74, $C$2:$C$767, C74, $D$2:$D$767, D74, $E$2:$E$767, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O74"/>
+      <c r="P74"/>
+    </row>
+    <row r="75" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D75" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E75" s="4">
-        <v>401</v>
+        <v>2660</v>
       </c>
       <c r="F75" s="4">
-        <v>-0.82849016939999998</v>
+        <v>-19.121894860000001</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="H75" s="5">
-        <v>404.35</v>
+        <v>3288.9</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J75" s="43" t="s">
-        <v>41</v>
-      </c>
+      <c r="J75" s="41"/>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B75, $C$2:$C$767, C75, $D$2:$D$767, D75, $E$2:$E$767, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O75"/>
+      <c r="P75"/>
+    </row>
+    <row r="76" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D76" s="4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E76" s="4">
-        <v>2435</v>
+        <v>18052</v>
       </c>
       <c r="F76" s="4">
-        <v>-0.49039640379999999</v>
+        <v>-19.230425060000002</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H76" s="5">
-        <v>2447</v>
+        <v>22350</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J76" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J76" s="41"/>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B76, $C$2:$C$767, C76, $D$2:$D$767, D76, $E$2:$E$767, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O76"/>
+      <c r="P76"/>
+    </row>
+    <row r="77" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D77" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E77" s="4">
-        <v>281</v>
+        <v>660</v>
       </c>
       <c r="F77" s="4">
-        <v>1.779676099E-2</v>
+        <v>-20.318725100000002</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="H77" s="5">
-        <v>280.95</v>
+        <v>828.3</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J77" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J77" s="41"/>
       <c r="K77" s="17"/>
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-      <c r="P77" s="26"/>
-    </row>
-    <row r="78" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="3">
-        <v>46252.635416666664</v>
+        <f>IF(COUNTIFS( $B$2:$B$767, B77, $C$2:$C$767, C77, $D$2:$D$767, D77, $E$2:$E$767, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O77"/>
+      <c r="P77"/>
+    </row>
+    <row r="78" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>10</v>
@@ -4744,30 +4835,30 @@
         <v>1</v>
       </c>
       <c r="E78" s="4">
-        <v>13552</v>
+        <v>4014</v>
       </c>
       <c r="F78" s="4">
-        <v>0.68350668650000002</v>
+        <v>-20.428189119999999</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H78" s="5">
-        <v>13460</v>
+        <v>5044.5</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J78" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J78" s="41"/>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
+        <f>IF(COUNTIFS( $B$2:$B$767, B78, $C$2:$C$767, C78, $D$2:$D$767, D78, $E$2:$E$767, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O78"/>
+      <c r="P78"/>
     </row>
     <row r="79" spans="1:16" s="25" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3">
@@ -4811,51 +4902,50 @@
         <v>26810</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B79, $C$2:$C$767, C79, $D$2:$D$767, D79, $E$2:$E$767, E79) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O79" s="10"/>
       <c r="P79" s="10"/>
     </row>
-    <row r="80" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D80" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E80" s="4">
-        <v>2470</v>
+        <v>2560</v>
       </c>
       <c r="F80" s="4">
-        <v>0.93992644049999996</v>
+        <v>-22.162425129999999</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H80" s="5">
-        <v>2447</v>
+        <v>3288.9</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J80" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J80" s="41"/>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-      <c r="P80" s="25"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B80, $C$2:$C$767, C80, $D$2:$D$767, D80, $E$2:$E$767, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O80"/>
+      <c r="P80"/>
     </row>
     <row r="81" spans="1:16" s="35" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="36">
@@ -4895,11 +4985,11 @@
         <v>5755</v>
       </c>
       <c r="M81" s="33">
-        <f t="shared" ref="M81:M86" si="2">ABS((D81*E81)-L81)</f>
+        <f>ABS((D81*E81)-L81)</f>
         <v>275</v>
       </c>
       <c r="N81" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B81, $C$2:$C$767, C81, $D$2:$D$767, D81, $E$2:$E$767, E81) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O81" s="46" t="s">
@@ -4945,11 +5035,11 @@
         <v>5805</v>
       </c>
       <c r="M82" s="33">
-        <f t="shared" si="2"/>
+        <f>ABS((D82*E82)-L82)</f>
         <v>225</v>
       </c>
       <c r="N82" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B82, $C$2:$C$767, C82, $D$2:$D$767, D82, $E$2:$E$767, E82) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O82" s="46" t="s">
@@ -4995,11 +5085,11 @@
         <v>10400</v>
       </c>
       <c r="M83" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D83*E83)-L83)</f>
         <v>300</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B83, $C$2:$C$767, C83, $D$2:$D$767, D83, $E$2:$E$767, E83) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -5041,11 +5131,11 @@
         <v>13052</v>
       </c>
       <c r="M84" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D84*E84)-L84)</f>
         <v>1246</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B84, $C$2:$C$767, C84, $D$2:$D$767, D84, $E$2:$E$767, E84) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -5087,62 +5177,57 @@
         <v>35880</v>
       </c>
       <c r="M85" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D85*E85)-L85)</f>
         <v>26710</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B85, $C$2:$C$767, C85, $D$2:$D$767, D85, $E$2:$E$767, E85) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O85" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="3">
-        <v>46275.457638888889</v>
+    <row r="86" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D86" s="4">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E86" s="4">
-        <v>222</v>
+        <v>3914</v>
       </c>
       <c r="F86" s="4">
-        <v>2.2805805110000001</v>
+        <v>-22.410546140000001</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="H86" s="5">
-        <v>217.05</v>
+        <v>5044.5</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J86" s="24" t="s">
+      <c r="J86" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="K86" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="L86" s="18">
-        <v>56375</v>
-      </c>
-      <c r="M86" s="18">
-        <f t="shared" si="2"/>
-        <v>34175</v>
-      </c>
-      <c r="N86" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
+      <c r="K86" s="17"/>
+      <c r="L86" s="17"/>
+      <c r="M86" s="17"/>
+      <c r="N86" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$767, B86, $C$2:$C$767, C86, $D$2:$D$767, D86, $E$2:$E$767, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O86"/>
+      <c r="P86"/>
     </row>
     <row r="87" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="11">
@@ -5179,7 +5264,7 @@
       <c r="L87" s="18"/>
       <c r="M87" s="18"/>
       <c r="N87" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B87, $C$2:$C$767, C87, $D$2:$D$767, D87, $E$2:$E$767, E87) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O87" s="46" t="s">
@@ -5224,11 +5309,11 @@
         <v>19730.5</v>
       </c>
       <c r="M88" s="33">
-        <f t="shared" ref="M88:M102" si="3">ABS((D88*E88)-L88)</f>
+        <f>ABS((D88*E88)-L88)</f>
         <v>504.5</v>
       </c>
       <c r="N88" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B88, $C$2:$C$767, C88, $D$2:$D$767, D88, $E$2:$E$767, E88) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O88" s="46" t="s">
@@ -5274,11 +5359,11 @@
         <v>19690</v>
       </c>
       <c r="M89" s="33">
-        <f t="shared" si="3"/>
+        <f>ABS((D89*E89)-L89)</f>
         <v>545</v>
       </c>
       <c r="N89" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B89, $C$2:$C$767, C89, $D$2:$D$767, D89, $E$2:$E$767, E89) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O89" s="46" t="s">
@@ -5324,11 +5409,11 @@
         <v>35880</v>
       </c>
       <c r="M90" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D90*E90)-L90)</f>
         <v>26610</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B90, $C$2:$C$767, C90, $D$2:$D$767, D90, $E$2:$E$767, E90) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O90" s="10"/>
@@ -5372,11 +5457,11 @@
         <v>5905</v>
       </c>
       <c r="M91" s="66">
-        <f t="shared" si="3"/>
+        <f>ABS((D91*E91)-L91)</f>
         <v>275</v>
       </c>
       <c r="N91" s="67" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B91, $C$2:$C$767, C91, $D$2:$D$767, D91, $E$2:$E$767, E91) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O91" s="68"/>
@@ -5420,11 +5505,11 @@
         <v>3560</v>
       </c>
       <c r="M92" s="33">
-        <f t="shared" si="3"/>
+        <f>ABS((D92*E92)-L92)</f>
         <v>175</v>
       </c>
       <c r="N92" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B92, $C$2:$C$767, C92, $D$2:$D$767, D92, $E$2:$E$767, E92) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O92" s="46" t="s">
@@ -5469,11 +5554,11 @@
         <v>3510</v>
       </c>
       <c r="M93" s="33">
-        <f t="shared" si="3"/>
+        <f>ABS((D93*E93)-L93)</f>
         <v>225</v>
       </c>
       <c r="N93" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B93, $C$2:$C$767, C93, $D$2:$D$767, D93, $E$2:$E$767, E93) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O93" s="46" t="s">
@@ -5519,11 +5604,11 @@
         <v>8700</v>
       </c>
       <c r="M94" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D94*E94)-L94)</f>
         <v>300</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B94, $C$2:$C$767, C94, $D$2:$D$767, D94, $E$2:$E$767, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O94" s="10"/>
@@ -5567,11 +5652,11 @@
         <v>8220</v>
       </c>
       <c r="M95" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D95*E95)-L95)</f>
         <v>360</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B95, $C$2:$C$767, C95, $D$2:$D$767, D95, $E$2:$E$767, E95) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O95" s="46" t="s">
@@ -5616,11 +5701,11 @@
         <v>20010</v>
       </c>
       <c r="M96" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D96*E96)-L96)</f>
         <v>450</v>
       </c>
       <c r="N96" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B96, $C$2:$C$767, C96, $D$2:$D$767, D96, $E$2:$E$767, E96) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O96" s="10"/>
@@ -5664,11 +5749,11 @@
         <v>9170</v>
       </c>
       <c r="M97" s="33">
-        <f t="shared" si="3"/>
+        <f>ABS((D97*E97)-L97)</f>
         <v>200</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B97, $C$2:$C$767, C97, $D$2:$D$767, D97, $E$2:$E$767, E97) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O97" s="10"/>
@@ -5712,11 +5797,11 @@
         <v>8480</v>
       </c>
       <c r="M98" s="27">
-        <f t="shared" si="3"/>
+        <f>ABS((D98*E98)-L98)</f>
         <v>280</v>
       </c>
       <c r="N98" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B98, $C$2:$C$767, C98, $D$2:$D$767, D98, $E$2:$E$767, E98) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O98" s="46" t="s">
@@ -5724,7 +5809,7 @@
       </c>
       <c r="P98" s="10"/>
     </row>
-    <row r="99" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -5762,11 +5847,11 @@
         <v>73800</v>
       </c>
       <c r="M99" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D99*E99)-L99)</f>
         <v>48320</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B99, $C$2:$C$767, C99, $D$2:$D$767, D99, $E$2:$E$767, E99) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O99" s="46" t="s">
@@ -5812,11 +5897,11 @@
         <v>20260</v>
       </c>
       <c r="M100" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D100*E100)-L100)</f>
         <v>300</v>
       </c>
       <c r="N100" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B100, $C$2:$C$767, C100, $D$2:$D$767, D100, $E$2:$E$767, E100) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O100"/>
@@ -5860,11 +5945,11 @@
         <v>9902</v>
       </c>
       <c r="M101" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D101*E101)-L101)</f>
         <v>646</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B101, $C$2:$C$767, C101, $D$2:$D$767, D101, $E$2:$E$767, E101) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O101" s="46" t="s">
@@ -5910,11 +5995,11 @@
         <v>35880</v>
       </c>
       <c r="M102" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D102*E102)-L102)</f>
         <v>26460</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B102, $C$2:$C$767, C102, $D$2:$D$767, D102, $E$2:$E$767, E102) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O102" s="10"/>
@@ -5950,7 +6035,7 @@
       </c>
       <c r="J103" s="40"/>
       <c r="N103" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B103, $C$2:$C$767, C103, $D$2:$D$767, D103, $E$2:$E$767, E103) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -5984,7 +6069,7 @@
       </c>
       <c r="J104" s="40"/>
       <c r="N104" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B104, $C$2:$C$767, C104, $D$2:$D$767, D104, $E$2:$E$767, E104) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O104" s="46" t="s">
@@ -6034,7 +6119,7 @@
         <v>300</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B105, $C$2:$C$767, C105, $D$2:$D$767, D105, $E$2:$E$767, E105) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O105"/>
@@ -6082,7 +6167,7 @@
         <v>300.00000000000182</v>
       </c>
       <c r="N106" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B106, $C$2:$C$767, C106, $D$2:$D$767, D106, $E$2:$E$767, E106) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O106" s="46" t="s">
@@ -6132,7 +6217,7 @@
         <v>274</v>
       </c>
       <c r="N107" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B107, $C$2:$C$767, C107, $D$2:$D$767, D107, $E$2:$E$767, E107) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O107" s="46" t="s">
@@ -6182,7 +6267,7 @@
         <v>150</v>
       </c>
       <c r="N108" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B108, $C$2:$C$767, C108, $D$2:$D$767, D108, $E$2:$E$767, E108) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -6228,7 +6313,7 @@
         <v>250</v>
       </c>
       <c r="N109" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B109, $C$2:$C$767, C109, $D$2:$D$767, D109, $E$2:$E$767, E109) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O109" s="10"/>
@@ -6264,7 +6349,7 @@
       </c>
       <c r="J110" s="40"/>
       <c r="N110" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B110, $C$2:$C$767, C110, $D$2:$D$767, D110, $E$2:$E$767, E110) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -6306,11 +6391,11 @@
         <v>20070</v>
       </c>
       <c r="M111" s="18">
-        <f t="shared" ref="M111:M123" si="4">ABS((D111*E111)-L111)</f>
+        <f>ABS((D111*E111)-L111)</f>
         <v>810</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B111, $C$2:$C$767, C111, $D$2:$D$767, D111, $E$2:$E$767, E111) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -6352,11 +6437,11 @@
         <v>15075</v>
       </c>
       <c r="M112" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D112*E112)-L112)</f>
         <v>645</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B112, $C$2:$C$767, C112, $D$2:$D$767, D112, $E$2:$E$767, E112) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O112" s="46" t="s">
@@ -6401,11 +6486,11 @@
         <v>9170</v>
       </c>
       <c r="M113" s="33">
-        <f t="shared" si="4"/>
+        <f>ABS((D113*E113)-L113)</f>
         <v>300</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B113, $C$2:$C$767, C113, $D$2:$D$767, D113, $E$2:$E$767, E113) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O113" s="10"/>
@@ -6449,11 +6534,11 @@
         <v>8420</v>
       </c>
       <c r="M114" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D114*E114)-L114)</f>
         <v>300</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B114, $C$2:$C$767, C114, $D$2:$D$767, D114, $E$2:$E$767, E114) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -6495,11 +6580,11 @@
         <v>11320</v>
       </c>
       <c r="M115" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D115*E115)-L115)</f>
         <v>400</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B115, $C$2:$C$767, C115, $D$2:$D$767, D115, $E$2:$E$767, E115) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -6541,11 +6626,11 @@
         <v>3005</v>
       </c>
       <c r="M116" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D116*E116)-L116)</f>
         <v>240</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B116, $C$2:$C$767, C116, $D$2:$D$767, D116, $E$2:$E$767, E116) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O116" s="10"/>
@@ -6589,17 +6674,17 @@
         <v>14100</v>
       </c>
       <c r="M117" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D117*E117)-L117)</f>
         <v>500</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B117, $C$2:$C$767, C117, $D$2:$D$767, D117, $E$2:$E$767, E117) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O117" s="10"/>
       <c r="P117" s="10"/>
     </row>
-    <row r="118" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -6637,11 +6722,11 @@
         <v>73800</v>
       </c>
       <c r="M118" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D118*E118)-L118)</f>
         <v>47900</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B118, $C$2:$C$767, C118, $D$2:$D$767, D118, $E$2:$E$767, E118) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O118" s="46" t="s">
@@ -6686,11 +6771,11 @@
         <v>18960</v>
       </c>
       <c r="M119" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D119*E119)-L119)</f>
         <v>816</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B119, $C$2:$C$767, C119, $D$2:$D$767, D119, $E$2:$E$767, E119) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -6732,15 +6817,15 @@
         <v>3300</v>
       </c>
       <c r="M120" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D120*E120)-L120)</f>
         <v>250</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B120, $C$2:$C$767, C120, $D$2:$D$767, D120, $E$2:$E$767, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3">
         <v>46266.375</v>
       </c>
@@ -6778,18 +6863,18 @@
         <v>25300</v>
       </c>
       <c r="M121" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D121*E121)-L121)</f>
         <v>650</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B121, $C$2:$C$767, C121, $D$2:$D$767, D121, $E$2:$E$767, E121) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O121" s="46" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -6827,11 +6912,11 @@
         <v>12480</v>
       </c>
       <c r="M122" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D122*E122)-L122)</f>
         <v>495</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B122, $C$2:$C$767, C122, $D$2:$D$767, D122, $E$2:$E$767, E122) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O122" s="46" t="s">
@@ -6876,11 +6961,11 @@
         <v>32200</v>
       </c>
       <c r="M123" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D123*E123)-L123)</f>
         <v>1200</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B123, $C$2:$C$767, C123, $D$2:$D$767, D123, $E$2:$E$767, E123) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -6914,7 +6999,7 @@
       </c>
       <c r="J124" s="40"/>
       <c r="N124" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B124, $C$2:$C$767, C124, $D$2:$D$767, D124, $E$2:$E$767, E124) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O124" s="25"/>
@@ -6957,11 +7042,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M125" s="33">
-        <f t="shared" ref="M125:M130" si="5">ABS((D125*E125)-L125)</f>
+        <f>ABS((D125*E125)-L125)</f>
         <v>710.99999999999636</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B125, $C$2:$C$767, C125, $D$2:$D$767, D125, $E$2:$E$767, E125) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O125" s="46" t="s">
@@ -7007,11 +7092,11 @@
         <v>8570</v>
       </c>
       <c r="M126" s="33">
-        <f t="shared" si="5"/>
+        <f>ABS((D126*E126)-L126)</f>
         <v>650</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B126, $C$2:$C$767, C126, $D$2:$D$767, D126, $E$2:$E$767, E126) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O126" s="46" t="s">
@@ -7056,11 +7141,11 @@
         <v>9270</v>
       </c>
       <c r="M127" s="18">
-        <f t="shared" si="5"/>
+        <f>ABS((D127*E127)-L127)</f>
         <v>300</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B127, $C$2:$C$767, C127, $D$2:$D$767, D127, $E$2:$E$767, E127) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P127" s="19"/>
@@ -7103,11 +7188,11 @@
         <v>10300</v>
       </c>
       <c r="M128" s="18">
-        <f t="shared" si="5"/>
+        <f>ABS((D128*E128)-L128)</f>
         <v>300</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B128, $C$2:$C$767, C128, $D$2:$D$767, D128, $E$2:$E$767, E128) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
@@ -7151,15 +7236,15 @@
         <v>14200</v>
       </c>
       <c r="M129" s="18">
-        <f t="shared" si="5"/>
+        <f>ABS((D129*E129)-L129)</f>
         <v>500</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f>IF(COUNTIFS( $B$2:$B$767, B129, $C$2:$C$767, C129, $D$2:$D$767, D129, $E$2:$E$767, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -7197,11 +7282,11 @@
         <v>25780</v>
       </c>
       <c r="M130" s="18">
-        <f t="shared" si="5"/>
+        <f>ABS((D130*E130)-L130)</f>
         <v>300</v>
       </c>
       <c r="N130" t="str">
-        <f t="shared" ref="N130:N193" si="6">IF(COUNTIFS( $B$2:$B$767, B130, $C$2:$C$767, C130, $D$2:$D$767, D130, $E$2:$E$767, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f>IF(COUNTIFS( $B$2:$B$767, B130, $C$2:$C$767, C130, $D$2:$D$767, D130, $E$2:$E$767, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="46" t="s">
@@ -7241,7 +7326,7 @@
         <v>117</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B131, $C$2:$C$767, C131, $D$2:$D$767, D131, $E$2:$E$767, E131) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7287,7 +7372,7 @@
         <v>651</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B132, $C$2:$C$767, C132, $D$2:$D$767, D132, $E$2:$E$767, E132) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7333,7 +7418,7 @@
         <v>300</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B133, $C$2:$C$767, C133, $D$2:$D$767, D133, $E$2:$E$767, E133) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7379,7 +7464,7 @@
         <v>650</v>
       </c>
       <c r="N134" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B134, $C$2:$C$767, C134, $D$2:$D$767, D134, $E$2:$E$767, E134) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O134"/>
@@ -7427,7 +7512,7 @@
         <v>270</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B135, $C$2:$C$767, C135, $D$2:$D$767, D135, $E$2:$E$767, E135) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O135" s="47" t="s">
@@ -7464,7 +7549,7 @@
       </c>
       <c r="J136" s="40"/>
       <c r="N136" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B136, $C$2:$C$767, C136, $D$2:$D$767, D136, $E$2:$E$767, E136) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7510,7 +7595,7 @@
         <v>880</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B137, $C$2:$C$767, C137, $D$2:$D$767, D137, $E$2:$E$767, E137) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O137" s="46" t="s">
@@ -7549,7 +7634,7 @@
         <v>118</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B138, $C$2:$C$767, C138, $D$2:$D$767, D138, $E$2:$E$767, E138) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7591,11 +7676,11 @@
         <v>4080</v>
       </c>
       <c r="M139" s="18">
-        <f t="shared" ref="M139:M144" si="7">ABS((D139*E139)-L139)</f>
+        <f>ABS((D139*E139)-L139)</f>
         <v>300</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B139, $C$2:$C$767, C139, $D$2:$D$767, D139, $E$2:$E$767, E139) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7637,11 +7722,11 @@
         <v>5370</v>
       </c>
       <c r="M140" s="18">
-        <f t="shared" si="7"/>
+        <f>ABS((D140*E140)-L140)</f>
         <v>320</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B140, $C$2:$C$767, C140, $D$2:$D$767, D140, $E$2:$E$767, E140) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7683,11 +7768,11 @@
         <v>16580</v>
       </c>
       <c r="M141" s="54">
-        <f t="shared" si="7"/>
+        <f>ABS((D141*E141)-L141)</f>
         <v>750</v>
       </c>
       <c r="N141" s="25" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B141, $C$2:$C$767, C141, $D$2:$D$767, D141, $E$2:$E$767, E141) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O141" s="25"/>
@@ -7733,11 +7818,11 @@
         <v>10410</v>
       </c>
       <c r="M142" s="18">
-        <f t="shared" si="7"/>
+        <f>ABS((D142*E142)-L142)</f>
         <v>300</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B142, $C$2:$C$767, C142, $D$2:$D$767, D142, $E$2:$E$767, E142) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O142" s="35"/>
@@ -7780,11 +7865,11 @@
         <v>73800</v>
       </c>
       <c r="M143" s="18">
-        <f t="shared" si="7"/>
+        <f>ABS((D143*E143)-L143)</f>
         <v>47480</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B143, $C$2:$C$767, C143, $D$2:$D$767, D143, $E$2:$E$767, E143) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7826,11 +7911,11 @@
         <v>12510</v>
       </c>
       <c r="M144" s="18">
-        <f t="shared" si="7"/>
+        <f>ABS((D144*E144)-L144)</f>
         <v>290</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B144, $C$2:$C$767, C144, $D$2:$D$767, D144, $E$2:$E$767, E144) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7864,7 +7949,7 @@
       </c>
       <c r="J145" s="40"/>
       <c r="N145" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B145, $C$2:$C$767, C145, $D$2:$D$767, D145, $E$2:$E$767, E145) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7906,11 +7991,11 @@
         <v>32900</v>
       </c>
       <c r="M146" s="33">
-        <f t="shared" ref="M146:M158" si="8">ABS((D146*E146)-L146)</f>
+        <f>ABS((D146*E146)-L146)</f>
         <v>1000</v>
       </c>
       <c r="N146" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B146, $C$2:$C$767, C146, $D$2:$D$767, D146, $E$2:$E$767, E146) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O146" s="26"/>
@@ -7953,11 +8038,11 @@
         <v>33200</v>
       </c>
       <c r="M147" s="33">
-        <f t="shared" si="8"/>
+        <f>ABS((D147*E147)-L147)</f>
         <v>700</v>
       </c>
       <c r="N147" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B147, $C$2:$C$767, C147, $D$2:$D$767, D147, $E$2:$E$767, E147) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -7999,11 +8084,11 @@
         <v>26020</v>
       </c>
       <c r="M148" s="18">
-        <f t="shared" si="8"/>
+        <f>ABS((D148*E148)-L148)</f>
         <v>340</v>
       </c>
       <c r="N148" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B148, $C$2:$C$767, C148, $D$2:$D$767, D148, $E$2:$E$767, E148) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O148" s="10"/>
@@ -8047,11 +8132,11 @@
         <v>11660</v>
       </c>
       <c r="M149" s="18">
-        <f t="shared" si="8"/>
+        <f>ABS((D149*E149)-L149)</f>
         <v>300</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B149, $C$2:$C$767, C149, $D$2:$D$767, D149, $E$2:$E$767, E149) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O149" s="46" t="s">
@@ -8096,11 +8181,11 @@
         <v>14400</v>
       </c>
       <c r="M150" s="18">
-        <f t="shared" si="8"/>
+        <f>ABS((D150*E150)-L150)</f>
         <v>500</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B150, $C$2:$C$767, C150, $D$2:$D$767, D150, $E$2:$E$767, E150) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8142,11 +8227,11 @@
         <v>5180</v>
       </c>
       <c r="M151" s="27">
-        <f t="shared" si="8"/>
+        <f>ABS((D151*E151)-L151)</f>
         <v>268</v>
       </c>
       <c r="N151" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B151, $C$2:$C$767, C151, $D$2:$D$767, D151, $E$2:$E$767, E151) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8188,11 +8273,11 @@
         <v>18140</v>
       </c>
       <c r="M152" s="27">
-        <f t="shared" si="8"/>
+        <f>ABS((D152*E152)-L152)</f>
         <v>650</v>
       </c>
       <c r="N152" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B152, $C$2:$C$767, C152, $D$2:$D$767, D152, $E$2:$E$767, E152) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O152" s="46" t="s">
@@ -8237,11 +8322,11 @@
         <v>26180</v>
       </c>
       <c r="M153" s="18">
-        <f t="shared" si="8"/>
+        <f>ABS((D153*E153)-L153)</f>
         <v>300</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B153, $C$2:$C$767, C153, $D$2:$D$767, D153, $E$2:$E$767, E153) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O153" s="10"/>
@@ -8285,11 +8370,11 @@
         <v>16755</v>
       </c>
       <c r="M154" s="18">
-        <f t="shared" si="8"/>
+        <f>ABS((D154*E154)-L154)</f>
         <v>295</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B154, $C$2:$C$767, C154, $D$2:$D$767, D154, $E$2:$E$767, E154) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8331,11 +8416,11 @@
         <v>8049</v>
       </c>
       <c r="M155" s="18">
-        <f t="shared" si="8"/>
+        <f>ABS((D155*E155)-L155)</f>
         <v>800</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B155, $C$2:$C$767, C155, $D$2:$D$767, D155, $E$2:$E$767, E155) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8377,11 +8462,11 @@
         <v>10510</v>
       </c>
       <c r="M156" s="18">
-        <f t="shared" si="8"/>
+        <f>ABS((D156*E156)-L156)</f>
         <v>300</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B156, $C$2:$C$767, C156, $D$2:$D$767, D156, $E$2:$E$767, E156) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8423,11 +8508,11 @@
         <v>18800</v>
       </c>
       <c r="M157" s="18">
-        <f t="shared" si="8"/>
+        <f>ABS((D157*E157)-L157)</f>
         <v>500</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B157, $C$2:$C$767, C157, $D$2:$D$767, D157, $E$2:$E$767, E157) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O157" s="47" t="s">
@@ -8472,11 +8557,11 @@
         <v>9470</v>
       </c>
       <c r="M158" s="18">
-        <f t="shared" si="8"/>
+        <f>ABS((D158*E158)-L158)</f>
         <v>300</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B158, $C$2:$C$767, C158, $D$2:$D$767, D158, $E$2:$E$767, E158) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8512,7 +8597,7 @@
         <v>118</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B159, $C$2:$C$767, C159, $D$2:$D$767, D159, $E$2:$E$767, E159) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8558,7 +8643,7 @@
         <v>300</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B160, $C$2:$C$767, C160, $D$2:$D$767, D160, $E$2:$E$767, E160) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8597,7 +8682,7 @@
       <c r="L161" s="54"/>
       <c r="M161" s="54"/>
       <c r="N161" s="25" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B161, $C$2:$C$767, C161, $D$2:$D$767, D161, $E$2:$E$767, E161) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O161" s="25"/>
@@ -8643,11 +8728,11 @@
         <v>12600</v>
       </c>
       <c r="M162" s="18">
-        <f t="shared" ref="M162:M168" si="9">ABS((D162*E162)-L162)</f>
+        <f>ABS((D162*E162)-L162)</f>
         <v>360</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B162, $C$2:$C$767, C162, $D$2:$D$767, D162, $E$2:$E$767, E162) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8689,11 +8774,11 @@
         <v>3400</v>
       </c>
       <c r="M163" s="18">
-        <f t="shared" si="9"/>
+        <f>ABS((D163*E163)-L163)</f>
         <v>250</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B163, $C$2:$C$767, C163, $D$2:$D$767, D163, $E$2:$E$767, E163) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8735,11 +8820,11 @@
         <v>7578</v>
       </c>
       <c r="M164" s="33">
-        <f t="shared" si="9"/>
+        <f>ABS((D164*E164)-L164)</f>
         <v>294</v>
       </c>
       <c r="N164" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B164, $C$2:$C$767, C164, $D$2:$D$767, D164, $E$2:$E$767, E164) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O164" s="10"/>
@@ -8783,11 +8868,11 @@
         <v>7578</v>
       </c>
       <c r="M165" s="33">
-        <f t="shared" si="9"/>
+        <f>ABS((D165*E165)-L165)</f>
         <v>294</v>
       </c>
       <c r="N165" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B165, $C$2:$C$767, C165, $D$2:$D$767, D165, $E$2:$E$767, E165) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8829,11 +8914,11 @@
         <v>4968</v>
       </c>
       <c r="M166" s="33">
-        <f t="shared" si="9"/>
+        <f>ABS((D166*E166)-L166)</f>
         <v>280</v>
       </c>
       <c r="N166" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B166, $C$2:$C$767, C166, $D$2:$D$767, D166, $E$2:$E$767, E166) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8875,11 +8960,11 @@
         <v>8820</v>
       </c>
       <c r="M167" s="33">
-        <f t="shared" si="9"/>
+        <f>ABS((D167*E167)-L167)</f>
         <v>650</v>
       </c>
       <c r="N167" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B167, $C$2:$C$767, C167, $D$2:$D$767, D167, $E$2:$E$767, E167) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8921,11 +9006,11 @@
         <v>36946</v>
       </c>
       <c r="M168" s="33">
-        <f t="shared" si="9"/>
+        <f>ABS((D168*E168)-L168)</f>
         <v>934</v>
       </c>
       <c r="N168" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B168, $C$2:$C$767, C168, $D$2:$D$767, D168, $E$2:$E$767, E168) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -8966,7 +9051,7 @@
       <c r="L169" s="17"/>
       <c r="M169" s="17"/>
       <c r="N169" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B169, $C$2:$C$767, C169, $D$2:$D$767, D169, $E$2:$E$767, E169) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9000,7 +9085,7 @@
       </c>
       <c r="J170" s="40"/>
       <c r="N170" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B170, $C$2:$C$767, C170, $D$2:$D$767, D170, $E$2:$E$767, E170) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O170" s="35"/>
@@ -9047,7 +9132,7 @@
         <v>500</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B171, $C$2:$C$767, C171, $D$2:$D$767, D171, $E$2:$E$767, E171) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9093,7 +9178,7 @@
         <v>450</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B172, $C$2:$C$767, C172, $D$2:$D$767, D172, $E$2:$E$767, E172) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9129,7 +9214,7 @@
         <v>118</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B173, $C$2:$C$767, C173, $D$2:$D$767, D173, $E$2:$E$767, E173) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9175,7 +9260,7 @@
         <v>300</v>
       </c>
       <c r="N174" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B174, $C$2:$C$767, C174, $D$2:$D$767, D174, $E$2:$E$767, E174) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9221,7 +9306,7 @@
         <v>650</v>
       </c>
       <c r="N175" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B175, $C$2:$C$767, C175, $D$2:$D$767, D175, $E$2:$E$767, E175) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O175" s="46" t="s">
@@ -9261,7 +9346,7 @@
         <v>117</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B176, $C$2:$C$767, C176, $D$2:$D$767, D176, $E$2:$E$767, E176) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9307,7 +9392,7 @@
         <v>250</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B177, $C$2:$C$767, C177, $D$2:$D$767, D177, $E$2:$E$767, E177) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9353,7 +9438,7 @@
         <v>300</v>
       </c>
       <c r="N178" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B178, $C$2:$C$767, C178, $D$2:$D$767, D178, $E$2:$E$767, E178) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9390,7 +9475,7 @@
       <c r="L179" s="18"/>
       <c r="M179" s="18"/>
       <c r="N179" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B179, $C$2:$C$767, C179, $D$2:$D$767, D179, $E$2:$E$767, E179) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O179" s="10"/>
@@ -9438,7 +9523,7 @@
         <v>250</v>
       </c>
       <c r="N180" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B180, $C$2:$C$767, C180, $D$2:$D$767, D180, $E$2:$E$767, E180) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O180" s="10"/>
@@ -9476,7 +9561,7 @@
         <v>156</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B181, $C$2:$C$767, C181, $D$2:$D$767, D181, $E$2:$E$767, E181) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9512,7 +9597,7 @@
         <v>118</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B182, $C$2:$C$767, C182, $D$2:$D$767, D182, $E$2:$E$767, E182) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O182" s="46" t="s">
@@ -9549,7 +9634,7 @@
       </c>
       <c r="J183" s="21"/>
       <c r="N183" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B183, $C$2:$C$767, C183, $D$2:$D$767, D183, $E$2:$E$767, E183) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9595,7 +9680,7 @@
         <v>300</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B184, $C$2:$C$767, C184, $D$2:$D$767, D184, $E$2:$E$767, E184) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O184" s="46" t="s">
@@ -9645,7 +9730,7 @@
         <v>501</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B185, $C$2:$C$767, C185, $D$2:$D$767, D185, $E$2:$E$767, E185) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O185" s="46" t="s">
@@ -9685,7 +9770,7 @@
         <v>117</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B186, $C$2:$C$767, C186, $D$2:$D$767, D186, $E$2:$E$767, E186) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9731,7 +9816,7 @@
         <v>700</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B187, $C$2:$C$767, C187, $D$2:$D$767, D187, $E$2:$E$767, E187) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O187" s="35"/>
@@ -9778,7 +9863,7 @@
         <v>250</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B188, $C$2:$C$767, C188, $D$2:$D$767, D188, $E$2:$E$767, E188) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P188" s="35"/>
@@ -9825,7 +9910,7 @@
         <v>1000</v>
       </c>
       <c r="N189" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B189, $C$2:$C$767, C189, $D$2:$D$767, D189, $E$2:$E$767, E189) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P189" s="35"/>
@@ -9872,7 +9957,7 @@
         <v>320</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B190, $C$2:$C$767, C190, $D$2:$D$767, D190, $E$2:$E$767, E190) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9918,7 +10003,7 @@
         <v>448</v>
       </c>
       <c r="N191" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B191, $C$2:$C$767, C191, $D$2:$D$767, D191, $E$2:$E$767, E191) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9954,7 +10039,7 @@
         <v>117</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B192, $C$2:$C$767, C192, $D$2:$D$767, D192, $E$2:$E$767, E192) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10000,7 +10085,7 @@
         <v>300</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B193, $C$2:$C$767, C193, $D$2:$D$767, D193, $E$2:$E$767, E193) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O193" s="10"/>
@@ -10036,7 +10121,7 @@
       </c>
       <c r="J194" s="40"/>
       <c r="N194" s="10" t="str">
-        <f t="shared" ref="N194:N257" si="10">IF(COUNTIFS( $B$2:$B$767, B194, $C$2:$C$767, C194, $D$2:$D$767, D194, $E$2:$E$767, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f>IF(COUNTIFS( $B$2:$B$767, B194, $C$2:$C$767, C194, $D$2:$D$767, D194, $E$2:$E$767, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10082,7 +10167,7 @@
         <v>300</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B195, $C$2:$C$767, C195, $D$2:$D$767, D195, $E$2:$E$767, E195) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P195" s="26"/>
@@ -10129,7 +10214,7 @@
         <v>400</v>
       </c>
       <c r="N196" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B196, $C$2:$C$767, C196, $D$2:$D$767, D196, $E$2:$E$767, E196) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10168,7 +10253,7 @@
         <v>144</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B197, $C$2:$C$767, C197, $D$2:$D$767, D197, $E$2:$E$767, E197) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10214,7 +10299,7 @@
         <v>140</v>
       </c>
       <c r="N198" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B198, $C$2:$C$767, C198, $D$2:$D$767, D198, $E$2:$E$767, E198) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O198" s="10"/>
@@ -10261,7 +10346,7 @@
         <v>300</v>
       </c>
       <c r="N199" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B199, $C$2:$C$767, C199, $D$2:$D$767, D199, $E$2:$E$767, E199) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O199" s="10"/>
@@ -10299,7 +10384,7 @@
         <v>117</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B200, $C$2:$C$767, C200, $D$2:$D$767, D200, $E$2:$E$767, E200) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10333,7 +10418,7 @@
       </c>
       <c r="J201" s="40"/>
       <c r="N201" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B201, $C$2:$C$767, C201, $D$2:$D$767, D201, $E$2:$E$767, E201) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P201" s="35"/>
@@ -10380,7 +10465,7 @@
         <v>300</v>
       </c>
       <c r="N202" s="34" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B202, $C$2:$C$767, C202, $D$2:$D$767, D202, $E$2:$E$767, E202) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O202" s="35"/>
@@ -10427,7 +10512,7 @@
         <v>253</v>
       </c>
       <c r="N203" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B203, $C$2:$C$767, C203, $D$2:$D$767, D203, $E$2:$E$767, E203) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O203" s="35"/>
@@ -10474,7 +10559,7 @@
         <v>260</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B204, $C$2:$C$767, C204, $D$2:$D$767, D204, $E$2:$E$767, E204) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10510,7 +10595,7 @@
         <v>198</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B205, $C$2:$C$767, C205, $D$2:$D$767, D205, $E$2:$E$767, E205) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10546,7 +10631,7 @@
         <v>117</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B206, $C$2:$C$767, C206, $D$2:$D$767, D206, $E$2:$E$767, E206) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10582,7 +10667,7 @@
         <v>118</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B207, $C$2:$C$767, C207, $D$2:$D$767, D207, $E$2:$E$767, E207) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10628,7 +10713,7 @@
         <v>800</v>
       </c>
       <c r="N208" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B208, $C$2:$C$767, C208, $D$2:$D$767, D208, $E$2:$E$767, E208) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10674,7 +10759,7 @@
         <v>300</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B209, $C$2:$C$767, C209, $D$2:$D$767, D209, $E$2:$E$767, E209) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10720,7 +10805,7 @@
         <v>188</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B210, $C$2:$C$767, C210, $D$2:$D$767, D210, $E$2:$E$767, E210) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P210" s="35"/>
@@ -10757,7 +10842,7 @@
         <v>55</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B211, $C$2:$C$767, C211, $D$2:$D$767, D211, $E$2:$E$767, E211) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10796,7 +10881,7 @@
         <v>145</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B212, $C$2:$C$767, C212, $D$2:$D$767, D212, $E$2:$E$767, E212) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10842,7 +10927,7 @@
         <v>940</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B213, $C$2:$C$767, C213, $D$2:$D$767, D213, $E$2:$E$767, E213) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10888,7 +10973,7 @@
         <v>450</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B214, $C$2:$C$767, C214, $D$2:$D$767, D214, $E$2:$E$767, E214) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10924,7 +11009,7 @@
         <v>118</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B215, $C$2:$C$767, C215, $D$2:$D$767, D215, $E$2:$E$767, E215) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10970,7 +11055,7 @@
         <v>300</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B216, $C$2:$C$767, C216, $D$2:$D$767, D216, $E$2:$E$767, E216) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11006,7 +11091,7 @@
         <v>118</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B217, $C$2:$C$767, C217, $D$2:$D$767, D217, $E$2:$E$767, E217) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11052,7 +11137,7 @@
         <v>370</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B218, $C$2:$C$767, C218, $D$2:$D$767, D218, $E$2:$E$767, E218) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P218" s="35"/>
@@ -11099,7 +11184,7 @@
         <v>527.5</v>
       </c>
       <c r="N219" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B219, $C$2:$C$767, C219, $D$2:$D$767, D219, $E$2:$E$767, E219) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O219" s="35"/>
@@ -11142,7 +11227,7 @@
       <c r="L220" s="33"/>
       <c r="M220" s="33"/>
       <c r="N220" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B220, $C$2:$C$767, C220, $D$2:$D$767, D220, $E$2:$E$767, E220) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O220" s="35"/>
@@ -11181,7 +11266,7 @@
       <c r="L221" s="18"/>
       <c r="M221" s="18"/>
       <c r="N221" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B221, $C$2:$C$767, C221, $D$2:$D$767, D221, $E$2:$E$767, E221) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O221" s="10"/>
@@ -11229,7 +11314,7 @@
         <v>1800</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B222, $C$2:$C$767, C222, $D$2:$D$767, D222, $E$2:$E$767, E222) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11263,7 +11348,7 @@
       </c>
       <c r="J223" s="40"/>
       <c r="N223" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B223, $C$2:$C$767, C223, $D$2:$D$767, D223, $E$2:$E$767, E223) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11309,7 +11394,7 @@
         <v>650</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B224, $C$2:$C$767, C224, $D$2:$D$767, D224, $E$2:$E$767, E224) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O224" s="35"/>
@@ -11356,7 +11441,7 @@
         <v>500</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B225, $C$2:$C$767, C225, $D$2:$D$767, D225, $E$2:$E$767, E225) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O225" s="46" t="s">
@@ -11398,7 +11483,7 @@
       <c r="L226" s="18"/>
       <c r="M226" s="18"/>
       <c r="N226" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B226, $C$2:$C$767, C226, $D$2:$D$767, D226, $E$2:$E$767, E226) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P226" s="10"/>
@@ -11435,7 +11520,7 @@
         <v>117</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B227, $C$2:$C$767, C227, $D$2:$D$767, D227, $E$2:$E$767, E227) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11469,7 +11554,7 @@
       </c>
       <c r="J228" s="40"/>
       <c r="N228" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B228, $C$2:$C$767, C228, $D$2:$D$767, D228, $E$2:$E$767, E228) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11503,7 +11588,7 @@
       </c>
       <c r="J229" s="40"/>
       <c r="N229" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B229, $C$2:$C$767, C229, $D$2:$D$767, D229, $E$2:$E$767, E229) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O229" s="35"/>
@@ -11540,7 +11625,7 @@
         <v>118</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B230, $C$2:$C$767, C230, $D$2:$D$767, D230, $E$2:$E$767, E230) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11574,7 +11659,7 @@
       </c>
       <c r="J231" s="40"/>
       <c r="N231" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B231, $C$2:$C$767, C231, $D$2:$D$767, D231, $E$2:$E$767, E231) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11620,7 +11705,7 @@
         <v>260</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B232, $C$2:$C$767, C232, $D$2:$D$767, D232, $E$2:$E$767, E232) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11654,7 +11739,7 @@
       </c>
       <c r="J233" s="40"/>
       <c r="N233" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B233, $C$2:$C$767, C233, $D$2:$D$767, D233, $E$2:$E$767, E233) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11700,7 +11785,7 @@
         <v>250</v>
       </c>
       <c r="N234" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B234, $C$2:$C$767, C234, $D$2:$D$767, D234, $E$2:$E$767, E234) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11746,7 +11831,7 @@
         <v>300</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B235, $C$2:$C$767, C235, $D$2:$D$767, D235, $E$2:$E$767, E235) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11782,7 +11867,7 @@
         <v>117</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B236, $C$2:$C$767, C236, $D$2:$D$767, D236, $E$2:$E$767, E236) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11816,7 +11901,7 @@
       </c>
       <c r="J237" s="40"/>
       <c r="N237" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B237, $C$2:$C$767, C237, $D$2:$D$767, D237, $E$2:$E$767, E237) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11862,7 +11947,7 @@
         <v>300</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B238, $C$2:$C$767, C238, $D$2:$D$767, D238, $E$2:$E$767, E238) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11898,7 +11983,7 @@
         <v>55</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B239, $C$2:$C$767, C239, $D$2:$D$767, D239, $E$2:$E$767, E239) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11934,7 +12019,7 @@
         <v>117</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B240, $C$2:$C$767, C240, $D$2:$D$767, D240, $E$2:$E$767, E240) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P240" s="35"/>
@@ -11981,7 +12066,7 @@
         <v>650</v>
       </c>
       <c r="N241" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B241, $C$2:$C$767, C241, $D$2:$D$767, D241, $E$2:$E$767, E241) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P241" s="35"/>
@@ -12018,7 +12103,7 @@
         <v>118</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B242, $C$2:$C$767, C242, $D$2:$D$767, D242, $E$2:$E$767, E242) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12054,7 +12139,7 @@
         <v>118</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B243, $C$2:$C$767, C243, $D$2:$D$767, D243, $E$2:$E$767, E243) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O243" s="35"/>
@@ -12091,7 +12176,7 @@
         <v>118</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B244, $C$2:$C$767, C244, $D$2:$D$767, D244, $E$2:$E$767, E244) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12128,7 +12213,7 @@
       <c r="L245" s="18"/>
       <c r="M245" s="18"/>
       <c r="N245" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B245, $C$2:$C$767, C245, $D$2:$D$767, D245, $E$2:$E$767, E245) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O245" s="10"/>
@@ -12166,7 +12251,7 @@
         <v>117</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B246, $C$2:$C$767, C246, $D$2:$D$767, D246, $E$2:$E$767, E246) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12212,7 +12297,7 @@
         <v>285</v>
       </c>
       <c r="N247" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B247, $C$2:$C$767, C247, $D$2:$D$767, D247, $E$2:$E$767, E247) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12258,7 +12343,7 @@
         <v>726</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B248, $C$2:$C$767, C248, $D$2:$D$767, D248, $E$2:$E$767, E248) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12297,7 +12382,7 @@
         <v>146</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B249, $C$2:$C$767, C249, $D$2:$D$767, D249, $E$2:$E$767, E249) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12331,7 +12416,7 @@
       </c>
       <c r="J250" s="40"/>
       <c r="N250" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B250, $C$2:$C$767, C250, $D$2:$D$767, D250, $E$2:$E$767, E250) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12365,7 +12450,7 @@
       </c>
       <c r="J251" s="40"/>
       <c r="N251" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B251, $C$2:$C$767, C251, $D$2:$D$767, D251, $E$2:$E$767, E251) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12399,7 +12484,7 @@
       </c>
       <c r="J252" s="40"/>
       <c r="N252" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B252, $C$2:$C$767, C252, $D$2:$D$767, D252, $E$2:$E$767, E252) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12445,7 +12530,7 @@
         <v>300</v>
       </c>
       <c r="N253" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B253, $C$2:$C$767, C253, $D$2:$D$767, D253, $E$2:$E$767, E253) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12491,7 +12576,7 @@
         <v>300</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B254, $C$2:$C$767, C254, $D$2:$D$767, D254, $E$2:$E$767, E254) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O254" s="10"/>
@@ -12527,7 +12612,7 @@
       </c>
       <c r="J255" s="40"/>
       <c r="N255" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B255, $C$2:$C$767, C255, $D$2:$D$767, D255, $E$2:$E$767, E255) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12573,7 +12658,7 @@
         <v>275</v>
       </c>
       <c r="N256" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B256, $C$2:$C$767, C256, $D$2:$D$767, D256, $E$2:$E$767, E256) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12607,7 +12692,7 @@
       </c>
       <c r="J257" s="40"/>
       <c r="N257" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B257, $C$2:$C$767, C257, $D$2:$D$767, D257, $E$2:$E$767, E257) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12643,7 +12728,7 @@
         <v>118</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f t="shared" ref="N258:N291" si="11">IF(COUNTIFS( $B$2:$B$767, B258, $C$2:$C$767, C258, $D$2:$D$767, D258, $E$2:$E$767, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f>IF(COUNTIFS( $B$2:$B$767, B258, $C$2:$C$767, C258, $D$2:$D$767, D258, $E$2:$E$767, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12677,7 +12762,7 @@
       </c>
       <c r="J259" s="40"/>
       <c r="N259" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B259, $C$2:$C$767, C259, $D$2:$D$767, D259, $E$2:$E$767, E259) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12713,7 +12798,7 @@
         <v>118</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B260, $C$2:$C$767, C260, $D$2:$D$767, D260, $E$2:$E$767, E260) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O260" s="35"/>
@@ -12750,7 +12835,7 @@
         <v>118</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B261, $C$2:$C$767, C261, $D$2:$D$767, D261, $E$2:$E$767, E261) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12796,7 +12881,7 @@
         <v>480</v>
       </c>
       <c r="N262" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B262, $C$2:$C$767, C262, $D$2:$D$767, D262, $E$2:$E$767, E262) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12830,7 +12915,7 @@
       </c>
       <c r="J263" s="40"/>
       <c r="N263" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B263, $C$2:$C$767, C263, $D$2:$D$767, D263, $E$2:$E$767, E263) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P263" s="35"/>
@@ -12865,7 +12950,7 @@
       </c>
       <c r="J264" s="40"/>
       <c r="N264" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B264, $C$2:$C$767, C264, $D$2:$D$767, D264, $E$2:$E$767, E264) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12901,7 +12986,7 @@
         <v>118</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B265, $C$2:$C$767, C265, $D$2:$D$767, D265, $E$2:$E$767, E265) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12947,7 +13032,7 @@
         <v>250</v>
       </c>
       <c r="N266" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B266, $C$2:$C$767, C266, $D$2:$D$767, D266, $E$2:$E$767, E266) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P266" s="35"/>
@@ -12984,7 +13069,7 @@
         <v>117</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B267, $C$2:$C$767, C267, $D$2:$D$767, D267, $E$2:$E$767, E267) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13020,7 +13105,7 @@
         <v>118</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B268, $C$2:$C$767, C268, $D$2:$D$767, D268, $E$2:$E$767, E268) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13054,7 +13139,7 @@
       </c>
       <c r="J269" s="40"/>
       <c r="N269" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B269, $C$2:$C$767, C269, $D$2:$D$767, D269, $E$2:$E$767, E269) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13100,7 +13185,7 @@
         <v>300</v>
       </c>
       <c r="N270" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B270, $C$2:$C$767, C270, $D$2:$D$767, D270, $E$2:$E$767, E270) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13134,7 +13219,7 @@
       </c>
       <c r="J271" s="40"/>
       <c r="N271" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B271, $C$2:$C$767, C271, $D$2:$D$767, D271, $E$2:$E$767, E271) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13168,7 +13253,7 @@
       </c>
       <c r="J272" s="40"/>
       <c r="N272" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B272, $C$2:$C$767, C272, $D$2:$D$767, D272, $E$2:$E$767, E272) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13202,7 +13287,7 @@
       </c>
       <c r="J273" s="40"/>
       <c r="N273" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B273, $C$2:$C$767, C273, $D$2:$D$767, D273, $E$2:$E$767, E273) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O273" s="35"/>
@@ -13237,7 +13322,7 @@
       </c>
       <c r="J274" s="40"/>
       <c r="N274" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B274, $C$2:$C$767, C274, $D$2:$D$767, D274, $E$2:$E$767, E274) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13273,7 +13358,7 @@
         <v>118</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B275, $C$2:$C$767, C275, $D$2:$D$767, D275, $E$2:$E$767, E275) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13307,7 +13392,7 @@
       </c>
       <c r="J276" s="40"/>
       <c r="N276" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B276, $C$2:$C$767, C276, $D$2:$D$767, D276, $E$2:$E$767, E276) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13353,7 +13438,7 @@
         <v>250</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B277, $C$2:$C$767, C277, $D$2:$D$767, D277, $E$2:$E$767, E277) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13387,7 +13472,7 @@
       </c>
       <c r="J278" s="40"/>
       <c r="N278" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B278, $C$2:$C$767, C278, $D$2:$D$767, D278, $E$2:$E$767, E278) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13421,7 +13506,7 @@
       </c>
       <c r="J279" s="40"/>
       <c r="N279" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B279, $C$2:$C$767, C279, $D$2:$D$767, D279, $E$2:$E$767, E279) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P279" s="35"/>
@@ -13456,7 +13541,7 @@
       </c>
       <c r="J280" s="40"/>
       <c r="N280" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B280, $C$2:$C$767, C280, $D$2:$D$767, D280, $E$2:$E$767, E280) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13490,7 +13575,7 @@
       </c>
       <c r="J281" s="40"/>
       <c r="N281" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B281, $C$2:$C$767, C281, $D$2:$D$767, D281, $E$2:$E$767, E281) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13524,7 +13609,7 @@
       </c>
       <c r="J282" s="40"/>
       <c r="N282" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B282, $C$2:$C$767, C282, $D$2:$D$767, D282, $E$2:$E$767, E282) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13560,7 +13645,7 @@
         <v>118</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B283, $C$2:$C$767, C283, $D$2:$D$767, D283, $E$2:$E$767, E283) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13596,7 +13681,7 @@
         <v>55</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B284, $C$2:$C$767, C284, $D$2:$D$767, D284, $E$2:$E$767, E284) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13632,7 +13717,7 @@
         <v>118</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B285, $C$2:$C$767, C285, $D$2:$D$767, D285, $E$2:$E$767, E285) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13666,7 +13751,7 @@
       </c>
       <c r="J286" s="40"/>
       <c r="N286" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B286, $C$2:$C$767, C286, $D$2:$D$767, D286, $E$2:$E$767, E286) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13712,7 +13797,7 @@
         <v>250</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B287, $C$2:$C$767, C287, $D$2:$D$767, D287, $E$2:$E$767, E287) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13746,7 +13831,7 @@
       </c>
       <c r="J288" s="40"/>
       <c r="N288" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B288, $C$2:$C$767, C288, $D$2:$D$767, D288, $E$2:$E$767, E288) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13780,7 +13865,7 @@
       </c>
       <c r="J289" s="40"/>
       <c r="N289" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B289, $C$2:$C$767, C289, $D$2:$D$767, D289, $E$2:$E$767, E289) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13814,7 +13899,7 @@
       </c>
       <c r="J290" s="40"/>
       <c r="N290" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B290, $C$2:$C$767, C290, $D$2:$D$767, D290, $E$2:$E$767, E290) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O290" s="35"/>
@@ -13849,29 +13934,19 @@
       </c>
       <c r="J291" s="40"/>
       <c r="N291" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(COUNTIFS( $B$2:$B$767, B291, $C$2:$C$767, C291, $D$2:$D$767, D291, $E$2:$E$767, E291) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P291" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="2">
       <filters>
-        <filter val="GRSEEQ"/>
+        <filter val="B"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="S"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="14">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P291">
-      <sortCondition ref="F1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P86">
+      <sortCondition descending="1" ref="F1:F291"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_11sep26_Fri.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_11sep26_Fri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14B6B1A-CA60-47B6-8DC2-D70C476504AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8185570C-B780-4695-B0A8-4022A1306DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1103,7 +1103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1278,28 +1278,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="22" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1725,7 +1703,7 @@
         <v>34175</v>
       </c>
       <c r="N2" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B2, $C$2:$C$767, C2, $D$2:$D$767, D2, $E$2:$E$767, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$767, B2, $C$2:$C$767, C2, $D$2:$D$767, D2, $E$2:$E$767, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -1766,7 +1744,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B3, $C$2:$C$767, C3, $D$2:$D$767, D3, $E$2:$E$767, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -1807,7 +1785,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B4, $C$2:$C$767, C4, $D$2:$D$767, D4, $E$2:$E$767, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -1848,7 +1826,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B5, $C$2:$C$767, C5, $D$2:$D$767, D5, $E$2:$E$767, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -1889,7 +1867,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B6, $C$2:$C$767, C6, $D$2:$D$767, D6, $E$2:$E$767, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -1930,7 +1908,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B7, $C$2:$C$767, C7, $D$2:$D$767, D7, $E$2:$E$767, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -1969,7 +1947,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B8, $C$2:$C$767, C8, $D$2:$D$767, D8, $E$2:$E$767, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="26"/>
@@ -2017,7 +1995,7 @@
         <v>500</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B9, $C$2:$C$767, C9, $D$2:$D$767, D9, $E$2:$E$767, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -2058,7 +2036,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B10, $C$2:$C$767, C10, $D$2:$D$767, D10, $E$2:$E$767, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10"/>
@@ -2097,7 +2075,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B11, $C$2:$C$767, C11, $D$2:$D$767, D11, $E$2:$E$767, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="19"/>
@@ -2138,7 +2116,7 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B12, $C$2:$C$767, C12, $D$2:$D$767, D12, $E$2:$E$767, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P12" s="34"/>
@@ -2178,7 +2156,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B13, $C$2:$C$767, C13, $D$2:$D$767, D13, $E$2:$E$767, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
@@ -2219,7 +2197,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B14, $C$2:$C$767, C14, $D$2:$D$767, D14, $E$2:$E$767, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="10"/>
@@ -2267,7 +2245,7 @@
         <v>300</v>
       </c>
       <c r="N15" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B15, $C$2:$C$767, C15, $D$2:$D$767, D15, $E$2:$E$767, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="10"/>
@@ -2308,7 +2286,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B16, $C$2:$C$767, C16, $D$2:$D$767, D16, $E$2:$E$767, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="10"/>
@@ -2347,7 +2325,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B17, $C$2:$C$767, C17, $D$2:$D$767, D17, $E$2:$E$767, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="10"/>
@@ -2388,7 +2366,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B18, $C$2:$C$767, C18, $D$2:$D$767, D18, $E$2:$E$767, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P18" s="10"/>
@@ -2428,7 +2406,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B19, $C$2:$C$767, C19, $D$2:$D$767, D19, $E$2:$E$767, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="10"/>
@@ -2476,7 +2454,7 @@
         <v>300</v>
       </c>
       <c r="N20" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B20, $C$2:$C$767, C20, $D$2:$D$767, D20, $E$2:$E$767, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2522,7 +2500,7 @@
         <v>525</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B21, $C$2:$C$767, C21, $D$2:$D$767, D21, $E$2:$E$767, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="10"/>
@@ -2561,7 +2539,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B22, $C$2:$C$767, C22, $D$2:$D$767, D22, $E$2:$E$767, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22" s="10"/>
@@ -2602,7 +2580,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B23, $C$2:$C$767, C23, $D$2:$D$767, D23, $E$2:$E$767, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23" s="10"/>
@@ -2649,7 +2627,7 @@
         <v>300</v>
       </c>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B24, $C$2:$C$767, C24, $D$2:$D$767, D24, $E$2:$E$767, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24" s="10"/>
@@ -2690,7 +2668,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B25, $C$2:$C$767, C25, $D$2:$D$767, D25, $E$2:$E$767, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25" s="10"/>
@@ -2731,7 +2709,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B26, $C$2:$C$767, C26, $D$2:$D$767, D26, $E$2:$E$767, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2770,7 +2748,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B27, $C$2:$C$767, C27, $D$2:$D$767, D27, $E$2:$E$767, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="34"/>
@@ -2810,7 +2788,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B28, $C$2:$C$767, C28, $D$2:$D$767, D28, $E$2:$E$767, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28" s="10"/>
@@ -2851,7 +2829,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B29, $C$2:$C$767, C29, $D$2:$D$767, D29, $E$2:$E$767, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2898,7 +2876,7 @@
         <v>650</v>
       </c>
       <c r="N30" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B30, $C$2:$C$767, C30, $D$2:$D$767, D30, $E$2:$E$767, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P30" s="10"/>
@@ -2938,7 +2916,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B31, $C$2:$C$767, C31, $D$2:$D$767, D31, $E$2:$E$767, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2977,7 +2955,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B32, $C$2:$C$767, C32, $D$2:$D$767, D32, $E$2:$E$767, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3016,7 +2994,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B33, $C$2:$C$767, C33, $D$2:$D$767, D33, $E$2:$E$767, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3055,7 +3033,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B34, $C$2:$C$767, C34, $D$2:$D$767, D34, $E$2:$E$767, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3092,7 +3070,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B35, $C$2:$C$767, C35, $D$2:$D$767, D35, $E$2:$E$767, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P35" s="10"/>
@@ -3139,7 +3117,7 @@
         <v>516</v>
       </c>
       <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B36, $C$2:$C$767, C36, $D$2:$D$767, D36, $E$2:$E$767, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36" s="10"/>
@@ -3187,7 +3165,7 @@
         <v>300</v>
       </c>
       <c r="N37" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B37, $C$2:$C$767, C37, $D$2:$D$767, D37, $E$2:$E$767, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37" s="10"/>
@@ -3226,7 +3204,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B38, $C$2:$C$767, C38, $D$2:$D$767, D38, $E$2:$E$767, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P38" s="10"/>
@@ -3266,7 +3244,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B39, $C$2:$C$767, C39, $D$2:$D$767, D39, $E$2:$E$767, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39" s="10"/>
@@ -3307,7 +3285,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B40, $C$2:$C$767, C40, $D$2:$D$767, D40, $E$2:$E$767, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3344,7 +3322,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B41, $C$2:$C$767, C41, $D$2:$D$767, D41, $E$2:$E$767, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -3392,7 +3370,7 @@
         <v>460</v>
       </c>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B42, $C$2:$C$767, C42, $D$2:$D$767, D42, $E$2:$E$767, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -3430,7 +3408,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B43, $C$2:$C$767, C43, $D$2:$D$767, D43, $E$2:$E$767, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P43"/>
@@ -3470,7 +3448,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B44, $C$2:$C$767, C44, $D$2:$D$767, D44, $E$2:$E$767, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -3509,7 +3487,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B45, $C$2:$C$767, C45, $D$2:$D$767, D45, $E$2:$E$767, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -3557,7 +3535,7 @@
         <v>300</v>
       </c>
       <c r="N46" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B46, $C$2:$C$767, C46, $D$2:$D$767, D46, $E$2:$E$767, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -3598,7 +3576,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B47, $C$2:$C$767, C47, $D$2:$D$767, D47, $E$2:$E$767, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -3639,7 +3617,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B48, $C$2:$C$767, C48, $D$2:$D$767, D48, $E$2:$E$767, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -3680,7 +3658,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B49, $C$2:$C$767, C49, $D$2:$D$767, D49, $E$2:$E$767, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49"/>
@@ -3721,7 +3699,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B50, $C$2:$C$767, C50, $D$2:$D$767, D50, $E$2:$E$767, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P50"/>
@@ -3769,7 +3747,7 @@
         <v>540</v>
       </c>
       <c r="N51" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B51, $C$2:$C$767, C51, $D$2:$D$767, D51, $E$2:$E$767, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -3808,7 +3786,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B52, $C$2:$C$767, C52, $D$2:$D$767, D52, $E$2:$E$767, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -3850,7 +3828,7 @@
         <v>3156</v>
       </c>
       <c r="N53" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B53, $C$2:$C$767, C53, $D$2:$D$767, D53, $E$2:$E$767, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P53" s="19"/>
@@ -3888,7 +3866,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B54, $C$2:$C$767, C54, $D$2:$D$767, D54, $E$2:$E$767, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -3927,7 +3905,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B55, $C$2:$C$767, C55, $D$2:$D$767, D55, $E$2:$E$767, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -3966,7 +3944,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B56, $C$2:$C$767, C56, $D$2:$D$767, D56, $E$2:$E$767, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -4009,7 +3987,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B57, $C$2:$C$767, C57, $D$2:$D$767, D57, $E$2:$E$767, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -4050,7 +4028,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B58, $C$2:$C$767, C58, $D$2:$D$767, D58, $E$2:$E$767, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -4091,7 +4069,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B59, $C$2:$C$767, C59, $D$2:$D$767, D59, $E$2:$E$767, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
@@ -4130,7 +4108,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B60, $C$2:$C$767, C60, $D$2:$D$767, D60, $E$2:$E$767, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60"/>
@@ -4169,7 +4147,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B61, $C$2:$C$767, C61, $D$2:$D$767, D61, $E$2:$E$767, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
@@ -4217,7 +4195,7 @@
         <v>300</v>
       </c>
       <c r="N62" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B62, $C$2:$C$767, C62, $D$2:$D$767, D62, $E$2:$E$767, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62"/>
@@ -4258,7 +4236,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B63, $C$2:$C$767, C63, $D$2:$D$767, D63, $E$2:$E$767, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
@@ -4297,7 +4275,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B64, $C$2:$C$767, C64, $D$2:$D$767, D64, $E$2:$E$767, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -4336,7 +4314,7 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B65, $C$2:$C$767, C65, $D$2:$D$767, D65, $E$2:$E$767, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65"/>
@@ -4384,7 +4362,7 @@
         <v>442</v>
       </c>
       <c r="N66" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B66, $C$2:$C$767, C66, $D$2:$D$767, D66, $E$2:$E$767, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$767, B66, $C$2:$C$767, C66, $D$2:$D$767, D66, $E$2:$E$767, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
@@ -4423,7 +4401,7 @@
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B67, $C$2:$C$767, C67, $D$2:$D$767, D67, $E$2:$E$767, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67"/>
@@ -4464,7 +4442,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B68, $C$2:$C$767, C68, $D$2:$D$767, D68, $E$2:$E$767, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68"/>
@@ -4503,7 +4481,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B69, $C$2:$C$767, C69, $D$2:$D$767, D69, $E$2:$E$767, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -4542,7 +4520,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B70, $C$2:$C$767, C70, $D$2:$D$767, D70, $E$2:$E$767, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -4581,7 +4559,7 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B71, $C$2:$C$767, C71, $D$2:$D$767, D71, $E$2:$E$767, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71"/>
@@ -4620,7 +4598,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B72, $C$2:$C$767, C72, $D$2:$D$767, D72, $E$2:$E$767, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
@@ -4659,7 +4637,7 @@
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B73, $C$2:$C$767, C73, $D$2:$D$767, D73, $E$2:$E$767, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73"/>
@@ -4698,7 +4676,7 @@
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B74, $C$2:$C$767, C74, $D$2:$D$767, D74, $E$2:$E$767, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74"/>
@@ -4737,7 +4715,7 @@
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B75, $C$2:$C$767, C75, $D$2:$D$767, D75, $E$2:$E$767, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75"/>
@@ -4776,7 +4754,7 @@
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B76, $C$2:$C$767, C76, $D$2:$D$767, D76, $E$2:$E$767, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76"/>
@@ -4815,7 +4793,7 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B77, $C$2:$C$767, C77, $D$2:$D$767, D77, $E$2:$E$767, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77"/>
@@ -4854,7 +4832,7 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B78, $C$2:$C$767, C78, $D$2:$D$767, D78, $E$2:$E$767, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78"/>
@@ -4902,7 +4880,7 @@
         <v>26810</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B79, $C$2:$C$767, C79, $D$2:$D$767, D79, $E$2:$E$767, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="10"/>
@@ -4941,7 +4919,7 @@
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B80, $C$2:$C$767, C80, $D$2:$D$767, D80, $E$2:$E$767, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80"/>
@@ -4989,7 +4967,7 @@
         <v>275</v>
       </c>
       <c r="N81" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B81, $C$2:$C$767, C81, $D$2:$D$767, D81, $E$2:$E$767, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O81" s="46" t="s">
@@ -5039,7 +5017,7 @@
         <v>225</v>
       </c>
       <c r="N82" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B82, $C$2:$C$767, C82, $D$2:$D$767, D82, $E$2:$E$767, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O82" s="46" t="s">
@@ -5089,7 +5067,7 @@
         <v>300</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B83, $C$2:$C$767, C83, $D$2:$D$767, D83, $E$2:$E$767, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5135,7 +5113,7 @@
         <v>1246</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B84, $C$2:$C$767, C84, $D$2:$D$767, D84, $E$2:$E$767, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5181,7 +5159,7 @@
         <v>26710</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B85, $C$2:$C$767, C85, $D$2:$D$767, D85, $E$2:$E$767, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="46" t="s">
@@ -5223,7 +5201,7 @@
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
       <c r="N86" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B86, $C$2:$C$767, C86, $D$2:$D$767, D86, $E$2:$E$767, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O86"/>
@@ -5264,7 +5242,7 @@
       <c r="L87" s="18"/>
       <c r="M87" s="18"/>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B87, $C$2:$C$767, C87, $D$2:$D$767, D87, $E$2:$E$767, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="46" t="s">
@@ -5309,11 +5287,11 @@
         <v>19730.5</v>
       </c>
       <c r="M88" s="33">
-        <f>ABS((D88*E88)-L88)</f>
+        <f t="shared" ref="M88:M102" si="2">ABS((D88*E88)-L88)</f>
         <v>504.5</v>
       </c>
       <c r="N88" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B88, $C$2:$C$767, C88, $D$2:$D$767, D88, $E$2:$E$767, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O88" s="46" t="s">
@@ -5359,11 +5337,11 @@
         <v>19690</v>
       </c>
       <c r="M89" s="33">
-        <f>ABS((D89*E89)-L89)</f>
+        <f t="shared" si="2"/>
         <v>545</v>
       </c>
       <c r="N89" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B89, $C$2:$C$767, C89, $D$2:$D$767, D89, $E$2:$E$767, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O89" s="46" t="s">
@@ -5409,63 +5387,63 @@
         <v>35880</v>
       </c>
       <c r="M90" s="18">
-        <f>ABS((D90*E90)-L90)</f>
+        <f t="shared" si="2"/>
         <v>26610</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B90, $C$2:$C$767, C90, $D$2:$D$767, D90, $E$2:$E$767, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="10"/>
       <c r="P90" s="10"/>
     </row>
-    <row r="91" spans="1:16" s="67" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="61">
+    <row r="91" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="3">
         <v>46265.375694444447</v>
       </c>
-      <c r="B91" s="62" t="s">
+      <c r="B91" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C91" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91" s="63">
+      <c r="C91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="4">
         <v>5</v>
       </c>
-      <c r="E91" s="63">
+      <c r="E91" s="4">
         <v>1236</v>
       </c>
-      <c r="F91" s="63">
+      <c r="F91" s="4">
         <v>3.7086759520000001</v>
       </c>
-      <c r="G91" s="64" t="s">
+      <c r="G91" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H91" s="65">
+      <c r="H91" s="5">
         <v>1191.8</v>
       </c>
-      <c r="I91" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="66" t="s">
+      <c r="I91" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="K91" s="66" t="s">
+      <c r="K91" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="L91" s="66">
+      <c r="L91" s="18">
         <v>5905</v>
       </c>
-      <c r="M91" s="66">
-        <f>ABS((D91*E91)-L91)</f>
+      <c r="M91" s="18">
+        <f t="shared" si="2"/>
         <v>275</v>
       </c>
-      <c r="N91" s="67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B91, $C$2:$C$767, C91, $D$2:$D$767, D91, $E$2:$E$767, E91) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O91" s="68"/>
-      <c r="P91" s="68"/>
+      <c r="N91" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O91" s="10"/>
+      <c r="P91" s="10"/>
     </row>
     <row r="92" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="36">
@@ -5505,11 +5483,11 @@
         <v>3560</v>
       </c>
       <c r="M92" s="33">
-        <f>ABS((D92*E92)-L92)</f>
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="N92" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B92, $C$2:$C$767, C92, $D$2:$D$767, D92, $E$2:$E$767, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O92" s="46" t="s">
@@ -5554,11 +5532,11 @@
         <v>3510</v>
       </c>
       <c r="M93" s="33">
-        <f>ABS((D93*E93)-L93)</f>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="N93" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B93, $C$2:$C$767, C93, $D$2:$D$767, D93, $E$2:$E$767, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O93" s="46" t="s">
@@ -5604,11 +5582,11 @@
         <v>8700</v>
       </c>
       <c r="M94" s="18">
-        <f>ABS((D94*E94)-L94)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B94, $C$2:$C$767, C94, $D$2:$D$767, D94, $E$2:$E$767, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94" s="10"/>
@@ -5652,11 +5630,11 @@
         <v>8220</v>
       </c>
       <c r="M95" s="18">
-        <f>ABS((D95*E95)-L95)</f>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B95, $C$2:$C$767, C95, $D$2:$D$767, D95, $E$2:$E$767, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95" s="46" t="s">
@@ -5701,11 +5679,11 @@
         <v>20010</v>
       </c>
       <c r="M96" s="18">
-        <f>ABS((D96*E96)-L96)</f>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="N96" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B96, $C$2:$C$767, C96, $D$2:$D$767, D96, $E$2:$E$767, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O96" s="10"/>
@@ -5749,11 +5727,11 @@
         <v>9170</v>
       </c>
       <c r="M97" s="33">
-        <f>ABS((D97*E97)-L97)</f>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B97, $C$2:$C$767, C97, $D$2:$D$767, D97, $E$2:$E$767, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O97" s="10"/>
@@ -5797,11 +5775,11 @@
         <v>8480</v>
       </c>
       <c r="M98" s="27">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" si="2"/>
         <v>280</v>
       </c>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B98, $C$2:$C$767, C98, $D$2:$D$767, D98, $E$2:$E$767, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="46" t="s">
@@ -5847,11 +5825,11 @@
         <v>73800</v>
       </c>
       <c r="M99" s="18">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="2"/>
         <v>48320</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B99, $C$2:$C$767, C99, $D$2:$D$767, D99, $E$2:$E$767, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="46" t="s">
@@ -5897,11 +5875,11 @@
         <v>20260</v>
       </c>
       <c r="M100" s="18">
-        <f>ABS((D100*E100)-L100)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N100" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B100, $C$2:$C$767, C100, $D$2:$D$767, D100, $E$2:$E$767, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O100"/>
@@ -5945,11 +5923,11 @@
         <v>9902</v>
       </c>
       <c r="M101" s="18">
-        <f>ABS((D101*E101)-L101)</f>
+        <f t="shared" si="2"/>
         <v>646</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B101, $C$2:$C$767, C101, $D$2:$D$767, D101, $E$2:$E$767, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="46" t="s">
@@ -5995,11 +5973,11 @@
         <v>35880</v>
       </c>
       <c r="M102" s="18">
-        <f>ABS((D102*E102)-L102)</f>
+        <f t="shared" si="2"/>
         <v>26460</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B102, $C$2:$C$767, C102, $D$2:$D$767, D102, $E$2:$E$767, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="10"/>
@@ -6035,7 +6013,7 @@
       </c>
       <c r="J103" s="40"/>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B103, $C$2:$C$767, C103, $D$2:$D$767, D103, $E$2:$E$767, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6069,7 +6047,7 @@
       </c>
       <c r="J104" s="40"/>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B104, $C$2:$C$767, C104, $D$2:$D$767, D104, $E$2:$E$767, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="46" t="s">
@@ -6119,7 +6097,7 @@
         <v>300</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B105, $C$2:$C$767, C105, $D$2:$D$767, D105, $E$2:$E$767, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105"/>
@@ -6167,7 +6145,7 @@
         <v>300.00000000000182</v>
       </c>
       <c r="N106" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B106, $C$2:$C$767, C106, $D$2:$D$767, D106, $E$2:$E$767, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="46" t="s">
@@ -6217,7 +6195,7 @@
         <v>274</v>
       </c>
       <c r="N107" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B107, $C$2:$C$767, C107, $D$2:$D$767, D107, $E$2:$E$767, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="46" t="s">
@@ -6267,7 +6245,7 @@
         <v>150</v>
       </c>
       <c r="N108" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B108, $C$2:$C$767, C108, $D$2:$D$767, D108, $E$2:$E$767, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -6313,7 +6291,7 @@
         <v>250</v>
       </c>
       <c r="N109" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B109, $C$2:$C$767, C109, $D$2:$D$767, D109, $E$2:$E$767, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O109" s="10"/>
@@ -6349,7 +6327,7 @@
       </c>
       <c r="J110" s="40"/>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B110, $C$2:$C$767, C110, $D$2:$D$767, D110, $E$2:$E$767, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6391,11 +6369,11 @@
         <v>20070</v>
       </c>
       <c r="M111" s="18">
-        <f>ABS((D111*E111)-L111)</f>
+        <f t="shared" ref="M111:M123" si="3">ABS((D111*E111)-L111)</f>
         <v>810</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B111, $C$2:$C$767, C111, $D$2:$D$767, D111, $E$2:$E$767, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6437,11 +6415,11 @@
         <v>15075</v>
       </c>
       <c r="M112" s="18">
-        <f>ABS((D112*E112)-L112)</f>
+        <f t="shared" si="3"/>
         <v>645</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B112, $C$2:$C$767, C112, $D$2:$D$767, D112, $E$2:$E$767, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O112" s="46" t="s">
@@ -6486,11 +6464,11 @@
         <v>9170</v>
       </c>
       <c r="M113" s="33">
-        <f>ABS((D113*E113)-L113)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B113, $C$2:$C$767, C113, $D$2:$D$767, D113, $E$2:$E$767, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O113" s="10"/>
@@ -6534,11 +6512,11 @@
         <v>8420</v>
       </c>
       <c r="M114" s="18">
-        <f>ABS((D114*E114)-L114)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B114, $C$2:$C$767, C114, $D$2:$D$767, D114, $E$2:$E$767, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6580,11 +6558,11 @@
         <v>11320</v>
       </c>
       <c r="M115" s="18">
-        <f>ABS((D115*E115)-L115)</f>
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B115, $C$2:$C$767, C115, $D$2:$D$767, D115, $E$2:$E$767, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6626,11 +6604,11 @@
         <v>3005</v>
       </c>
       <c r="M116" s="18">
-        <f>ABS((D116*E116)-L116)</f>
+        <f t="shared" si="3"/>
         <v>240</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B116, $C$2:$C$767, C116, $D$2:$D$767, D116, $E$2:$E$767, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="10"/>
@@ -6674,11 +6652,11 @@
         <v>14100</v>
       </c>
       <c r="M117" s="18">
-        <f>ABS((D117*E117)-L117)</f>
+        <f t="shared" si="3"/>
         <v>500</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B117, $C$2:$C$767, C117, $D$2:$D$767, D117, $E$2:$E$767, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="10"/>
@@ -6722,11 +6700,11 @@
         <v>73800</v>
       </c>
       <c r="M118" s="18">
-        <f>ABS((D118*E118)-L118)</f>
+        <f t="shared" si="3"/>
         <v>47900</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B118, $C$2:$C$767, C118, $D$2:$D$767, D118, $E$2:$E$767, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="46" t="s">
@@ -6771,11 +6749,11 @@
         <v>18960</v>
       </c>
       <c r="M119" s="18">
-        <f>ABS((D119*E119)-L119)</f>
+        <f t="shared" si="3"/>
         <v>816</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B119, $C$2:$C$767, C119, $D$2:$D$767, D119, $E$2:$E$767, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6817,11 +6795,11 @@
         <v>3300</v>
       </c>
       <c r="M120" s="18">
-        <f>ABS((D120*E120)-L120)</f>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B120, $C$2:$C$767, C120, $D$2:$D$767, D120, $E$2:$E$767, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6863,11 +6841,11 @@
         <v>25300</v>
       </c>
       <c r="M121" s="18">
-        <f>ABS((D121*E121)-L121)</f>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B121, $C$2:$C$767, C121, $D$2:$D$767, D121, $E$2:$E$767, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="46" t="s">
@@ -6912,11 +6890,11 @@
         <v>12480</v>
       </c>
       <c r="M122" s="18">
-        <f>ABS((D122*E122)-L122)</f>
+        <f t="shared" si="3"/>
         <v>495</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B122, $C$2:$C$767, C122, $D$2:$D$767, D122, $E$2:$E$767, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="46" t="s">
@@ -6961,11 +6939,11 @@
         <v>32200</v>
       </c>
       <c r="M123" s="18">
-        <f>ABS((D123*E123)-L123)</f>
+        <f t="shared" si="3"/>
         <v>1200</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B123, $C$2:$C$767, C123, $D$2:$D$767, D123, $E$2:$E$767, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6999,7 +6977,7 @@
       </c>
       <c r="J124" s="40"/>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B124, $C$2:$C$767, C124, $D$2:$D$767, D124, $E$2:$E$767, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="25"/>
@@ -7042,11 +7020,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M125" s="33">
-        <f>ABS((D125*E125)-L125)</f>
+        <f t="shared" ref="M125:M130" si="4">ABS((D125*E125)-L125)</f>
         <v>710.99999999999636</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B125, $C$2:$C$767, C125, $D$2:$D$767, D125, $E$2:$E$767, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O125" s="46" t="s">
@@ -7092,11 +7070,11 @@
         <v>8570</v>
       </c>
       <c r="M126" s="33">
-        <f>ABS((D126*E126)-L126)</f>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B126, $C$2:$C$767, C126, $D$2:$D$767, D126, $E$2:$E$767, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="46" t="s">
@@ -7141,11 +7119,11 @@
         <v>9270</v>
       </c>
       <c r="M127" s="18">
-        <f>ABS((D127*E127)-L127)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B127, $C$2:$C$767, C127, $D$2:$D$767, D127, $E$2:$E$767, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P127" s="19"/>
@@ -7188,11 +7166,11 @@
         <v>10300</v>
       </c>
       <c r="M128" s="18">
-        <f>ABS((D128*E128)-L128)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B128, $C$2:$C$767, C128, $D$2:$D$767, D128, $E$2:$E$767, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
@@ -7236,11 +7214,11 @@
         <v>14200</v>
       </c>
       <c r="M129" s="18">
-        <f>ABS((D129*E129)-L129)</f>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B129, $C$2:$C$767, C129, $D$2:$D$767, D129, $E$2:$E$767, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7282,11 +7260,11 @@
         <v>25780</v>
       </c>
       <c r="M130" s="18">
-        <f>ABS((D130*E130)-L130)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N130" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B130, $C$2:$C$767, C130, $D$2:$D$767, D130, $E$2:$E$767, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="5">IF(COUNTIFS( $B$2:$B$767, B130, $C$2:$C$767, C130, $D$2:$D$767, D130, $E$2:$E$767, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="46" t="s">
@@ -7326,7 +7304,7 @@
         <v>117</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B131, $C$2:$C$767, C131, $D$2:$D$767, D131, $E$2:$E$767, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7372,7 +7350,7 @@
         <v>651</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B132, $C$2:$C$767, C132, $D$2:$D$767, D132, $E$2:$E$767, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7418,7 +7396,7 @@
         <v>300</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B133, $C$2:$C$767, C133, $D$2:$D$767, D133, $E$2:$E$767, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7464,7 +7442,7 @@
         <v>650</v>
       </c>
       <c r="N134" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B134, $C$2:$C$767, C134, $D$2:$D$767, D134, $E$2:$E$767, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O134"/>
@@ -7512,7 +7490,7 @@
         <v>270</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B135, $C$2:$C$767, C135, $D$2:$D$767, D135, $E$2:$E$767, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O135" s="47" t="s">
@@ -7549,7 +7527,7 @@
       </c>
       <c r="J136" s="40"/>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B136, $C$2:$C$767, C136, $D$2:$D$767, D136, $E$2:$E$767, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7595,7 +7573,7 @@
         <v>880</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B137, $C$2:$C$767, C137, $D$2:$D$767, D137, $E$2:$E$767, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="46" t="s">
@@ -7634,7 +7612,7 @@
         <v>118</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B138, $C$2:$C$767, C138, $D$2:$D$767, D138, $E$2:$E$767, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7676,11 +7654,11 @@
         <v>4080</v>
       </c>
       <c r="M139" s="18">
-        <f>ABS((D139*E139)-L139)</f>
+        <f t="shared" ref="M139:M144" si="6">ABS((D139*E139)-L139)</f>
         <v>300</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B139, $C$2:$C$767, C139, $D$2:$D$767, D139, $E$2:$E$767, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7722,11 +7700,11 @@
         <v>5370</v>
       </c>
       <c r="M140" s="18">
-        <f>ABS((D140*E140)-L140)</f>
+        <f t="shared" si="6"/>
         <v>320</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B140, $C$2:$C$767, C140, $D$2:$D$767, D140, $E$2:$E$767, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7768,11 +7746,11 @@
         <v>16580</v>
       </c>
       <c r="M141" s="54">
-        <f>ABS((D141*E141)-L141)</f>
+        <f t="shared" si="6"/>
         <v>750</v>
       </c>
       <c r="N141" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B141, $C$2:$C$767, C141, $D$2:$D$767, D141, $E$2:$E$767, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="25"/>
@@ -7818,11 +7796,11 @@
         <v>10410</v>
       </c>
       <c r="M142" s="18">
-        <f>ABS((D142*E142)-L142)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B142, $C$2:$C$767, C142, $D$2:$D$767, D142, $E$2:$E$767, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="35"/>
@@ -7865,11 +7843,11 @@
         <v>73800</v>
       </c>
       <c r="M143" s="18">
-        <f>ABS((D143*E143)-L143)</f>
+        <f t="shared" si="6"/>
         <v>47480</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B143, $C$2:$C$767, C143, $D$2:$D$767, D143, $E$2:$E$767, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7911,11 +7889,11 @@
         <v>12510</v>
       </c>
       <c r="M144" s="18">
-        <f>ABS((D144*E144)-L144)</f>
+        <f t="shared" si="6"/>
         <v>290</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B144, $C$2:$C$767, C144, $D$2:$D$767, D144, $E$2:$E$767, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7949,7 +7927,7 @@
       </c>
       <c r="J145" s="40"/>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B145, $C$2:$C$767, C145, $D$2:$D$767, D145, $E$2:$E$767, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7991,11 +7969,11 @@
         <v>32900</v>
       </c>
       <c r="M146" s="33">
-        <f>ABS((D146*E146)-L146)</f>
+        <f t="shared" ref="M146:M158" si="7">ABS((D146*E146)-L146)</f>
         <v>1000</v>
       </c>
       <c r="N146" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B146, $C$2:$C$767, C146, $D$2:$D$767, D146, $E$2:$E$767, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O146" s="26"/>
@@ -8038,11 +8016,11 @@
         <v>33200</v>
       </c>
       <c r="M147" s="33">
-        <f>ABS((D147*E147)-L147)</f>
+        <f t="shared" si="7"/>
         <v>700</v>
       </c>
       <c r="N147" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B147, $C$2:$C$767, C147, $D$2:$D$767, D147, $E$2:$E$767, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8084,11 +8062,11 @@
         <v>26020</v>
       </c>
       <c r="M148" s="18">
-        <f>ABS((D148*E148)-L148)</f>
+        <f t="shared" si="7"/>
         <v>340</v>
       </c>
       <c r="N148" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B148, $C$2:$C$767, C148, $D$2:$D$767, D148, $E$2:$E$767, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="10"/>
@@ -8132,11 +8110,11 @@
         <v>11660</v>
       </c>
       <c r="M149" s="18">
-        <f>ABS((D149*E149)-L149)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B149, $C$2:$C$767, C149, $D$2:$D$767, D149, $E$2:$E$767, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="46" t="s">
@@ -8181,11 +8159,11 @@
         <v>14400</v>
       </c>
       <c r="M150" s="18">
-        <f>ABS((D150*E150)-L150)</f>
+        <f t="shared" si="7"/>
         <v>500</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B150, $C$2:$C$767, C150, $D$2:$D$767, D150, $E$2:$E$767, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8227,11 +8205,11 @@
         <v>5180</v>
       </c>
       <c r="M151" s="27">
-        <f>ABS((D151*E151)-L151)</f>
+        <f t="shared" si="7"/>
         <v>268</v>
       </c>
       <c r="N151" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B151, $C$2:$C$767, C151, $D$2:$D$767, D151, $E$2:$E$767, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8273,11 +8251,11 @@
         <v>18140</v>
       </c>
       <c r="M152" s="27">
-        <f>ABS((D152*E152)-L152)</f>
+        <f t="shared" si="7"/>
         <v>650</v>
       </c>
       <c r="N152" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B152, $C$2:$C$767, C152, $D$2:$D$767, D152, $E$2:$E$767, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="46" t="s">
@@ -8322,11 +8300,11 @@
         <v>26180</v>
       </c>
       <c r="M153" s="18">
-        <f>ABS((D153*E153)-L153)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B153, $C$2:$C$767, C153, $D$2:$D$767, D153, $E$2:$E$767, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="10"/>
@@ -8370,11 +8348,11 @@
         <v>16755</v>
       </c>
       <c r="M154" s="18">
-        <f>ABS((D154*E154)-L154)</f>
+        <f t="shared" si="7"/>
         <v>295</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B154, $C$2:$C$767, C154, $D$2:$D$767, D154, $E$2:$E$767, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8416,11 +8394,11 @@
         <v>8049</v>
       </c>
       <c r="M155" s="18">
-        <f>ABS((D155*E155)-L155)</f>
+        <f t="shared" si="7"/>
         <v>800</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B155, $C$2:$C$767, C155, $D$2:$D$767, D155, $E$2:$E$767, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8462,11 +8440,11 @@
         <v>10510</v>
       </c>
       <c r="M156" s="18">
-        <f>ABS((D156*E156)-L156)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B156, $C$2:$C$767, C156, $D$2:$D$767, D156, $E$2:$E$767, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8508,11 +8486,11 @@
         <v>18800</v>
       </c>
       <c r="M157" s="18">
-        <f>ABS((D157*E157)-L157)</f>
+        <f t="shared" si="7"/>
         <v>500</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B157, $C$2:$C$767, C157, $D$2:$D$767, D157, $E$2:$E$767, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O157" s="47" t="s">
@@ -8557,11 +8535,11 @@
         <v>9470</v>
       </c>
       <c r="M158" s="18">
-        <f>ABS((D158*E158)-L158)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B158, $C$2:$C$767, C158, $D$2:$D$767, D158, $E$2:$E$767, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8597,7 +8575,7 @@
         <v>118</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B159, $C$2:$C$767, C159, $D$2:$D$767, D159, $E$2:$E$767, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8643,7 +8621,7 @@
         <v>300</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B160, $C$2:$C$767, C160, $D$2:$D$767, D160, $E$2:$E$767, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8682,7 +8660,7 @@
       <c r="L161" s="54"/>
       <c r="M161" s="54"/>
       <c r="N161" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B161, $C$2:$C$767, C161, $D$2:$D$767, D161, $E$2:$E$767, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="25"/>
@@ -8728,11 +8706,11 @@
         <v>12600</v>
       </c>
       <c r="M162" s="18">
-        <f>ABS((D162*E162)-L162)</f>
+        <f t="shared" ref="M162:M168" si="8">ABS((D162*E162)-L162)</f>
         <v>360</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B162, $C$2:$C$767, C162, $D$2:$D$767, D162, $E$2:$E$767, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8774,11 +8752,11 @@
         <v>3400</v>
       </c>
       <c r="M163" s="18">
-        <f>ABS((D163*E163)-L163)</f>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B163, $C$2:$C$767, C163, $D$2:$D$767, D163, $E$2:$E$767, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8820,11 +8798,11 @@
         <v>7578</v>
       </c>
       <c r="M164" s="33">
-        <f>ABS((D164*E164)-L164)</f>
+        <f t="shared" si="8"/>
         <v>294</v>
       </c>
       <c r="N164" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B164, $C$2:$C$767, C164, $D$2:$D$767, D164, $E$2:$E$767, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O164" s="10"/>
@@ -8868,40 +8846,40 @@
         <v>7578</v>
       </c>
       <c r="M165" s="33">
-        <f>ABS((D165*E165)-L165)</f>
+        <f t="shared" si="8"/>
         <v>294</v>
       </c>
       <c r="N165" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B165, $C$2:$C$767, C165, $D$2:$D$767, D165, $E$2:$E$767, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
     <row r="166" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="69">
+      <c r="A166" s="61">
         <v>46267.424305555556</v>
       </c>
-      <c r="B166" s="70" t="s">
+      <c r="B166" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="C166" s="70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D166" s="71">
+      <c r="C166" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D166" s="63">
         <v>2</v>
       </c>
-      <c r="E166" s="71">
+      <c r="E166" s="63">
         <v>2624</v>
       </c>
-      <c r="F166" s="71">
+      <c r="F166" s="63">
         <v>8.9746251919999995</v>
       </c>
-      <c r="G166" s="72" t="s">
+      <c r="G166" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="H166" s="73">
+      <c r="H166" s="65">
         <v>2407.9</v>
       </c>
-      <c r="I166" s="70" t="s">
+      <c r="I166" s="62" t="s">
         <v>8</v>
       </c>
       <c r="J166" s="33" t="s">
@@ -8914,40 +8892,40 @@
         <v>4968</v>
       </c>
       <c r="M166" s="33">
-        <f>ABS((D166*E166)-L166)</f>
+        <f t="shared" si="8"/>
         <v>280</v>
       </c>
       <c r="N166" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B166, $C$2:$C$767, C166, $D$2:$D$767, D166, $E$2:$E$767, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
     <row r="167" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="69">
+      <c r="A167" s="61">
         <v>46272.451388888891</v>
       </c>
-      <c r="B167" s="70" t="s">
+      <c r="B167" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C167" s="70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D167" s="71">
+      <c r="C167" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" s="63">
         <v>5</v>
       </c>
-      <c r="E167" s="71">
+      <c r="E167" s="63">
         <v>1894</v>
       </c>
-      <c r="F167" s="71">
+      <c r="F167" s="63">
         <v>8.975834292</v>
       </c>
-      <c r="G167" s="72" t="s">
+      <c r="G167" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="H167" s="73">
+      <c r="H167" s="65">
         <v>1738</v>
       </c>
-      <c r="I167" s="70" t="s">
+      <c r="I167" s="62" t="s">
         <v>8</v>
       </c>
       <c r="J167" s="35" t="s">
@@ -8960,40 +8938,40 @@
         <v>8820</v>
       </c>
       <c r="M167" s="33">
-        <f>ABS((D167*E167)-L167)</f>
+        <f t="shared" si="8"/>
         <v>650</v>
       </c>
       <c r="N167" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B167, $C$2:$C$767, C167, $D$2:$D$767, D167, $E$2:$E$767, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
     <row r="168" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="69">
+      <c r="A168" s="61">
         <v>46272.390972222223</v>
       </c>
-      <c r="B168" s="70" t="s">
+      <c r="B168" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C168" s="70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D168" s="71">
+      <c r="C168" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168" s="63">
         <v>20</v>
       </c>
-      <c r="E168" s="71">
+      <c r="E168" s="63">
         <v>1894</v>
       </c>
-      <c r="F168" s="71">
+      <c r="F168" s="63">
         <v>8.975834292</v>
       </c>
-      <c r="G168" s="72" t="s">
+      <c r="G168" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="H168" s="73">
+      <c r="H168" s="65">
         <v>1738</v>
       </c>
-      <c r="I168" s="70" t="s">
+      <c r="I168" s="62" t="s">
         <v>8</v>
       </c>
       <c r="J168" s="35" t="s">
@@ -9006,11 +8984,11 @@
         <v>36946</v>
       </c>
       <c r="M168" s="33">
-        <f>ABS((D168*E168)-L168)</f>
+        <f t="shared" si="8"/>
         <v>934</v>
       </c>
       <c r="N168" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B168, $C$2:$C$767, C168, $D$2:$D$767, D168, $E$2:$E$767, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9051,7 +9029,7 @@
       <c r="L169" s="17"/>
       <c r="M169" s="17"/>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B169, $C$2:$C$767, C169, $D$2:$D$767, D169, $E$2:$E$767, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9062,7 +9040,7 @@
       <c r="B170" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C170" s="74" t="s">
+      <c r="C170" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D170" s="8">
@@ -9085,7 +9063,7 @@
       </c>
       <c r="J170" s="40"/>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B170, $C$2:$C$767, C170, $D$2:$D$767, D170, $E$2:$E$767, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O170" s="35"/>
@@ -9132,7 +9110,7 @@
         <v>500</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B171, $C$2:$C$767, C171, $D$2:$D$767, D171, $E$2:$E$767, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9178,7 +9156,7 @@
         <v>450</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B172, $C$2:$C$767, C172, $D$2:$D$767, D172, $E$2:$E$767, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9214,7 +9192,7 @@
         <v>118</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B173, $C$2:$C$767, C173, $D$2:$D$767, D173, $E$2:$E$767, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9260,7 +9238,7 @@
         <v>300</v>
       </c>
       <c r="N174" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B174, $C$2:$C$767, C174, $D$2:$D$767, D174, $E$2:$E$767, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9306,7 +9284,7 @@
         <v>650</v>
       </c>
       <c r="N175" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B175, $C$2:$C$767, C175, $D$2:$D$767, D175, $E$2:$E$767, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O175" s="46" t="s">
@@ -9346,7 +9324,7 @@
         <v>117</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B176, $C$2:$C$767, C176, $D$2:$D$767, D176, $E$2:$E$767, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9392,7 +9370,7 @@
         <v>250</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B177, $C$2:$C$767, C177, $D$2:$D$767, D177, $E$2:$E$767, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9438,7 +9416,7 @@
         <v>300</v>
       </c>
       <c r="N178" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B178, $C$2:$C$767, C178, $D$2:$D$767, D178, $E$2:$E$767, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9475,7 +9453,7 @@
       <c r="L179" s="18"/>
       <c r="M179" s="18"/>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B179, $C$2:$C$767, C179, $D$2:$D$767, D179, $E$2:$E$767, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="10"/>
@@ -9523,7 +9501,7 @@
         <v>250</v>
       </c>
       <c r="N180" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B180, $C$2:$C$767, C180, $D$2:$D$767, D180, $E$2:$E$767, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="10"/>
@@ -9561,7 +9539,7 @@
         <v>156</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B181, $C$2:$C$767, C181, $D$2:$D$767, D181, $E$2:$E$767, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9597,7 +9575,7 @@
         <v>118</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B182, $C$2:$C$767, C182, $D$2:$D$767, D182, $E$2:$E$767, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O182" s="46" t="s">
@@ -9634,7 +9612,7 @@
       </c>
       <c r="J183" s="21"/>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B183, $C$2:$C$767, C183, $D$2:$D$767, D183, $E$2:$E$767, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9680,7 +9658,7 @@
         <v>300</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B184, $C$2:$C$767, C184, $D$2:$D$767, D184, $E$2:$E$767, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="46" t="s">
@@ -9730,7 +9708,7 @@
         <v>501</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B185, $C$2:$C$767, C185, $D$2:$D$767, D185, $E$2:$E$767, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="46" t="s">
@@ -9770,7 +9748,7 @@
         <v>117</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B186, $C$2:$C$767, C186, $D$2:$D$767, D186, $E$2:$E$767, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9816,7 +9794,7 @@
         <v>700</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B187, $C$2:$C$767, C187, $D$2:$D$767, D187, $E$2:$E$767, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O187" s="35"/>
@@ -9863,7 +9841,7 @@
         <v>250</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B188, $C$2:$C$767, C188, $D$2:$D$767, D188, $E$2:$E$767, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P188" s="35"/>
@@ -9910,7 +9888,7 @@
         <v>1000</v>
       </c>
       <c r="N189" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B189, $C$2:$C$767, C189, $D$2:$D$767, D189, $E$2:$E$767, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P189" s="35"/>
@@ -9957,7 +9935,7 @@
         <v>320</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B190, $C$2:$C$767, C190, $D$2:$D$767, D190, $E$2:$E$767, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10003,7 +9981,7 @@
         <v>448</v>
       </c>
       <c r="N191" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B191, $C$2:$C$767, C191, $D$2:$D$767, D191, $E$2:$E$767, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10039,7 +10017,7 @@
         <v>117</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B192, $C$2:$C$767, C192, $D$2:$D$767, D192, $E$2:$E$767, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10085,7 +10063,7 @@
         <v>300</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B193, $C$2:$C$767, C193, $D$2:$D$767, D193, $E$2:$E$767, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O193" s="10"/>
@@ -10121,7 +10099,7 @@
       </c>
       <c r="J194" s="40"/>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B194, $C$2:$C$767, C194, $D$2:$D$767, D194, $E$2:$E$767, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="9">IF(COUNTIFS( $B$2:$B$767, B194, $C$2:$C$767, C194, $D$2:$D$767, D194, $E$2:$E$767, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10167,7 +10145,7 @@
         <v>300</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B195, $C$2:$C$767, C195, $D$2:$D$767, D195, $E$2:$E$767, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P195" s="26"/>
@@ -10214,7 +10192,7 @@
         <v>400</v>
       </c>
       <c r="N196" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B196, $C$2:$C$767, C196, $D$2:$D$767, D196, $E$2:$E$767, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10253,7 +10231,7 @@
         <v>144</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B197, $C$2:$C$767, C197, $D$2:$D$767, D197, $E$2:$E$767, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10299,7 +10277,7 @@
         <v>140</v>
       </c>
       <c r="N198" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B198, $C$2:$C$767, C198, $D$2:$D$767, D198, $E$2:$E$767, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
       <c r="O198" s="10"/>
@@ -10346,7 +10324,7 @@
         <v>300</v>
       </c>
       <c r="N199" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B199, $C$2:$C$767, C199, $D$2:$D$767, D199, $E$2:$E$767, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
       <c r="O199" s="10"/>
@@ -10384,7 +10362,7 @@
         <v>117</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B200, $C$2:$C$767, C200, $D$2:$D$767, D200, $E$2:$E$767, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10418,7 +10396,7 @@
       </c>
       <c r="J201" s="40"/>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B201, $C$2:$C$767, C201, $D$2:$D$767, D201, $E$2:$E$767, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P201" s="35"/>
@@ -10465,7 +10443,7 @@
         <v>300</v>
       </c>
       <c r="N202" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B202, $C$2:$C$767, C202, $D$2:$D$767, D202, $E$2:$E$767, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="35"/>
@@ -10512,7 +10490,7 @@
         <v>253</v>
       </c>
       <c r="N203" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B203, $C$2:$C$767, C203, $D$2:$D$767, D203, $E$2:$E$767, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O203" s="35"/>
@@ -10559,7 +10537,7 @@
         <v>260</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B204, $C$2:$C$767, C204, $D$2:$D$767, D204, $E$2:$E$767, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10595,7 +10573,7 @@
         <v>198</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B205, $C$2:$C$767, C205, $D$2:$D$767, D205, $E$2:$E$767, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10631,7 +10609,7 @@
         <v>117</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B206, $C$2:$C$767, C206, $D$2:$D$767, D206, $E$2:$E$767, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10667,7 +10645,7 @@
         <v>118</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B207, $C$2:$C$767, C207, $D$2:$D$767, D207, $E$2:$E$767, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10713,7 +10691,7 @@
         <v>800</v>
       </c>
       <c r="N208" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B208, $C$2:$C$767, C208, $D$2:$D$767, D208, $E$2:$E$767, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10759,7 +10737,7 @@
         <v>300</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B209, $C$2:$C$767, C209, $D$2:$D$767, D209, $E$2:$E$767, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10805,7 +10783,7 @@
         <v>188</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B210, $C$2:$C$767, C210, $D$2:$D$767, D210, $E$2:$E$767, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P210" s="35"/>
@@ -10842,7 +10820,7 @@
         <v>55</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B211, $C$2:$C$767, C211, $D$2:$D$767, D211, $E$2:$E$767, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10881,7 +10859,7 @@
         <v>145</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B212, $C$2:$C$767, C212, $D$2:$D$767, D212, $E$2:$E$767, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10927,7 +10905,7 @@
         <v>940</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B213, $C$2:$C$767, C213, $D$2:$D$767, D213, $E$2:$E$767, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10973,7 +10951,7 @@
         <v>450</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B214, $C$2:$C$767, C214, $D$2:$D$767, D214, $E$2:$E$767, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11009,7 +10987,7 @@
         <v>118</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B215, $C$2:$C$767, C215, $D$2:$D$767, D215, $E$2:$E$767, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11055,7 +11033,7 @@
         <v>300</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B216, $C$2:$C$767, C216, $D$2:$D$767, D216, $E$2:$E$767, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11091,7 +11069,7 @@
         <v>118</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B217, $C$2:$C$767, C217, $D$2:$D$767, D217, $E$2:$E$767, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11137,7 +11115,7 @@
         <v>370</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B218, $C$2:$C$767, C218, $D$2:$D$767, D218, $E$2:$E$767, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P218" s="35"/>
@@ -11184,7 +11162,7 @@
         <v>527.5</v>
       </c>
       <c r="N219" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B219, $C$2:$C$767, C219, $D$2:$D$767, D219, $E$2:$E$767, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O219" s="35"/>
@@ -11227,7 +11205,7 @@
       <c r="L220" s="33"/>
       <c r="M220" s="33"/>
       <c r="N220" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B220, $C$2:$C$767, C220, $D$2:$D$767, D220, $E$2:$E$767, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O220" s="35"/>
@@ -11266,7 +11244,7 @@
       <c r="L221" s="18"/>
       <c r="M221" s="18"/>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B221, $C$2:$C$767, C221, $D$2:$D$767, D221, $E$2:$E$767, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="10"/>
@@ -11314,7 +11292,7 @@
         <v>1800</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B222, $C$2:$C$767, C222, $D$2:$D$767, D222, $E$2:$E$767, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11348,7 +11326,7 @@
       </c>
       <c r="J223" s="40"/>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B223, $C$2:$C$767, C223, $D$2:$D$767, D223, $E$2:$E$767, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11394,7 +11372,7 @@
         <v>650</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B224, $C$2:$C$767, C224, $D$2:$D$767, D224, $E$2:$E$767, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O224" s="35"/>
@@ -11441,7 +11419,7 @@
         <v>500</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B225, $C$2:$C$767, C225, $D$2:$D$767, D225, $E$2:$E$767, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O225" s="46" t="s">
@@ -11483,7 +11461,7 @@
       <c r="L226" s="18"/>
       <c r="M226" s="18"/>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B226, $C$2:$C$767, C226, $D$2:$D$767, D226, $E$2:$E$767, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P226" s="10"/>
@@ -11520,7 +11498,7 @@
         <v>117</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B227, $C$2:$C$767, C227, $D$2:$D$767, D227, $E$2:$E$767, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11554,7 +11532,7 @@
       </c>
       <c r="J228" s="40"/>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B228, $C$2:$C$767, C228, $D$2:$D$767, D228, $E$2:$E$767, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11588,7 +11566,7 @@
       </c>
       <c r="J229" s="40"/>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B229, $C$2:$C$767, C229, $D$2:$D$767, D229, $E$2:$E$767, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="35"/>
@@ -11625,7 +11603,7 @@
         <v>118</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B230, $C$2:$C$767, C230, $D$2:$D$767, D230, $E$2:$E$767, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11659,7 +11637,7 @@
       </c>
       <c r="J231" s="40"/>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B231, $C$2:$C$767, C231, $D$2:$D$767, D231, $E$2:$E$767, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11705,7 +11683,7 @@
         <v>260</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B232, $C$2:$C$767, C232, $D$2:$D$767, D232, $E$2:$E$767, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11739,7 +11717,7 @@
       </c>
       <c r="J233" s="40"/>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B233, $C$2:$C$767, C233, $D$2:$D$767, D233, $E$2:$E$767, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11785,7 +11763,7 @@
         <v>250</v>
       </c>
       <c r="N234" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B234, $C$2:$C$767, C234, $D$2:$D$767, D234, $E$2:$E$767, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11831,7 +11809,7 @@
         <v>300</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B235, $C$2:$C$767, C235, $D$2:$D$767, D235, $E$2:$E$767, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11867,7 +11845,7 @@
         <v>117</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B236, $C$2:$C$767, C236, $D$2:$D$767, D236, $E$2:$E$767, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11901,7 +11879,7 @@
       </c>
       <c r="J237" s="40"/>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B237, $C$2:$C$767, C237, $D$2:$D$767, D237, $E$2:$E$767, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11947,7 +11925,7 @@
         <v>300</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B238, $C$2:$C$767, C238, $D$2:$D$767, D238, $E$2:$E$767, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11983,7 +11961,7 @@
         <v>55</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B239, $C$2:$C$767, C239, $D$2:$D$767, D239, $E$2:$E$767, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12019,7 +11997,7 @@
         <v>117</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B240, $C$2:$C$767, C240, $D$2:$D$767, D240, $E$2:$E$767, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P240" s="35"/>
@@ -12066,7 +12044,7 @@
         <v>650</v>
       </c>
       <c r="N241" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B241, $C$2:$C$767, C241, $D$2:$D$767, D241, $E$2:$E$767, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P241" s="35"/>
@@ -12103,7 +12081,7 @@
         <v>118</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B242, $C$2:$C$767, C242, $D$2:$D$767, D242, $E$2:$E$767, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12139,7 +12117,7 @@
         <v>118</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B243, $C$2:$C$767, C243, $D$2:$D$767, D243, $E$2:$E$767, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O243" s="35"/>
@@ -12176,7 +12154,7 @@
         <v>118</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B244, $C$2:$C$767, C244, $D$2:$D$767, D244, $E$2:$E$767, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12213,7 +12191,7 @@
       <c r="L245" s="18"/>
       <c r="M245" s="18"/>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B245, $C$2:$C$767, C245, $D$2:$D$767, D245, $E$2:$E$767, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="10"/>
@@ -12251,7 +12229,7 @@
         <v>117</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B246, $C$2:$C$767, C246, $D$2:$D$767, D246, $E$2:$E$767, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12297,7 +12275,7 @@
         <v>285</v>
       </c>
       <c r="N247" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B247, $C$2:$C$767, C247, $D$2:$D$767, D247, $E$2:$E$767, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12343,7 +12321,7 @@
         <v>726</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B248, $C$2:$C$767, C248, $D$2:$D$767, D248, $E$2:$E$767, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12382,7 +12360,7 @@
         <v>146</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B249, $C$2:$C$767, C249, $D$2:$D$767, D249, $E$2:$E$767, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12416,7 +12394,7 @@
       </c>
       <c r="J250" s="40"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B250, $C$2:$C$767, C250, $D$2:$D$767, D250, $E$2:$E$767, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12450,7 +12428,7 @@
       </c>
       <c r="J251" s="40"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B251, $C$2:$C$767, C251, $D$2:$D$767, D251, $E$2:$E$767, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12484,7 +12462,7 @@
       </c>
       <c r="J252" s="40"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B252, $C$2:$C$767, C252, $D$2:$D$767, D252, $E$2:$E$767, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12530,7 +12508,7 @@
         <v>300</v>
       </c>
       <c r="N253" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B253, $C$2:$C$767, C253, $D$2:$D$767, D253, $E$2:$E$767, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12576,7 +12554,7 @@
         <v>300</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B254, $C$2:$C$767, C254, $D$2:$D$767, D254, $E$2:$E$767, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="10"/>
@@ -12612,7 +12590,7 @@
       </c>
       <c r="J255" s="40"/>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B255, $C$2:$C$767, C255, $D$2:$D$767, D255, $E$2:$E$767, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12658,7 +12636,7 @@
         <v>275</v>
       </c>
       <c r="N256" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B256, $C$2:$C$767, C256, $D$2:$D$767, D256, $E$2:$E$767, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12692,7 +12670,7 @@
       </c>
       <c r="J257" s="40"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B257, $C$2:$C$767, C257, $D$2:$D$767, D257, $E$2:$E$767, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12728,7 +12706,7 @@
         <v>118</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B258, $C$2:$C$767, C258, $D$2:$D$767, D258, $E$2:$E$767, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N291" si="10">IF(COUNTIFS( $B$2:$B$767, B258, $C$2:$C$767, C258, $D$2:$D$767, D258, $E$2:$E$767, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12762,7 +12740,7 @@
       </c>
       <c r="J259" s="40"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B259, $C$2:$C$767, C259, $D$2:$D$767, D259, $E$2:$E$767, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12798,7 +12776,7 @@
         <v>118</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B260, $C$2:$C$767, C260, $D$2:$D$767, D260, $E$2:$E$767, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="35"/>
@@ -12835,7 +12813,7 @@
         <v>118</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B261, $C$2:$C$767, C261, $D$2:$D$767, D261, $E$2:$E$767, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12881,7 +12859,7 @@
         <v>480</v>
       </c>
       <c r="N262" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B262, $C$2:$C$767, C262, $D$2:$D$767, D262, $E$2:$E$767, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12915,7 +12893,7 @@
       </c>
       <c r="J263" s="40"/>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B263, $C$2:$C$767, C263, $D$2:$D$767, D263, $E$2:$E$767, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P263" s="35"/>
@@ -12950,7 +12928,7 @@
       </c>
       <c r="J264" s="40"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B264, $C$2:$C$767, C264, $D$2:$D$767, D264, $E$2:$E$767, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12986,7 +12964,7 @@
         <v>118</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B265, $C$2:$C$767, C265, $D$2:$D$767, D265, $E$2:$E$767, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13032,7 +13010,7 @@
         <v>250</v>
       </c>
       <c r="N266" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B266, $C$2:$C$767, C266, $D$2:$D$767, D266, $E$2:$E$767, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P266" s="35"/>
@@ -13069,7 +13047,7 @@
         <v>117</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B267, $C$2:$C$767, C267, $D$2:$D$767, D267, $E$2:$E$767, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13105,7 +13083,7 @@
         <v>118</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B268, $C$2:$C$767, C268, $D$2:$D$767, D268, $E$2:$E$767, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13139,7 +13117,7 @@
       </c>
       <c r="J269" s="40"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B269, $C$2:$C$767, C269, $D$2:$D$767, D269, $E$2:$E$767, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13185,7 +13163,7 @@
         <v>300</v>
       </c>
       <c r="N270" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B270, $C$2:$C$767, C270, $D$2:$D$767, D270, $E$2:$E$767, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13219,7 +13197,7 @@
       </c>
       <c r="J271" s="40"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B271, $C$2:$C$767, C271, $D$2:$D$767, D271, $E$2:$E$767, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13253,7 +13231,7 @@
       </c>
       <c r="J272" s="40"/>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B272, $C$2:$C$767, C272, $D$2:$D$767, D272, $E$2:$E$767, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13287,7 +13265,7 @@
       </c>
       <c r="J273" s="40"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B273, $C$2:$C$767, C273, $D$2:$D$767, D273, $E$2:$E$767, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O273" s="35"/>
@@ -13322,7 +13300,7 @@
       </c>
       <c r="J274" s="40"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B274, $C$2:$C$767, C274, $D$2:$D$767, D274, $E$2:$E$767, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13358,7 +13336,7 @@
         <v>118</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B275, $C$2:$C$767, C275, $D$2:$D$767, D275, $E$2:$E$767, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13392,7 +13370,7 @@
       </c>
       <c r="J276" s="40"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B276, $C$2:$C$767, C276, $D$2:$D$767, D276, $E$2:$E$767, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13438,7 +13416,7 @@
         <v>250</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B277, $C$2:$C$767, C277, $D$2:$D$767, D277, $E$2:$E$767, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13472,7 +13450,7 @@
       </c>
       <c r="J278" s="40"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B278, $C$2:$C$767, C278, $D$2:$D$767, D278, $E$2:$E$767, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13506,7 +13484,7 @@
       </c>
       <c r="J279" s="40"/>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B279, $C$2:$C$767, C279, $D$2:$D$767, D279, $E$2:$E$767, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P279" s="35"/>
@@ -13541,7 +13519,7 @@
       </c>
       <c r="J280" s="40"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B280, $C$2:$C$767, C280, $D$2:$D$767, D280, $E$2:$E$767, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13575,7 +13553,7 @@
       </c>
       <c r="J281" s="40"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B281, $C$2:$C$767, C281, $D$2:$D$767, D281, $E$2:$E$767, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13609,7 +13587,7 @@
       </c>
       <c r="J282" s="40"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B282, $C$2:$C$767, C282, $D$2:$D$767, D282, $E$2:$E$767, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13645,7 +13623,7 @@
         <v>118</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B283, $C$2:$C$767, C283, $D$2:$D$767, D283, $E$2:$E$767, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13681,7 +13659,7 @@
         <v>55</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B284, $C$2:$C$767, C284, $D$2:$D$767, D284, $E$2:$E$767, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13717,7 +13695,7 @@
         <v>118</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B285, $C$2:$C$767, C285, $D$2:$D$767, D285, $E$2:$E$767, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13751,7 +13729,7 @@
       </c>
       <c r="J286" s="40"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B286, $C$2:$C$767, C286, $D$2:$D$767, D286, $E$2:$E$767, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13797,7 +13775,7 @@
         <v>250</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B287, $C$2:$C$767, C287, $D$2:$D$767, D287, $E$2:$E$767, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13831,7 +13809,7 @@
       </c>
       <c r="J288" s="40"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B288, $C$2:$C$767, C288, $D$2:$D$767, D288, $E$2:$E$767, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13865,7 +13843,7 @@
       </c>
       <c r="J289" s="40"/>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B289, $C$2:$C$767, C289, $D$2:$D$767, D289, $E$2:$E$767, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13899,7 +13877,7 @@
       </c>
       <c r="J290" s="40"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B290, $C$2:$C$767, C290, $D$2:$D$767, D290, $E$2:$E$767, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O290" s="35"/>
@@ -13934,7 +13912,7 @@
       </c>
       <c r="J291" s="40"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$767, B291, $C$2:$C$767, C291, $D$2:$D$767, D291, $E$2:$E$767, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
